--- a/BELGRANO 1646/Octubre/Octubre-BLG1646.xlsx
+++ b/BELGRANO 1646/Octubre/Octubre-BLG1646.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistema\Desktop\rc-consorcio2025\BELGRANO 1646\Octubre\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\RC CONSORCIO 2025\BELGRANO 1646\Octubre\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06B96ADE-A2E8-42CB-B756-427A04C25C76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2BD8B6A-6E5B-466C-99CF-6CEA2744A355}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RESUMEN" sheetId="1" r:id="rId1"/>
@@ -20,14 +20,14 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="1">PRORRATEO!$A$1:$N$64</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$F$124</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$F$120</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="271" uniqueCount="178">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="266" uniqueCount="173">
   <si>
     <t>consorciobelgrano1640@gmail.com</t>
   </si>
@@ -523,54 +523,6 @@
     <t>GASTOS PARTICULARES</t>
   </si>
   <si>
-    <t>Servisur - programacion de relojes</t>
-  </si>
-  <si>
-    <t>Servisur - plafones led de 12W en escaleras y pallieres - Sensor de movimiento escalera piso 5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Casa Ruan - 14 plafones led y un sensor </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Prestigio - compra de Loxon Color </t>
-  </si>
-  <si>
-    <t>Salvatierra Matias -Servicio de diagnostico por imágenes en 6B - Cuota 2/2</t>
-  </si>
-  <si>
-    <t>SEGURO OBLIGATORIO SR DIEGO BRITEZ FEDERACION PATRONAL DEBITO AUTOMATICO 04/09</t>
-  </si>
-  <si>
-    <t>Numero 1859135 Debito automatico 01/09</t>
-  </si>
-  <si>
-    <t>Debito 02/09</t>
-  </si>
-  <si>
-    <t>Pago mis cuentas 05/09</t>
-  </si>
-  <si>
-    <t>Debito 12/09</t>
-  </si>
-  <si>
-    <t>Debito 23/09</t>
-  </si>
-  <si>
-    <t>Fumigacion 29/09</t>
-  </si>
-  <si>
-    <t>Mano de obra y materiales trabajo en UF 28 - Por ruidos molestos</t>
-  </si>
-  <si>
-    <t>Rohe - Envio de ceramicas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Leonardo Balcazza - Sellado de balcon parte de losa, salida carpinteria mecanica, sellado de fisuras entre union de olsas y pared -  Aplicación de tapagoteras SIKA UF 43 </t>
-  </si>
-  <si>
-    <t>Energroup</t>
-  </si>
-  <si>
     <t>VTO: 14/11</t>
   </si>
   <si>
@@ -580,12 +532,6 @@
     <t>Contessi - Provision y colocacion de tres tubos de luz led en cabinas de los acensores</t>
   </si>
   <si>
-    <t>Carta documento 11A</t>
-  </si>
-  <si>
-    <t>Envio carta documento</t>
-  </si>
-  <si>
     <t>Ferreteria el herrero - Lamparas, pico, pinceleta, rodillo, aguarras x3, cinta, silicona, etc</t>
   </si>
   <si>
@@ -596,6 +542,45 @@
   </si>
   <si>
     <t>Ingreso mes de SEPTIEMBRE</t>
+  </si>
+  <si>
+    <t>Numero 1859135 Debito automatico 01/10</t>
+  </si>
+  <si>
+    <t>Debito 02/10</t>
+  </si>
+  <si>
+    <t>SEGURO OBLIGATORIO SR DIEGO BRITEZ FEDERACION PATRONAL DEBITO AUTOMATICO 06/10</t>
+  </si>
+  <si>
+    <t>Pago mis cuentas 08/10</t>
+  </si>
+  <si>
+    <t>Debito 13/10</t>
+  </si>
+  <si>
+    <t>Luis Barrazza - Colocacion de porcelanatos - UF 27 y 29</t>
+  </si>
+  <si>
+    <t>Debito 24/10</t>
+  </si>
+  <si>
+    <t>Fumigacion 28/10</t>
+  </si>
+  <si>
+    <t>Energroup - SERVICE DE MANTENIMIENTO PREVENTIVO</t>
+  </si>
+  <si>
+    <t>Energroup - SERVICIO CORRECTIVO CAMBIO DE BATERIAS POR 2 UNIDADES DE 180 AMP</t>
+  </si>
+  <si>
+    <t>Medianera Mural - Reparacion de sellados de vidrios (frente y contrafrente) departamentos "A" en pisos 12, 10, 8 y 3 - 09/10</t>
+  </si>
+  <si>
+    <t>Cartas de documento 11A</t>
+  </si>
+  <si>
+    <t>Envios cartas documento</t>
   </si>
 </sst>
 </file>
@@ -613,7 +598,7 @@
     <numFmt numFmtId="167" formatCode="_-&quot;$&quot;\ * #,##0_-;\-&quot;$&quot;\ * #,##0_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="168" formatCode="_-[$$-2C0A]\ * #,##0.00_-;\-[$$-2C0A]\ * #,##0.00_-;_-[$$-2C0A]\ * &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="24" x14ac:knownFonts="1">
+  <fonts count="25" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -785,6 +770,13 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="12">
     <fill>
@@ -1324,7 +1316,7 @@
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="250">
+  <cellXfs count="248">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="34" xfId="0" applyBorder="1"/>
@@ -1534,9 +1526,6 @@
     <xf numFmtId="44" fontId="6" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="6" fontId="6" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="44" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="44" fontId="14" fillId="6" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="2" fillId="6" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1559,7 +1548,6 @@
     <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="44" fontId="15" fillId="9" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="21" fillId="3" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
@@ -1592,28 +1580,12 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="167" fontId="6" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="167" fontId="6" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="167" fontId="4" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="6" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="44" fontId="20" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1696,51 +1668,51 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="6" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="35" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="37" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="5" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="5" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="31" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="33" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="15" fillId="5" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="6" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="35" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="37" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="5" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="5" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="11" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1765,6 +1737,12 @@
     <xf numFmtId="0" fontId="2" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="44" fontId="20" fillId="3" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="6" fillId="11" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="4" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="6" fontId="24" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="21" fillId="3" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="15" fillId="9" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Millares" xfId="3" builtinId="3"/>
@@ -2130,24 +2108,24 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:P134"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:P130"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="33.44140625" customWidth="1"/>
-    <col min="2" max="2" width="36.88671875" customWidth="1"/>
-    <col min="3" max="3" width="17.44140625" customWidth="1"/>
-    <col min="4" max="4" width="21.6640625" customWidth="1"/>
-    <col min="5" max="5" width="15.6640625" customWidth="1"/>
+    <col min="1" max="1" width="33.42578125" customWidth="1"/>
+    <col min="2" max="2" width="36.85546875" customWidth="1"/>
+    <col min="3" max="3" width="17.42578125" customWidth="1"/>
+    <col min="4" max="4" width="21.7109375" customWidth="1"/>
+    <col min="5" max="5" width="15.7109375" customWidth="1"/>
     <col min="6" max="6" width="13" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.88671875" customWidth="1"/>
-    <col min="8" max="8" width="14.88671875" customWidth="1"/>
+    <col min="7" max="7" width="15.85546875" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" customWidth="1"/>
     <col min="9" max="9" width="13" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.5546875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.5703125" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="18" customWidth="1"/>
-    <col min="13" max="13" width="18.33203125" customWidth="1"/>
+    <col min="13" max="13" width="18.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="8"/>
       <c r="B1" s="97" t="s">
         <v>118</v>
@@ -2156,7 +2134,7 @@
       <c r="D1" s="8"/>
       <c r="E1" s="8"/>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="64"/>
       <c r="B2" s="65" t="s">
         <v>0</v>
@@ -2165,7 +2143,7 @@
       <c r="D2" s="65"/>
       <c r="E2" s="66"/>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="67"/>
       <c r="B3" s="68" t="s">
         <v>88</v>
@@ -2174,7 +2152,7 @@
       <c r="D3" s="68"/>
       <c r="E3" s="69"/>
     </row>
-    <row r="4" spans="1:5" ht="33.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:5" ht="33.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="67"/>
       <c r="B4" s="68" t="s">
         <v>89</v>
@@ -2183,20 +2161,20 @@
       <c r="D4" s="68"/>
       <c r="E4" s="69"/>
     </row>
-    <row r="5" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="70" t="s">
         <v>1</v>
       </c>
       <c r="B5" s="71" t="s">
-        <v>175</v>
+        <v>157</v>
       </c>
       <c r="C5" s="71" t="s">
-        <v>169</v>
+        <v>153</v>
       </c>
       <c r="D5" s="71"/>
       <c r="E5" s="72"/>
     </row>
-    <row r="6" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="67" t="s">
         <v>99</v>
       </c>
@@ -2205,7 +2183,7 @@
       <c r="D6" s="68"/>
       <c r="E6" s="69"/>
     </row>
-    <row r="7" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="70" t="s">
         <v>98</v>
       </c>
@@ -2214,125 +2192,125 @@
       <c r="D7" s="71"/>
       <c r="E7" s="72"/>
     </row>
-    <row r="9" spans="1:5" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="10" spans="1:5" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="11" spans="1:5" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="12" spans="1:5" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B14" s="202" t="s">
+    <row r="9" spans="1:5" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="10" spans="1:5" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="11" spans="1:5" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="12" spans="1:5" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B14" s="194" t="s">
         <v>134</v>
       </c>
-      <c r="C14" s="203"/>
-      <c r="D14" s="204"/>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B15" s="205"/>
-      <c r="C15" s="206"/>
-      <c r="D15" s="207"/>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B16" s="205"/>
-      <c r="C16" s="206"/>
-      <c r="D16" s="207"/>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="B17" s="208"/>
-      <c r="C17" s="209"/>
-      <c r="D17" s="210"/>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="C14" s="195"/>
+      <c r="D14" s="196"/>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B15" s="197"/>
+      <c r="C15" s="198"/>
+      <c r="D15" s="199"/>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B16" s="197"/>
+      <c r="C16" s="198"/>
+      <c r="D16" s="199"/>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B17" s="200"/>
+      <c r="C17" s="201"/>
+      <c r="D17" s="202"/>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" s="3"/>
     </row>
-    <row r="20" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="21" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="21" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A21" s="61" t="s">
         <v>86</v>
       </c>
       <c r="B21" s="62"/>
       <c r="C21" s="63"/>
       <c r="D21" s="59"/>
-      <c r="E21" s="186" t="s">
+      <c r="E21" s="184" t="s">
         <v>121</v>
       </c>
-      <c r="F21" s="187" t="s">
+      <c r="F21" s="185" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" s="120" t="s">
         <v>142</v>
       </c>
       <c r="B22" s="7" t="s">
-        <v>176</v>
+        <v>158</v>
       </c>
       <c r="C22" s="7"/>
       <c r="D22" s="129"/>
-      <c r="E22" s="185"/>
-      <c r="F22" s="185"/>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="E22" s="183"/>
+      <c r="F22" s="183"/>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" s="120" t="s">
         <v>126</v>
       </c>
       <c r="B23" s="7"/>
       <c r="C23" s="7"/>
-      <c r="D23" s="172">
-        <v>1356359.4</v>
+      <c r="D23" s="242">
+        <v>1376395.8</v>
       </c>
       <c r="E23" s="133">
         <f>D23*91.91%</f>
-        <v>1246629.9245399998</v>
+        <v>1265045.3797799998</v>
       </c>
       <c r="F23" s="133">
         <f>D23*8.09%</f>
-        <v>109729.47545999999</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
+        <v>111350.42022</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" s="120" t="s">
         <v>2</v>
       </c>
       <c r="B24" s="7"/>
       <c r="C24" s="7"/>
-      <c r="D24" s="172">
-        <v>-295008.15999999997</v>
+      <c r="D24" s="242">
+        <v>-299366.09000000003</v>
       </c>
       <c r="E24" s="133">
         <f t="shared" ref="E24:E25" si="0">D24*91.91%</f>
-        <v>-271141.99985599995</v>
+        <v>-275147.37331900001</v>
       </c>
       <c r="F24" s="133">
         <f t="shared" ref="F24:F25" si="1">D24*8.09%</f>
-        <v>-23866.160143999998</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
+        <v>-24218.716681000002</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" s="120" t="s">
         <v>112</v>
       </c>
       <c r="B25" s="7"/>
       <c r="C25" s="7"/>
-      <c r="D25" s="172">
-        <v>0.76</v>
+      <c r="D25" s="242">
+        <v>0.28999999999999998</v>
       </c>
       <c r="E25" s="133">
         <f t="shared" si="0"/>
-        <v>0.69851599999999991</v>
+        <v>0.26653899999999997</v>
       </c>
       <c r="F25" s="133">
         <f t="shared" si="1"/>
-        <v>6.1484000000000004E-2</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
+        <v>2.3460999999999999E-2</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" s="120"/>
       <c r="B26" s="7"/>
       <c r="C26" s="7"/>
-      <c r="D26" s="172"/>
+      <c r="D26" s="170"/>
       <c r="E26" s="133"/>
       <c r="F26" s="7"/>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" s="95" t="s">
         <v>3</v>
       </c>
@@ -2340,32 +2318,32 @@
       <c r="C27" s="95"/>
       <c r="D27" s="107">
         <f>SUM(D23:D26)</f>
-        <v>1061352</v>
+        <v>1077030</v>
       </c>
       <c r="E27" s="107">
         <f>SUM(E23:E26)</f>
-        <v>975488.6231999998</v>
+        <v>989898.27299999981</v>
       </c>
       <c r="F27" s="107">
         <f>SUM(F23:F26)</f>
-        <v>85863.376799999998</v>
+        <v>87131.726999999999</v>
       </c>
       <c r="G27" s="108">
         <f>E27+F27</f>
-        <v>1061351.9999999998</v>
+        <v>1077029.9999999998</v>
       </c>
       <c r="H27" s="146" t="str">
         <f>IF(D27=G27, "", "Error")</f>
         <v/>
       </c>
     </row>
-    <row r="28" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A28" s="94" t="s">
         <v>109</v>
       </c>
       <c r="B28" s="7"/>
       <c r="C28" s="7"/>
-      <c r="D28" s="173">
+      <c r="D28" s="171">
         <v>0</v>
       </c>
       <c r="E28" s="133">
@@ -2378,11 +2356,11 @@
       </c>
       <c r="H28" s="146"/>
     </row>
-    <row r="29" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A29" s="94"/>
       <c r="B29" s="7"/>
       <c r="C29" s="7"/>
-      <c r="D29" s="172">
+      <c r="D29" s="170">
         <v>0</v>
       </c>
       <c r="E29" s="133">
@@ -2395,25 +2373,25 @@
       </c>
       <c r="H29" s="146"/>
     </row>
-    <row r="30" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A30" s="94"/>
       <c r="B30" s="7"/>
       <c r="C30" s="7"/>
-      <c r="D30" s="172"/>
+      <c r="D30" s="170"/>
       <c r="E30" s="7"/>
       <c r="F30" s="7"/>
       <c r="H30" s="146"/>
     </row>
-    <row r="31" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A31" s="94"/>
       <c r="B31" s="7"/>
       <c r="C31" s="7"/>
-      <c r="D31" s="172"/>
+      <c r="D31" s="170"/>
       <c r="E31" s="7"/>
       <c r="F31" s="7"/>
       <c r="H31" s="146"/>
     </row>
-    <row r="32" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A32" s="95" t="s">
         <v>117</v>
       </c>
@@ -2440,13 +2418,13 @@
         <v/>
       </c>
     </row>
-    <row r="33" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A33" s="94" t="s">
         <v>109</v>
       </c>
       <c r="B33" s="7"/>
       <c r="C33" s="7"/>
-      <c r="D33" s="173"/>
+      <c r="D33" s="171"/>
       <c r="E33" s="133">
         <f>D33*91.91%</f>
         <v>0</v>
@@ -2457,13 +2435,13 @@
       </c>
       <c r="H33" s="146"/>
     </row>
-    <row r="34" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A34" s="7" t="s">
         <v>130</v>
       </c>
       <c r="B34" s="7"/>
       <c r="C34" s="7"/>
-      <c r="D34" s="172"/>
+      <c r="D34" s="170"/>
       <c r="E34" s="133">
         <f t="shared" ref="E34:E35" si="3">D34*91.91%</f>
         <v>0</v>
@@ -2474,13 +2452,13 @@
       </c>
       <c r="H34" s="146"/>
     </row>
-    <row r="35" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A35" s="94" t="s">
         <v>2</v>
       </c>
       <c r="B35" s="7"/>
       <c r="C35" s="7"/>
-      <c r="D35" s="172"/>
+      <c r="D35" s="170"/>
       <c r="E35" s="133">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -2491,7 +2469,7 @@
       </c>
       <c r="H35" s="146"/>
     </row>
-    <row r="36" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A36" s="95" t="s">
         <v>110</v>
       </c>
@@ -2511,34 +2489,34 @@
       </c>
       <c r="H36" s="146"/>
     </row>
-    <row r="37" spans="1:8" ht="0.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:8" ht="0.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="128"/>
       <c r="B37" s="98"/>
       <c r="C37" s="98"/>
-      <c r="D37" s="172"/>
+      <c r="D37" s="170"/>
       <c r="E37" s="119"/>
       <c r="F37" s="119"/>
       <c r="H37" s="146"/>
     </row>
-    <row r="38" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A38" s="128"/>
       <c r="B38" s="98"/>
       <c r="C38" s="98"/>
-      <c r="D38" s="172"/>
+      <c r="D38" s="170"/>
       <c r="E38" s="119"/>
       <c r="F38" s="119"/>
       <c r="H38" s="146"/>
     </row>
-    <row r="39" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A39" s="98"/>
       <c r="B39" s="98"/>
       <c r="C39" s="110"/>
-      <c r="D39" s="172"/>
+      <c r="D39" s="170"/>
       <c r="E39" s="119"/>
       <c r="F39" s="119"/>
       <c r="H39" s="146"/>
     </row>
-    <row r="40" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A40" s="95" t="s">
         <v>117</v>
       </c>
@@ -2555,7 +2533,7 @@
       </c>
       <c r="H40" s="146"/>
     </row>
-    <row r="41" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A41" s="94"/>
       <c r="B41" s="7"/>
       <c r="C41" s="7"/>
@@ -2570,7 +2548,7 @@
       </c>
       <c r="H41" s="146"/>
     </row>
-    <row r="42" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A42" s="94"/>
       <c r="B42" s="7"/>
       <c r="C42" s="7"/>
@@ -2585,11 +2563,11 @@
       </c>
       <c r="H42" s="146"/>
     </row>
-    <row r="43" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A43" s="94"/>
       <c r="B43" s="7"/>
       <c r="C43" s="7"/>
-      <c r="D43" s="175"/>
+      <c r="D43" s="173"/>
       <c r="E43" s="133">
         <f>D43*91.91%</f>
         <v>0</v>
@@ -2600,7 +2578,7 @@
       </c>
       <c r="H43" s="146"/>
     </row>
-    <row r="44" spans="1:8" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:8" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A44" s="95" t="s">
         <v>127</v>
       </c>
@@ -2610,11 +2588,11 @@
         <f>SUM(D41:D43)</f>
         <v>0</v>
       </c>
-      <c r="E44" s="154">
+      <c r="E44" s="153">
         <f>SUM(E41:E43)</f>
         <v>0</v>
       </c>
-      <c r="F44" s="162">
+      <c r="F44" s="161">
         <f>SUM(F41:F43)</f>
         <v>0</v>
       </c>
@@ -2624,24 +2602,24 @@
       </c>
       <c r="H44" s="146"/>
     </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A45" s="94" t="s">
         <v>4</v>
       </c>
       <c r="B45" s="7"/>
       <c r="C45" s="7"/>
-      <c r="D45" s="175"/>
+      <c r="D45" s="173"/>
       <c r="E45" s="113"/>
       <c r="F45" s="100"/>
       <c r="H45" s="146"/>
     </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A46" s="94" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="B46" s="7"/>
       <c r="C46" s="98"/>
-      <c r="D46" s="112">
+      <c r="D46" s="180">
         <v>5020</v>
       </c>
       <c r="E46" s="133">
@@ -2654,15 +2632,15 @@
       </c>
       <c r="H46" s="146"/>
     </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A47" s="94" t="s">
         <v>5</v>
       </c>
       <c r="B47" s="7" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="C47" s="7"/>
-      <c r="D47" s="182">
+      <c r="D47" s="180">
         <f>113583.37+6781.8+61036.17</f>
         <v>181401.34</v>
       </c>
@@ -2676,28 +2654,29 @@
       </c>
       <c r="H47" s="146"/>
     </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A48" s="94" t="s">
         <v>135</v>
       </c>
       <c r="B48" s="98" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="C48" s="7"/>
-      <c r="D48" s="182">
-        <v>14011.05</v>
+      <c r="D48" s="180">
+        <f>600931.76+14011.05</f>
+        <v>614942.81000000006</v>
       </c>
       <c r="E48" s="133">
         <f>D48*91.91%</f>
-        <v>12877.556054999997</v>
+        <v>565193.93667099997</v>
       </c>
       <c r="F48" s="133">
         <f>D48*8.09%</f>
-        <v>1133.4939449999999</v>
+        <v>49748.873329000002</v>
       </c>
       <c r="H48" s="146"/>
     </row>
-    <row r="49" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A49" s="95" t="s">
         <v>6</v>
       </c>
@@ -2705,43 +2684,43 @@
       <c r="C49" s="96"/>
       <c r="D49" s="107">
         <f>SUM(D46:D48)</f>
-        <v>200432.38999999998</v>
+        <v>801364.15</v>
       </c>
       <c r="E49" s="107">
         <f t="shared" ref="E49:F49" si="6">SUM(E46:E48)</f>
-        <v>184217.40964899998</v>
+        <v>736533.79026499996</v>
       </c>
       <c r="F49" s="107">
         <f t="shared" si="6"/>
-        <v>16214.980351</v>
+        <v>64830.359735000005</v>
       </c>
       <c r="G49" s="108">
         <f>E49+F49</f>
-        <v>200432.38999999998</v>
+        <v>801364.14999999991</v>
       </c>
       <c r="H49" s="146" t="str">
         <f>IF(D49=G49, "", "Error")</f>
         <v/>
       </c>
     </row>
-    <row r="50" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A50" s="7" t="s">
         <v>7</v>
       </c>
       <c r="B50" s="7"/>
       <c r="C50" s="7"/>
-      <c r="D50" s="175"/>
+      <c r="D50" s="173"/>
       <c r="E50" s="114"/>
       <c r="F50" s="7"/>
       <c r="H50" s="146"/>
     </row>
-    <row r="51" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A51" s="179" t="s">
-        <v>171</v>
-      </c>
-      <c r="B51" s="168"/>
-      <c r="C51" s="169"/>
-      <c r="D51" s="199">
+    <row r="51" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A51" s="177" t="s">
+        <v>155</v>
+      </c>
+      <c r="B51" s="166"/>
+      <c r="C51" s="167"/>
+      <c r="D51" s="191">
         <v>39000</v>
       </c>
       <c r="E51" s="145">
@@ -2753,20 +2732,20 @@
         <f>D51</f>
         <v>39000</v>
       </c>
-      <c r="H51" s="156">
+      <c r="H51" s="155">
         <f>E51+F51</f>
         <v>39000</v>
       </c>
-      <c r="I51" s="170"/>
-      <c r="J51" s="170"/>
-    </row>
-    <row r="52" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A52" s="179" t="s">
+      <c r="I51" s="168"/>
+      <c r="J51" s="168"/>
+    </row>
+    <row r="52" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A52" s="177" t="s">
         <v>138</v>
       </c>
-      <c r="B52" s="168"/>
-      <c r="C52" s="169"/>
-      <c r="D52" s="182">
+      <c r="B52" s="166"/>
+      <c r="C52" s="167"/>
+      <c r="D52" s="180">
         <v>372000</v>
       </c>
       <c r="E52" s="145">
@@ -2778,1232 +2757,1114 @@
         <f>D52</f>
         <v>372000</v>
       </c>
-      <c r="H52" s="156">
+      <c r="H52" s="155">
         <f>E52+F52</f>
         <v>372000</v>
       </c>
-      <c r="I52" s="170">
+      <c r="I52" s="168">
         <f>H52-D52</f>
         <v>0</v>
       </c>
-      <c r="J52" s="170"/>
-    </row>
-    <row r="53" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J52" s="168"/>
+    </row>
+    <row r="53" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="120" t="s">
         <v>8</v>
       </c>
-      <c r="B53" s="157"/>
+      <c r="B53" s="156"/>
       <c r="C53" s="7"/>
-      <c r="D53" s="112">
-        <v>153807</v>
-      </c>
+      <c r="D53" s="112"/>
       <c r="E53" s="145">
-        <f t="shared" ref="E53:E57" si="7">D53*91.91%</f>
-        <v>141364.01369999998</v>
+        <f t="shared" ref="E53:E58" si="7">D53*91.91%</f>
+        <v>0</v>
       </c>
       <c r="F53" s="133">
-        <f t="shared" ref="F53:F57" si="8">D53*8.09%</f>
-        <v>12442.9863</v>
+        <f t="shared" ref="F53:F58" si="8">D53*8.09%</f>
+        <v>0</v>
       </c>
       <c r="G53" s="108">
-        <f t="shared" ref="G53:G67" si="9">D53</f>
-        <v>153807</v>
-      </c>
-      <c r="H53" s="156">
-        <f t="shared" ref="H53:H67" si="10">E53+F53</f>
-        <v>153806.99999999997</v>
-      </c>
-      <c r="I53" s="170"/>
-      <c r="J53" s="170"/>
-    </row>
-    <row r="54" spans="1:16" x14ac:dyDescent="0.3">
+        <f t="shared" ref="G53:G63" si="9">D53</f>
+        <v>0</v>
+      </c>
+      <c r="H53" s="155">
+        <f t="shared" ref="H53:H63" si="10">E53+F53</f>
+        <v>0</v>
+      </c>
+      <c r="I53" s="168"/>
+      <c r="J53" s="168"/>
+    </row>
+    <row r="54" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A54" s="94" t="s">
         <v>168</v>
       </c>
       <c r="B54" s="7"/>
       <c r="C54" s="7"/>
-      <c r="D54" s="112">
-        <v>0</v>
+      <c r="D54" s="180">
+        <v>148200</v>
       </c>
       <c r="E54" s="145">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>136210.62</v>
       </c>
       <c r="F54" s="133">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>11989.38</v>
       </c>
       <c r="G54" s="108">
         <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="H54" s="156">
+        <v>148200</v>
+      </c>
+      <c r="H54" s="155">
         <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="I54" s="170">
-        <f t="shared" ref="I54:I64" si="11">H54-D54</f>
-        <v>0</v>
-      </c>
-      <c r="J54" s="170">
-        <f t="shared" ref="J54:J67" si="12">G54-D54</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="55" spans="1:16" x14ac:dyDescent="0.3">
+        <v>148200</v>
+      </c>
+      <c r="I54" s="168">
+        <f t="shared" ref="I54:I62" si="11">H54-D54</f>
+        <v>0</v>
+      </c>
+      <c r="J54" s="168">
+        <f t="shared" ref="J54:J62" si="12">G54-D54</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A55" s="94" t="s">
-        <v>9</v>
-      </c>
-      <c r="B55" s="7" t="s">
-        <v>159</v>
-      </c>
+        <v>169</v>
+      </c>
+      <c r="B55" s="7"/>
       <c r="C55" s="7"/>
-      <c r="D55" s="112">
-        <v>129320</v>
+      <c r="D55" s="180">
+        <v>812358.3</v>
       </c>
       <c r="E55" s="145">
-        <f>D55*91.91%</f>
-        <v>118858.01199999999</v>
+        <f t="shared" si="7"/>
+        <v>746638.51353</v>
       </c>
       <c r="F55" s="133">
         <f t="shared" si="8"/>
-        <v>10461.987999999999</v>
+        <v>65719.786470000006</v>
       </c>
       <c r="G55" s="108">
         <f t="shared" si="9"/>
+        <v>812358.3</v>
+      </c>
+      <c r="H55" s="155">
+        <f t="shared" si="10"/>
+        <v>812358.3</v>
+      </c>
+      <c r="I55" s="168"/>
+      <c r="J55" s="168"/>
+    </row>
+    <row r="56" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A56" s="94" t="s">
+        <v>9</v>
+      </c>
+      <c r="B56" s="7" t="s">
+        <v>160</v>
+      </c>
+      <c r="C56" s="7"/>
+      <c r="D56" s="180">
         <v>129320</v>
       </c>
-      <c r="H55" s="156">
-        <f>E55+F55</f>
+      <c r="E56" s="145">
+        <f>D56*91.91%</f>
+        <v>118858.01199999999</v>
+      </c>
+      <c r="F56" s="133">
+        <f t="shared" si="8"/>
+        <v>10461.987999999999</v>
+      </c>
+      <c r="G56" s="108">
+        <f t="shared" si="9"/>
+        <v>129320</v>
+      </c>
+      <c r="H56" s="155">
+        <f>E56+F56</f>
         <v>129319.99999999999</v>
       </c>
-      <c r="I55" s="170">
+      <c r="I56" s="168">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="J55" s="170">
+      <c r="J56" s="168">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A56" s="94" t="s">
+    <row r="57" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A57" s="94" t="s">
         <v>11</v>
       </c>
-      <c r="B56" s="98" t="s">
-        <v>160</v>
-      </c>
-      <c r="C56" s="7"/>
-      <c r="D56" s="112">
+      <c r="B57" s="98" t="s">
+        <v>161</v>
+      </c>
+      <c r="C57" s="7"/>
+      <c r="D57" s="180">
         <v>655067.86</v>
       </c>
-      <c r="E56" s="145">
+      <c r="E57" s="145">
         <f t="shared" si="7"/>
         <v>602072.87012599991</v>
       </c>
-      <c r="F56" s="133">
+      <c r="F57" s="133">
         <f t="shared" si="8"/>
         <v>52994.989873999999</v>
       </c>
-      <c r="G56" s="108">
+      <c r="G57" s="108">
         <f t="shared" si="9"/>
         <v>655067.86</v>
       </c>
-      <c r="H56" s="156">
+      <c r="H57" s="155">
         <f t="shared" si="10"/>
         <v>655067.85999999987</v>
       </c>
-      <c r="I56" s="170">
+      <c r="I57" s="168">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="J56" s="170">
+      <c r="J57" s="168">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A57" s="128" t="s">
+    <row r="58" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A58" s="128" t="s">
         <v>10</v>
       </c>
-      <c r="B57" s="98" t="s">
-        <v>163</v>
-      </c>
-      <c r="C57" s="98"/>
-      <c r="D57" s="112">
-        <f>2276949.43-1173289.52</f>
-        <v>1103659.9100000001</v>
-      </c>
-      <c r="E57" s="145">
+      <c r="B58" s="98" t="s">
+        <v>166</v>
+      </c>
+      <c r="C58" s="98"/>
+      <c r="D58" s="180">
+        <v>1107047.99</v>
+      </c>
+      <c r="E58" s="145">
         <f t="shared" si="7"/>
-        <v>1014373.823281</v>
-      </c>
-      <c r="F57" s="133">
+        <v>1017487.8076089999</v>
+      </c>
+      <c r="F58" s="133">
         <f t="shared" si="8"/>
-        <v>89286.086719000014</v>
-      </c>
-      <c r="G57" s="108">
-        <f t="shared" si="9"/>
-        <v>1103659.9100000001</v>
-      </c>
-      <c r="H57" s="156">
-        <f t="shared" si="10"/>
-        <v>1103659.9100000001</v>
-      </c>
-      <c r="I57" s="170">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="J57" s="170">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="58" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A58" s="219" t="s">
-        <v>164</v>
-      </c>
-      <c r="B58" s="220"/>
-      <c r="C58" s="221"/>
-      <c r="D58" s="112">
-        <v>50000</v>
-      </c>
-      <c r="E58" s="145">
-        <f t="shared" ref="E58:E61" si="13">D58</f>
-        <v>50000</v>
-      </c>
-      <c r="F58" s="133"/>
+        <v>89560.182390999995</v>
+      </c>
       <c r="G58" s="108">
         <f t="shared" si="9"/>
-        <v>50000</v>
-      </c>
-      <c r="H58" s="156">
+        <v>1107047.99</v>
+      </c>
+      <c r="H58" s="155">
         <f t="shared" si="10"/>
-        <v>50000</v>
-      </c>
-      <c r="I58" s="170">
+        <v>1107047.99</v>
+      </c>
+      <c r="I58" s="168">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="J58" s="170">
+      <c r="J58" s="168">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A59" s="214" t="s">
-        <v>157</v>
-      </c>
-      <c r="B59" s="215"/>
-      <c r="C59" s="216"/>
-      <c r="D59" s="112">
-        <v>159500</v>
+    <row r="59" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A59" s="211" t="s">
+        <v>167</v>
+      </c>
+      <c r="B59" s="212"/>
+      <c r="C59" s="213"/>
+      <c r="D59" s="180">
+        <v>51000</v>
       </c>
       <c r="E59" s="145">
-        <f t="shared" ref="E59:E60" si="14">D59*91.91%</f>
-        <v>146596.44999999998</v>
-      </c>
-      <c r="F59" s="133">
-        <f t="shared" ref="F59:F60" si="15">D59*8.09%</f>
-        <v>12903.55</v>
-      </c>
+        <f t="shared" ref="E59" si="13">D59</f>
+        <v>51000</v>
+      </c>
+      <c r="F59" s="133"/>
       <c r="G59" s="108">
         <f t="shared" si="9"/>
-        <v>159500</v>
-      </c>
-      <c r="H59" s="156">
+        <v>51000</v>
+      </c>
+      <c r="H59" s="155">
         <f t="shared" si="10"/>
-        <v>159499.99999999997</v>
-      </c>
-      <c r="I59" s="170"/>
-      <c r="J59" s="170"/>
-    </row>
-    <row r="60" spans="1:16" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A60" s="189" t="s">
-        <v>153</v>
-      </c>
-      <c r="B60" s="190"/>
-      <c r="C60" s="191"/>
-      <c r="D60" s="112">
-        <v>30000</v>
+        <v>51000</v>
+      </c>
+      <c r="I59" s="168">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="J59" s="168">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A60" s="186" t="s">
+        <v>165</v>
+      </c>
+      <c r="B60" s="98"/>
+      <c r="C60" s="98"/>
+      <c r="D60" s="180">
+        <v>400000</v>
       </c>
       <c r="E60" s="145">
-        <f t="shared" si="14"/>
-        <v>27572.999999999996</v>
+        <f t="shared" ref="E60:E63" si="14">D60*91.91%</f>
+        <v>367639.99999999994</v>
       </c>
       <c r="F60" s="133">
-        <f t="shared" si="15"/>
-        <v>2427</v>
+        <f t="shared" ref="F60:F63" si="15">D60*8.09%</f>
+        <v>32360</v>
       </c>
       <c r="G60" s="108">
         <f t="shared" si="9"/>
-        <v>30000</v>
-      </c>
-      <c r="H60" s="156">
+        <v>400000</v>
+      </c>
+      <c r="H60" s="155">
         <f t="shared" si="10"/>
-        <v>29999.999999999996</v>
-      </c>
-      <c r="I60" s="170"/>
-      <c r="J60" s="170"/>
-    </row>
-    <row r="61" spans="1:16" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A61" s="197" t="s">
+        <v>399999.99999999994</v>
+      </c>
+      <c r="I60" s="168">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="J60" s="168">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="M60" s="179" t="s">
+        <v>137</v>
+      </c>
+      <c r="N60" s="7"/>
+      <c r="O60" s="7"/>
+      <c r="P60" s="180">
+        <v>358487.12</v>
+      </c>
+    </row>
+    <row r="61" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A61" s="7" t="s">
         <v>154</v>
       </c>
-      <c r="B61" s="190"/>
-      <c r="C61" s="191"/>
-      <c r="D61" s="112">
-        <v>250000</v>
+      <c r="B61" s="98"/>
+      <c r="C61" s="98"/>
+      <c r="D61" s="180">
+        <v>47279.57</v>
       </c>
       <c r="E61" s="145">
-        <f t="shared" si="13"/>
-        <v>250000</v>
+        <f t="shared" ref="E61:E62" si="16">D61</f>
+        <v>47279.57</v>
       </c>
       <c r="F61" s="133"/>
       <c r="G61" s="108">
         <f t="shared" si="9"/>
-        <v>250000</v>
-      </c>
-      <c r="H61" s="156">
+        <v>47279.57</v>
+      </c>
+      <c r="H61" s="155">
         <f t="shared" si="10"/>
-        <v>250000</v>
-      </c>
-      <c r="I61" s="170"/>
-      <c r="J61" s="170"/>
-    </row>
-    <row r="62" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A62" s="188" t="s">
-        <v>165</v>
-      </c>
-      <c r="B62" s="98"/>
-      <c r="C62" s="98"/>
-      <c r="D62" s="112">
-        <v>280000</v>
+        <v>47279.57</v>
+      </c>
+      <c r="I61" s="168"/>
+      <c r="J61" s="168"/>
+    </row>
+    <row r="62" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A62" s="7" t="s">
+        <v>119</v>
+      </c>
+      <c r="B62" s="7"/>
+      <c r="C62" s="7"/>
+      <c r="D62" s="180">
+        <v>88294</v>
       </c>
       <c r="E62" s="145">
-        <f t="shared" ref="E62:E65" si="16">D62*91.91%</f>
-        <v>257347.99999999997</v>
-      </c>
-      <c r="F62" s="133">
-        <f t="shared" ref="F62:F66" si="17">D62*8.09%</f>
-        <v>22652</v>
-      </c>
+        <f t="shared" si="16"/>
+        <v>88294</v>
+      </c>
+      <c r="F62" s="133"/>
       <c r="G62" s="108">
         <f t="shared" si="9"/>
-        <v>280000</v>
-      </c>
-      <c r="H62" s="156">
+        <v>88294</v>
+      </c>
+      <c r="H62" s="155">
         <f t="shared" si="10"/>
-        <v>280000</v>
-      </c>
-      <c r="I62" s="170">
+        <v>88294</v>
+      </c>
+      <c r="I62" s="168">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="J62" s="170">
+      <c r="J62" s="168">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="M62" s="181" t="s">
-        <v>137</v>
-      </c>
-      <c r="N62" s="7"/>
-      <c r="O62" s="7"/>
-      <c r="P62" s="182">
-        <v>358487.12</v>
-      </c>
-    </row>
-    <row r="63" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A63" s="7" t="s">
-        <v>170</v>
-      </c>
-      <c r="B63" s="98"/>
-      <c r="C63" s="98"/>
-      <c r="D63" s="182">
-        <v>47279.57</v>
+    </row>
+    <row r="63" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A63" s="120" t="s">
+        <v>156</v>
+      </c>
+      <c r="B63" s="113"/>
+      <c r="C63" s="7"/>
+      <c r="D63" s="180">
+        <v>90143.44</v>
       </c>
       <c r="E63" s="145">
-        <f t="shared" ref="E63:E64" si="18">D63</f>
-        <v>47279.57</v>
-      </c>
-      <c r="F63" s="133"/>
+        <f t="shared" si="14"/>
+        <v>82850.835703999997</v>
+      </c>
+      <c r="F63" s="133">
+        <f t="shared" si="15"/>
+        <v>7292.6042960000004</v>
+      </c>
       <c r="G63" s="108">
         <f t="shared" si="9"/>
-        <v>47279.57</v>
-      </c>
-      <c r="H63" s="156">
-        <f t="shared" si="10"/>
-        <v>47279.57</v>
-      </c>
-      <c r="I63" s="170"/>
-      <c r="J63" s="170"/>
-    </row>
-    <row r="64" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A64" s="7" t="s">
-        <v>119</v>
-      </c>
-      <c r="B64" s="7"/>
-      <c r="C64" s="7"/>
-      <c r="D64" s="182">
-        <v>88294</v>
-      </c>
-      <c r="E64" s="145">
-        <f t="shared" si="18"/>
-        <v>88294</v>
-      </c>
-      <c r="F64" s="133"/>
-      <c r="G64" s="108">
-        <f t="shared" si="9"/>
-        <v>88294</v>
-      </c>
-      <c r="H64" s="156">
-        <f t="shared" si="10"/>
-        <v>88294</v>
-      </c>
-      <c r="I64" s="170">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="J64" s="170">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="65" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A65" s="120" t="s">
-        <v>174</v>
-      </c>
-      <c r="B65" s="113"/>
-      <c r="C65" s="7"/>
-      <c r="D65" s="182">
         <v>90143.44</v>
       </c>
-      <c r="E65" s="145">
-        <f t="shared" si="16"/>
-        <v>82850.835703999997</v>
-      </c>
-      <c r="F65" s="133">
-        <f t="shared" si="17"/>
-        <v>7292.6042960000004</v>
-      </c>
-      <c r="G65" s="108">
-        <f t="shared" si="9"/>
-        <v>90143.44</v>
-      </c>
-      <c r="H65" s="156">
+      <c r="H63" s="155">
         <f t="shared" si="10"/>
         <v>90143.44</v>
       </c>
-      <c r="I65" s="170"/>
-      <c r="J65" s="170"/>
-    </row>
-    <row r="66" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A66" s="120" t="s">
-        <v>166</v>
-      </c>
-      <c r="B66" s="113"/>
+      <c r="I63" s="168"/>
+      <c r="J63" s="168"/>
+    </row>
+    <row r="64" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A64" s="95" t="s">
+        <v>12</v>
+      </c>
+      <c r="B64" s="96"/>
+      <c r="C64" s="96"/>
+      <c r="D64" s="107">
+        <f>SUM(D51:D63)</f>
+        <v>3939711.16</v>
+      </c>
+      <c r="E64" s="107">
+        <f>SUM(E51:E63)</f>
+        <v>3669332.2289689998</v>
+      </c>
+      <c r="F64" s="107">
+        <f>SUM(F51:F63)</f>
+        <v>270378.93103099999</v>
+      </c>
+      <c r="G64" s="108">
+        <f>E64+F64</f>
+        <v>3939711.1599999997</v>
+      </c>
+      <c r="H64" s="146" t="str">
+        <f>IF(D64=G64, "", "Error")</f>
+        <v/>
+      </c>
+      <c r="I64" s="168">
+        <f>D64-G64</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A65" s="7"/>
+      <c r="B65" s="7"/>
+      <c r="C65" s="7"/>
+      <c r="D65" s="173"/>
+      <c r="E65" s="114"/>
+      <c r="F65" s="7"/>
+      <c r="H65" s="146"/>
+    </row>
+    <row r="66" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A66" s="7"/>
+      <c r="B66" s="7"/>
       <c r="C66" s="7"/>
-      <c r="D66" s="112">
-        <v>40000</v>
-      </c>
-      <c r="E66" s="145">
-        <f>D66*91.91%</f>
-        <v>36764</v>
-      </c>
-      <c r="F66" s="133">
-        <f t="shared" si="17"/>
-        <v>3236</v>
-      </c>
-      <c r="G66" s="108">
-        <f t="shared" si="9"/>
-        <v>40000</v>
-      </c>
-      <c r="H66" s="156">
-        <f t="shared" si="10"/>
-        <v>40000</v>
-      </c>
-      <c r="I66" s="170"/>
-      <c r="J66" s="170"/>
-    </row>
-    <row r="67" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A67" s="198" t="s">
-        <v>155</v>
-      </c>
-      <c r="B67" s="151"/>
-      <c r="C67" s="151"/>
-      <c r="D67" s="196">
-        <v>95800</v>
-      </c>
-      <c r="E67" s="145">
-        <f t="shared" ref="E67" si="19">D67</f>
-        <v>95800</v>
-      </c>
-      <c r="F67" s="133"/>
-      <c r="G67" s="108">
-        <f t="shared" si="9"/>
-        <v>95800</v>
-      </c>
-      <c r="H67" s="156">
-        <f t="shared" si="10"/>
-        <v>95800</v>
-      </c>
-      <c r="I67" t="str">
-        <f>IF(G67=H67, "", "Error")</f>
-        <v/>
-      </c>
-      <c r="J67" s="170">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="68" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A68" s="95" t="s">
-        <v>12</v>
-      </c>
-      <c r="B68" s="96"/>
-      <c r="C68" s="96"/>
-      <c r="D68" s="107">
-        <f>SUM(D51:D67)</f>
-        <v>3583871.78</v>
-      </c>
-      <c r="E68" s="107">
-        <f>SUM(E51:E67)</f>
-        <v>3370174.5748109999</v>
-      </c>
-      <c r="F68" s="107">
-        <f>SUM(F51:F67)</f>
-        <v>213697.205189</v>
-      </c>
-      <c r="G68" s="108">
-        <f>E68+F68</f>
-        <v>3583871.78</v>
-      </c>
-      <c r="H68" s="146" t="str">
-        <f>IF(D68=G68, "", "Error")</f>
-        <v/>
-      </c>
-      <c r="I68" s="170">
-        <f>D68-G68</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="69" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+      <c r="D66" s="173"/>
+      <c r="E66" s="113"/>
+      <c r="F66" s="7"/>
+      <c r="H66" s="146"/>
+    </row>
+    <row r="67" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A67" s="7"/>
+      <c r="B67" s="7"/>
+      <c r="C67" s="7"/>
+      <c r="D67" s="173"/>
+      <c r="E67" s="113"/>
+      <c r="F67" s="7"/>
+      <c r="H67" s="146"/>
+    </row>
+    <row r="68" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A68" s="94" t="s">
+        <v>141</v>
+      </c>
+      <c r="B68" s="98"/>
+      <c r="C68" s="7"/>
+      <c r="D68" s="180">
+        <v>112680</v>
+      </c>
+      <c r="E68" s="145">
+        <f>D68*91.91%</f>
+        <v>103564.18799999999</v>
+      </c>
+      <c r="F68" s="133">
+        <f>D68*8.09%</f>
+        <v>9115.8119999999999</v>
+      </c>
+      <c r="G68" s="154"/>
+      <c r="H68" s="146"/>
+    </row>
+    <row r="69" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A69" s="7"/>
       <c r="B69" s="7"/>
       <c r="C69" s="7"/>
-      <c r="D69" s="175"/>
-      <c r="E69" s="114"/>
+      <c r="D69" s="112"/>
+      <c r="E69" s="157">
+        <f>D69</f>
+        <v>0</v>
+      </c>
       <c r="F69" s="7"/>
       <c r="H69" s="146"/>
-    </row>
-    <row r="70" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A70" s="7"/>
-      <c r="B70" s="7"/>
-      <c r="C70" s="7"/>
-      <c r="D70" s="175"/>
-      <c r="E70" s="113"/>
-      <c r="F70" s="7"/>
-      <c r="H70" s="146"/>
-    </row>
-    <row r="71" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+      <c r="I69" s="108"/>
+    </row>
+    <row r="70" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A70" s="95" t="s">
+        <v>16</v>
+      </c>
+      <c r="B70" s="95"/>
+      <c r="C70" s="95"/>
+      <c r="D70" s="107">
+        <f>SUM(D68:D69)</f>
+        <v>112680</v>
+      </c>
+      <c r="E70" s="107">
+        <f>SUM(E68:E69)</f>
+        <v>103564.18799999999</v>
+      </c>
+      <c r="F70" s="107">
+        <f>SUM(F68:F69)</f>
+        <v>9115.8119999999999</v>
+      </c>
+      <c r="G70" s="108">
+        <f>E70+F70</f>
+        <v>112680</v>
+      </c>
+      <c r="H70" s="146" t="str">
+        <f>IF(D70=G70, "", "Error")</f>
+        <v/>
+      </c>
+      <c r="J70" s="108"/>
+    </row>
+    <row r="71" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A71" s="7"/>
       <c r="B71" s="7"/>
       <c r="C71" s="7"/>
-      <c r="D71" s="175"/>
-      <c r="E71" s="113"/>
+      <c r="D71" s="173"/>
+      <c r="E71" s="114"/>
       <c r="F71" s="7"/>
       <c r="H71" s="146"/>
     </row>
-    <row r="72" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A72" s="94" t="s">
-        <v>141</v>
-      </c>
-      <c r="B72" s="98"/>
+    <row r="72" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A72" s="7"/>
+      <c r="B72" s="7"/>
       <c r="C72" s="7"/>
-      <c r="D72" s="182">
-        <v>112680</v>
-      </c>
-      <c r="E72" s="145">
-        <f>D72*91.91%</f>
-        <v>103564.18799999999</v>
-      </c>
-      <c r="F72" s="133">
-        <f>D72*8.09%</f>
-        <v>9115.8119999999999</v>
-      </c>
-      <c r="G72" s="155"/>
+      <c r="D72" s="173"/>
+      <c r="E72" s="113"/>
+      <c r="F72" s="7"/>
       <c r="H72" s="146"/>
     </row>
-    <row r="73" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A73" s="7"/>
+    <row r="73" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A73" s="94" t="s">
+        <v>13</v>
+      </c>
       <c r="B73" s="7"/>
       <c r="C73" s="7"/>
-      <c r="D73" s="112"/>
-      <c r="E73" s="158">
-        <f>D73</f>
-        <v>0</v>
-      </c>
+      <c r="D73" s="173"/>
+      <c r="E73" s="113"/>
       <c r="F73" s="7"/>
       <c r="H73" s="146"/>
-      <c r="I73" s="108"/>
-    </row>
-    <row r="74" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A74" s="95" t="s">
-        <v>16</v>
-      </c>
-      <c r="B74" s="95"/>
-      <c r="C74" s="95"/>
-      <c r="D74" s="107">
-        <f>SUM(D72:D73)</f>
-        <v>112680</v>
-      </c>
-      <c r="E74" s="107">
-        <f>SUM(E72:E73)</f>
-        <v>103564.18799999999</v>
-      </c>
-      <c r="F74" s="107">
-        <f>SUM(F72:F73)</f>
-        <v>9115.8119999999999</v>
-      </c>
-      <c r="G74" s="108">
-        <f>E74+F74</f>
-        <v>112680</v>
-      </c>
-      <c r="H74" s="146" t="str">
-        <f>IF(D74=G74, "", "Error")</f>
-        <v/>
-      </c>
-      <c r="J74" s="108"/>
-    </row>
-    <row r="75" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A75" s="7"/>
+    </row>
+    <row r="74" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A74" s="94" t="s">
+        <v>14</v>
+      </c>
+      <c r="B74" s="7" t="s">
+        <v>116</v>
+      </c>
+      <c r="C74" s="7"/>
+      <c r="D74" s="180">
+        <v>246000</v>
+      </c>
+      <c r="E74" s="145">
+        <f>D74*91.91%</f>
+        <v>226098.59999999998</v>
+      </c>
+      <c r="F74" s="133">
+        <f>D74*8.09%</f>
+        <v>19901.400000000001</v>
+      </c>
+      <c r="G74" t="s">
+        <v>139</v>
+      </c>
+      <c r="H74" s="146"/>
+    </row>
+    <row r="75" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A75" s="94" t="s">
+        <v>107</v>
+      </c>
       <c r="B75" s="7"/>
       <c r="C75" s="7"/>
-      <c r="D75" s="175"/>
-      <c r="E75" s="114"/>
-      <c r="F75" s="7"/>
+      <c r="D75" s="180">
+        <v>35000</v>
+      </c>
+      <c r="E75" s="145">
+        <f>D75*91.91%</f>
+        <v>32168.499999999996</v>
+      </c>
+      <c r="F75" s="133">
+        <f>D75*8.09%</f>
+        <v>2831.5</v>
+      </c>
       <c r="H75" s="146"/>
-    </row>
-    <row r="76" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+      <c r="J75" s="112"/>
+    </row>
+    <row r="76" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A76" s="7"/>
       <c r="B76" s="7"/>
       <c r="C76" s="7"/>
-      <c r="D76" s="175"/>
-      <c r="E76" s="113"/>
+      <c r="D76" s="173"/>
+      <c r="E76" s="115"/>
       <c r="F76" s="7"/>
       <c r="H76" s="146"/>
-    </row>
-    <row r="77" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A77" s="94" t="s">
-        <v>13</v>
-      </c>
-      <c r="B77" s="7"/>
-      <c r="C77" s="7"/>
-      <c r="D77" s="175"/>
-      <c r="E77" s="113"/>
-      <c r="F77" s="7"/>
-      <c r="H77" s="146"/>
-    </row>
-    <row r="78" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J76" s="108"/>
+    </row>
+    <row r="77" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A77" s="95" t="s">
+        <v>100</v>
+      </c>
+      <c r="B77" s="95"/>
+      <c r="C77" s="95"/>
+      <c r="D77" s="107">
+        <f>SUM(D74:D76)</f>
+        <v>281000</v>
+      </c>
+      <c r="E77" s="107">
+        <f>SUM(E74:E76)</f>
+        <v>258267.09999999998</v>
+      </c>
+      <c r="F77" s="107">
+        <f>SUM(F74:F76)</f>
+        <v>22732.9</v>
+      </c>
+      <c r="G77" s="108">
+        <f>E77+F77</f>
+        <v>281000</v>
+      </c>
+      <c r="H77" s="146" t="str">
+        <f>IF(D77=G77, "", "Error")</f>
+        <v/>
+      </c>
+      <c r="J77" s="108"/>
+    </row>
+    <row r="78" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" s="94" t="s">
-        <v>14</v>
-      </c>
-      <c r="B78" s="7" t="s">
-        <v>116</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="B78" s="7"/>
       <c r="C78" s="7"/>
-      <c r="D78" s="112">
-        <v>246000</v>
-      </c>
-      <c r="E78" s="145">
-        <f>D78*91.91%</f>
-        <v>226098.59999999998</v>
-      </c>
-      <c r="F78" s="133">
-        <f>D78*8.09%</f>
-        <v>19901.400000000001</v>
-      </c>
-      <c r="G78" t="s">
-        <v>139</v>
-      </c>
+      <c r="D78" s="112"/>
+      <c r="E78" s="116"/>
+      <c r="F78" s="7"/>
       <c r="H78" s="146"/>
     </row>
-    <row r="79" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A79" s="94" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="B79" s="7"/>
       <c r="C79" s="7"/>
-      <c r="D79" s="112">
-        <v>30000</v>
+      <c r="D79" s="243">
+        <v>230178.74</v>
       </c>
       <c r="E79" s="145">
         <f>D79*91.91%</f>
-        <v>27572.999999999996</v>
+        <v>211557.27993399996</v>
       </c>
       <c r="F79" s="133">
         <f>D79*8.09%</f>
-        <v>2427</v>
+        <v>18621.460066</v>
       </c>
       <c r="H79" s="146"/>
-      <c r="J79" s="112"/>
-    </row>
-    <row r="80" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A80" s="7"/>
+    </row>
+    <row r="80" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A80" s="94" t="s">
+        <v>102</v>
+      </c>
       <c r="B80" s="7"/>
-      <c r="C80" s="7"/>
-      <c r="D80" s="175"/>
-      <c r="E80" s="115"/>
-      <c r="F80" s="7"/>
+      <c r="C80" s="121"/>
+      <c r="D80" s="243">
+        <v>44400</v>
+      </c>
+      <c r="E80" s="145">
+        <f>D80*91.91%</f>
+        <v>40808.039999999994</v>
+      </c>
+      <c r="F80" s="133">
+        <f>D80*8.09%</f>
+        <v>3591.96</v>
+      </c>
       <c r="H80" s="146"/>
-      <c r="J80" s="108"/>
-    </row>
-    <row r="81" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="81" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A81" s="95" t="s">
-        <v>100</v>
+        <v>15</v>
       </c>
       <c r="B81" s="95"/>
       <c r="C81" s="95"/>
-      <c r="D81" s="107">
-        <f>SUM(D78:D80)</f>
-        <v>276000</v>
-      </c>
-      <c r="E81" s="107">
-        <f>SUM(E78:E80)</f>
-        <v>253671.59999999998</v>
-      </c>
-      <c r="F81" s="107">
-        <f>SUM(F78:F80)</f>
-        <v>22328.400000000001</v>
+      <c r="D81" s="152">
+        <f>SUM(D79:D80)</f>
+        <v>274578.74</v>
+      </c>
+      <c r="E81" s="143">
+        <f t="shared" ref="E81:F81" si="17">SUM(E79:E80)</f>
+        <v>252365.31993399997</v>
+      </c>
+      <c r="F81" s="143">
+        <f t="shared" si="17"/>
+        <v>22213.420065999999</v>
       </c>
       <c r="G81" s="108">
         <f>E81+F81</f>
-        <v>276000</v>
+        <v>274578.74</v>
       </c>
       <c r="H81" s="146" t="str">
         <f>IF(D81=G81, "", "Error")</f>
         <v/>
       </c>
-      <c r="J81" s="108"/>
-    </row>
-    <row r="82" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A82" s="94" t="s">
-        <v>100</v>
-      </c>
+    </row>
+    <row r="82" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A82" s="7"/>
       <c r="B82" s="7"/>
       <c r="C82" s="7"/>
-      <c r="D82" s="112"/>
-      <c r="E82" s="116"/>
+      <c r="D82" s="174"/>
+      <c r="E82" s="12"/>
       <c r="F82" s="7"/>
       <c r="H82" s="146"/>
     </row>
-    <row r="83" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A83" s="94" t="s">
-        <v>101</v>
-      </c>
-      <c r="B83" s="7"/>
-      <c r="C83" s="7"/>
-      <c r="D83" s="112">
-        <v>230178.74</v>
-      </c>
-      <c r="E83" s="145">
+    <row r="83" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A83" s="99" t="s">
+        <v>133</v>
+      </c>
+      <c r="B83" s="99"/>
+      <c r="C83" s="99"/>
+      <c r="D83" s="175">
+        <f>7000000-5970688.01</f>
+        <v>1029311.9900000002</v>
+      </c>
+      <c r="E83" s="117">
         <f>D83*91.91%</f>
-        <v>211557.27993399996</v>
-      </c>
-      <c r="F83" s="133">
+        <v>946040.65000900009</v>
+      </c>
+      <c r="F83" s="135">
         <f>D83*8.09%</f>
-        <v>18621.460066</v>
-      </c>
-      <c r="H83" s="146"/>
-    </row>
-    <row r="84" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A84" s="94" t="s">
-        <v>102</v>
-      </c>
-      <c r="B84" s="7"/>
-      <c r="C84" s="121"/>
-      <c r="D84" s="112">
-        <v>44400</v>
-      </c>
-      <c r="E84" s="145">
-        <f>D84*91.91%</f>
-        <v>40808.039999999994</v>
-      </c>
-      <c r="F84" s="133">
-        <f>D84*8.09%</f>
-        <v>3591.96</v>
-      </c>
+        <v>83271.339991000015</v>
+      </c>
+      <c r="G83" s="108">
+        <f>E83+F83</f>
+        <v>1029311.9900000001</v>
+      </c>
+      <c r="H83" s="146" t="str">
+        <f>IF(D83=G83, "", "Error")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="84" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A84" s="1"/>
+      <c r="D84" s="172"/>
+      <c r="E84" s="2"/>
+      <c r="F84" s="10"/>
+      <c r="G84" s="151"/>
       <c r="H84" s="146"/>
     </row>
-    <row r="85" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A85" s="95" t="s">
-        <v>15</v>
-      </c>
-      <c r="B85" s="95"/>
-      <c r="C85" s="95"/>
-      <c r="D85" s="153">
-        <f>SUM(D83:D84)</f>
-        <v>274578.74</v>
-      </c>
-      <c r="E85" s="143">
-        <f t="shared" ref="E85:F85" si="20">SUM(E83:E84)</f>
-        <v>252365.31993399997</v>
-      </c>
-      <c r="F85" s="143">
-        <f t="shared" si="20"/>
-        <v>22213.420065999999</v>
+    <row r="85" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A85" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="B85" s="60"/>
+      <c r="C85" s="5"/>
+      <c r="D85" s="176">
+        <f>SUM(D83+D81+D77+D70+D64+D49+D32+D27+D44)</f>
+        <v>7515676.040000001</v>
+      </c>
+      <c r="E85" s="144">
+        <f>SUM(E83+E81+E77+E70+E64+E49+E32+E27+E44)</f>
+        <v>6956001.5501770005</v>
+      </c>
+      <c r="F85" s="144">
+        <f>SUM(F83+F81+F77+F70+F64+F49+F32+F27+F44)</f>
+        <v>559674.48982300004</v>
       </c>
       <c r="G85" s="108">
         <f>E85+F85</f>
-        <v>274578.74</v>
+        <v>7515676.040000001</v>
       </c>
       <c r="H85" s="146" t="str">
         <f>IF(D85=G85, "", "Error")</f>
         <v/>
       </c>
-    </row>
-    <row r="86" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A86" s="7"/>
-      <c r="B86" s="7"/>
-      <c r="C86" s="7"/>
-      <c r="D86" s="176"/>
-      <c r="E86" s="12"/>
-      <c r="F86" s="7"/>
-      <c r="H86" s="146"/>
-    </row>
-    <row r="87" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A87" s="99" t="s">
-        <v>133</v>
-      </c>
-      <c r="B87" s="99"/>
-      <c r="C87" s="99"/>
-      <c r="D87" s="177">
-        <f>7000000-5970688.01</f>
-        <v>1029311.9900000002</v>
-      </c>
-      <c r="E87" s="117">
-        <f>D87*91.91%</f>
-        <v>946040.65000900009</v>
-      </c>
-      <c r="F87" s="135">
-        <f>D87*8.09%</f>
-        <v>83271.339991000015</v>
-      </c>
-      <c r="G87" s="108">
-        <f>E87+F87</f>
-        <v>1029311.9900000001</v>
-      </c>
-      <c r="H87" s="146" t="str">
-        <f>IF(D87=G87, "", "Error")</f>
+      <c r="I85" s="168">
+        <f>D85-G85</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="D86" s="172"/>
+      <c r="E86" s="108"/>
+    </row>
+    <row r="87" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A87" s="182" t="s">
+        <v>152</v>
+      </c>
+      <c r="B87" s="140"/>
+      <c r="C87" s="140"/>
+      <c r="E87" s="108"/>
+    </row>
+    <row r="88" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A88" s="1"/>
+      <c r="C88" s="138"/>
+      <c r="E88" s="108"/>
+    </row>
+    <row r="89" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A89" s="1"/>
+      <c r="C89" s="138"/>
+      <c r="E89" s="108"/>
+    </row>
+    <row r="90" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A90" s="141" t="s">
+        <v>29</v>
+      </c>
+      <c r="B90" s="142"/>
+      <c r="C90" s="139">
+        <f>SUM(C88:C89)</f>
+        <v>0</v>
+      </c>
+      <c r="E90" s="108"/>
+    </row>
+    <row r="91" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="E91" s="108"/>
+    </row>
+    <row r="92" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="E92" s="136"/>
+    </row>
+    <row r="93" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A93" s="209" t="s">
+        <v>113</v>
+      </c>
+      <c r="B93" s="210"/>
+      <c r="C93" s="210"/>
+      <c r="D93" s="210"/>
+      <c r="E93" s="163" t="s">
+        <v>21</v>
+      </c>
+      <c r="F93" s="164" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="94" spans="1:9" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A94" s="206" t="s">
+        <v>170</v>
+      </c>
+      <c r="B94" s="207"/>
+      <c r="C94" s="208"/>
+      <c r="D94" s="180">
+        <v>2900000</v>
+      </c>
+      <c r="E94" s="145">
+        <f t="shared" ref="E94:E95" si="18">D94*91.91%</f>
+        <v>2665389.9999999995</v>
+      </c>
+      <c r="F94" s="133">
+        <f t="shared" ref="F94:F95" si="19">D94*8.09%</f>
+        <v>234610</v>
+      </c>
+    </row>
+    <row r="95" spans="1:9" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A95" s="214"/>
+      <c r="B95" s="215"/>
+      <c r="C95" s="216"/>
+      <c r="D95" s="112"/>
+      <c r="E95" s="145">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="F95" s="133">
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A96" s="203" t="s">
+        <v>29</v>
+      </c>
+      <c r="B96" s="204"/>
+      <c r="C96" s="205"/>
+      <c r="D96" s="162">
+        <f>SUM(D94:D95)</f>
+        <v>2900000</v>
+      </c>
+      <c r="E96" s="162">
+        <f>SUM(E94:E95)</f>
+        <v>2665389.9999999995</v>
+      </c>
+      <c r="F96" s="162">
+        <f>SUM(F94:F95)</f>
+        <v>234610</v>
+      </c>
+      <c r="H96" s="108">
+        <f>E96+F96</f>
+        <v>2899999.9999999995</v>
+      </c>
+      <c r="I96" s="146" t="str">
+        <f>IF(D96=H96, "", "Error")</f>
         <v/>
       </c>
     </row>
-    <row r="88" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A88" s="1"/>
-      <c r="D88" s="174"/>
-      <c r="E88" s="2"/>
-      <c r="F88" s="10"/>
-      <c r="G88" s="152"/>
-      <c r="H88" s="146"/>
-    </row>
-    <row r="89" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A89" s="4" t="s">
-        <v>103</v>
-      </c>
-      <c r="B89" s="60"/>
-      <c r="C89" s="5"/>
-      <c r="D89" s="178">
-        <f>SUM(D87+D85+D81+D74+D68+D49+D32+D27+D44)</f>
-        <v>6538226.8999999994</v>
-      </c>
-      <c r="E89" s="144">
-        <f>SUM(E87+E85+E81+E74+E68+E49+E32+E27+E44)</f>
-        <v>6085522.3656029999</v>
-      </c>
-      <c r="F89" s="144">
-        <f>SUM(F87+F85+F81+F74+F68+F49+F32+F27+F44)</f>
-        <v>452704.53439699998</v>
-      </c>
-      <c r="G89" s="108">
-        <f>E89+F89</f>
-        <v>6538226.9000000004</v>
-      </c>
-      <c r="H89" s="146" t="str">
-        <f>IF(D89=G89, "", "Error")</f>
-        <v/>
-      </c>
-      <c r="I89" s="170">
-        <f>D89-G89</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="90" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="D90" s="174"/>
-      <c r="E90" s="108"/>
-    </row>
-    <row r="91" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A91" s="184" t="s">
-        <v>152</v>
-      </c>
-      <c r="B91" s="140"/>
-      <c r="C91" s="140"/>
-      <c r="E91" s="108"/>
-    </row>
-    <row r="92" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A92" s="1"/>
-      <c r="C92" s="138"/>
-      <c r="E92" s="108"/>
-    </row>
-    <row r="93" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A93" s="1"/>
-      <c r="C93" s="138"/>
-      <c r="E93" s="108"/>
-    </row>
-    <row r="94" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A94" s="141" t="s">
+    <row r="98" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E98" s="108"/>
+    </row>
+    <row r="99" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A99" s="102" t="s">
+        <v>104</v>
+      </c>
+      <c r="B99" s="103">
+        <f>D85</f>
+        <v>7515676.040000001</v>
+      </c>
+    </row>
+    <row r="100" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A100" s="104" t="s">
+        <v>106</v>
+      </c>
+      <c r="B100" s="105">
+        <f>D85-D83</f>
+        <v>6486364.0500000007</v>
+      </c>
+    </row>
+    <row r="101" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="D101" s="193"/>
+      <c r="E101" s="193"/>
+    </row>
+    <row r="102" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A102" s="74" t="s">
+        <v>90</v>
+      </c>
+      <c r="B102" s="75"/>
+      <c r="C102" s="76"/>
+      <c r="D102" s="193"/>
+      <c r="E102" s="193"/>
+    </row>
+    <row r="103" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A103" s="77" t="s">
+        <v>91</v>
+      </c>
+      <c r="B103" s="11">
+        <v>3617497.2979896166</v>
+      </c>
+      <c r="C103" s="78"/>
+      <c r="D103" s="193"/>
+      <c r="E103" s="193"/>
+    </row>
+    <row r="104" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A104" s="79" t="s">
+        <v>92</v>
+      </c>
+      <c r="B104" s="92">
+        <f>PRORRATEO!G52</f>
+        <v>6941937.3369510006</v>
+      </c>
+      <c r="C104" s="78" t="s">
+        <v>93</v>
+      </c>
+      <c r="D104" s="193"/>
+      <c r="E104" s="193"/>
+    </row>
+    <row r="105" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A105" s="79" t="s">
+        <v>115</v>
+      </c>
+      <c r="B105" s="165">
+        <f>-B100</f>
+        <v>-6486364.0500000007</v>
+      </c>
+      <c r="C105" s="76"/>
+      <c r="D105" s="193"/>
+      <c r="E105" s="193"/>
+      <c r="G105" s="112"/>
+    </row>
+    <row r="106" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A106" s="79" t="s">
+        <v>114</v>
+      </c>
+      <c r="B106" s="165">
+        <f>-D96</f>
+        <v>-2900000</v>
+      </c>
+      <c r="C106" s="76"/>
+      <c r="D106" s="193"/>
+      <c r="E106" s="193"/>
+      <c r="G106" s="124"/>
+    </row>
+    <row r="107" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A107" s="79" t="s">
+        <v>171</v>
+      </c>
+      <c r="B107" s="165">
+        <f>-77229-250000</f>
+        <v>-327229</v>
+      </c>
+      <c r="C107" s="76"/>
+      <c r="D107" s="189"/>
+      <c r="E107" s="189"/>
+      <c r="G107" s="124"/>
+    </row>
+    <row r="108" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A108" s="79" t="s">
+        <v>172</v>
+      </c>
+      <c r="B108" s="165">
+        <f>-19000*2</f>
+        <v>-38000</v>
+      </c>
+      <c r="C108" s="76"/>
+      <c r="D108" s="189"/>
+      <c r="E108" s="189"/>
+      <c r="G108" s="124"/>
+    </row>
+    <row r="109" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A109" s="79" t="s">
+        <v>105</v>
+      </c>
+      <c r="B109" s="165">
+        <f>-B116</f>
+        <v>-60000</v>
+      </c>
+      <c r="C109" s="80"/>
+    </row>
+    <row r="110" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A110" s="79" t="s">
+        <v>120</v>
+      </c>
+      <c r="B110" s="93">
+        <f>-C90</f>
+        <v>0</v>
+      </c>
+      <c r="C110" s="80"/>
+    </row>
+    <row r="111" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A111" s="79"/>
+      <c r="B111" s="75"/>
+      <c r="C111" s="150"/>
+    </row>
+    <row r="112" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A112" s="77" t="s">
+        <v>94</v>
+      </c>
+      <c r="B112" s="81">
+        <f>SUM(B103:B111)</f>
+        <v>747841.58494061604</v>
+      </c>
+      <c r="C112" s="150"/>
+    </row>
+    <row r="113" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A113" s="80"/>
+      <c r="C113" s="76"/>
+      <c r="D113" s="83"/>
+    </row>
+    <row r="114" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="C114" s="76"/>
+      <c r="D114" s="108"/>
+      <c r="E114" s="168"/>
+    </row>
+    <row r="115" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A115" s="74" t="s">
+        <v>95</v>
+      </c>
+      <c r="B115" s="244">
+        <v>-272694.54000000004</v>
+      </c>
+      <c r="C115" s="82"/>
+      <c r="D115" s="168"/>
+      <c r="E115" s="168"/>
+      <c r="F115" s="168"/>
+    </row>
+    <row r="116" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A116" s="77" t="s">
+        <v>159</v>
+      </c>
+      <c r="B116" s="93">
+        <v>60000</v>
+      </c>
+      <c r="C116" s="82"/>
+      <c r="D116" s="168"/>
+      <c r="E116" s="178"/>
+    </row>
+    <row r="117" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A117" s="77"/>
+      <c r="B117" s="165"/>
+      <c r="C117" s="82"/>
+      <c r="E117" s="108"/>
+    </row>
+    <row r="118" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A118" s="77"/>
+      <c r="B118" s="165"/>
+      <c r="C118" s="82"/>
+      <c r="E118" s="108"/>
+    </row>
+    <row r="119" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A119" s="100" t="s">
         <v>29</v>
       </c>
-      <c r="B94" s="142"/>
-      <c r="C94" s="139">
-        <f>SUM(C92:C93)</f>
-        <v>0</v>
-      </c>
-      <c r="E94" s="108"/>
-    </row>
-    <row r="95" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="E95" s="108"/>
-    </row>
-    <row r="96" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="E96" s="136"/>
-    </row>
-    <row r="97" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A97" s="217" t="s">
-        <v>113</v>
-      </c>
-      <c r="B97" s="218"/>
-      <c r="C97" s="218"/>
-      <c r="D97" s="218"/>
-      <c r="E97" s="164" t="s">
-        <v>21</v>
-      </c>
-      <c r="F97" s="165" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="98" spans="1:9" ht="36" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A98" s="214" t="s">
-        <v>156</v>
-      </c>
-      <c r="B98" s="215"/>
-      <c r="C98" s="216"/>
-      <c r="D98" s="112">
-        <v>317050.40000000002</v>
-      </c>
-      <c r="E98" s="145">
-        <f t="shared" ref="E98:E99" si="21">D98*91.91%</f>
-        <v>291401.02263999998</v>
-      </c>
-      <c r="F98" s="133">
-        <f t="shared" ref="F98:F99" si="22">D98*8.09%</f>
-        <v>25649.377360000002</v>
-      </c>
-    </row>
-    <row r="99" spans="1:9" ht="36" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A99" s="222" t="s">
-        <v>167</v>
-      </c>
-      <c r="B99" s="223"/>
-      <c r="C99" s="224"/>
-      <c r="D99" s="112">
-        <v>110000</v>
-      </c>
-      <c r="E99" s="145">
-        <f t="shared" si="21"/>
-        <v>101100.99999999999</v>
-      </c>
-      <c r="F99" s="133">
-        <f t="shared" si="22"/>
-        <v>8899</v>
-      </c>
-    </row>
-    <row r="100" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A100" s="211" t="s">
-        <v>29</v>
-      </c>
-      <c r="B100" s="212"/>
-      <c r="C100" s="213"/>
-      <c r="D100" s="163">
-        <f>SUM(D98:D99)</f>
-        <v>427050.4</v>
-      </c>
-      <c r="E100" s="163">
-        <f>SUM(E98:E99)</f>
-        <v>392502.02263999998</v>
-      </c>
-      <c r="F100" s="163">
-        <f>SUM(F98:F99)</f>
-        <v>34548.377359999999</v>
-      </c>
-      <c r="H100" s="108">
-        <f>E100+F100</f>
-        <v>427050.39999999997</v>
-      </c>
-      <c r="I100" s="146" t="str">
-        <f>IF(D100=H100, "", "Error")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="102" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="E102" s="108"/>
-    </row>
-    <row r="103" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A103" s="102" t="s">
-        <v>104</v>
-      </c>
-      <c r="B103" s="103">
-        <f>D89</f>
-        <v>6538226.8999999994</v>
-      </c>
-    </row>
-    <row r="104" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A104" s="104" t="s">
-        <v>106</v>
-      </c>
-      <c r="B104" s="105">
-        <f>D89-D87</f>
-        <v>5508914.9099999992</v>
-      </c>
-    </row>
-    <row r="105" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="D105" s="201"/>
-      <c r="E105" s="201"/>
-    </row>
-    <row r="106" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A106" s="74" t="s">
-        <v>90</v>
-      </c>
-      <c r="B106" s="75"/>
-      <c r="C106" s="76"/>
-      <c r="D106" s="201"/>
-      <c r="E106" s="201"/>
-    </row>
-    <row r="107" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A107" s="77" t="s">
-        <v>91</v>
-      </c>
-      <c r="B107" s="11">
-        <v>-3514251.2083843551</v>
-      </c>
-      <c r="C107" s="78"/>
-      <c r="D107" s="201"/>
-      <c r="E107" s="201"/>
-    </row>
-    <row r="108" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A108" s="79" t="s">
-        <v>92</v>
-      </c>
-      <c r="B108" s="92">
-        <f>PRORRATEO!G52</f>
-        <v>13569486.916373972</v>
-      </c>
-      <c r="C108" s="78" t="s">
-        <v>93</v>
-      </c>
-      <c r="D108" s="201"/>
-      <c r="E108" s="201"/>
-    </row>
-    <row r="109" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A109" s="79" t="s">
-        <v>115</v>
-      </c>
-      <c r="B109" s="167">
-        <f>-B104</f>
-        <v>-5508914.9099999992</v>
-      </c>
-      <c r="C109" s="76"/>
-      <c r="D109" s="201"/>
-      <c r="E109" s="201"/>
-      <c r="G109" s="112"/>
-    </row>
-    <row r="110" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A110" s="79" t="s">
-        <v>114</v>
-      </c>
-      <c r="B110" s="167">
-        <f>-D100</f>
-        <v>-427050.4</v>
-      </c>
-      <c r="C110" s="76"/>
-      <c r="D110" s="201"/>
-      <c r="E110" s="201"/>
-      <c r="G110" s="124"/>
-    </row>
-    <row r="111" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A111" s="79" t="s">
-        <v>172</v>
-      </c>
-      <c r="B111" s="167">
-        <v>-77229</v>
-      </c>
-      <c r="C111" s="76"/>
-      <c r="D111" s="194"/>
-      <c r="E111" s="194"/>
-      <c r="G111" s="124"/>
-    </row>
-    <row r="112" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A112" s="79" t="s">
-        <v>173</v>
-      </c>
-      <c r="B112" s="167">
-        <v>-19000</v>
-      </c>
-      <c r="C112" s="76"/>
-      <c r="D112" s="194"/>
-      <c r="E112" s="194"/>
-      <c r="G112" s="124"/>
-    </row>
-    <row r="113" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A113" s="79" t="s">
-        <v>105</v>
-      </c>
-      <c r="B113" s="167">
-        <f>-B120</f>
-        <v>-40000</v>
-      </c>
-      <c r="C113" s="80"/>
-    </row>
-    <row r="114" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A114" s="79" t="s">
-        <v>120</v>
-      </c>
-      <c r="B114" s="93">
-        <f>-C94</f>
-        <v>0</v>
-      </c>
-      <c r="C114" s="80"/>
-    </row>
-    <row r="115" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A115" s="79"/>
-      <c r="B115" s="75"/>
-      <c r="C115" s="150"/>
-    </row>
-    <row r="116" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A116" s="77" t="s">
-        <v>94</v>
-      </c>
-      <c r="B116" s="81">
-        <f>SUM(B107:B115)</f>
-        <v>3983041.3979896172</v>
-      </c>
-      <c r="C116" s="150"/>
-    </row>
-    <row r="117" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A117" s="80"/>
-      <c r="C117" s="76"/>
-      <c r="D117" s="83"/>
-    </row>
-    <row r="118" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="C118" s="76"/>
-      <c r="D118" s="108"/>
-      <c r="E118" s="170"/>
-    </row>
-    <row r="119" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A119" s="74" t="s">
-        <v>95</v>
-      </c>
-      <c r="B119" s="11">
-        <v>-312694.54000000004</v>
+      <c r="B119" s="101">
+        <f>SUM(B115:B118)</f>
+        <v>-212694.54000000004</v>
       </c>
       <c r="C119" s="82"/>
-      <c r="D119" s="170"/>
-      <c r="E119" s="170"/>
-      <c r="F119" s="170"/>
-    </row>
-    <row r="120" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A120" s="77" t="s">
-        <v>177</v>
-      </c>
-      <c r="B120" s="93">
-        <v>40000</v>
-      </c>
-      <c r="C120" s="82"/>
-      <c r="D120" s="170"/>
-      <c r="E120" s="180"/>
-    </row>
-    <row r="121" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A121" s="77"/>
-      <c r="B121" s="167"/>
-      <c r="C121" s="82"/>
-      <c r="E121" s="108"/>
-    </row>
-    <row r="122" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A122" s="77"/>
-      <c r="B122" s="167"/>
-      <c r="C122" s="82"/>
-      <c r="E122" s="108"/>
-    </row>
-    <row r="123" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A123" s="100" t="s">
-        <v>29</v>
-      </c>
-      <c r="B123" s="101">
-        <f>SUM(B119:B122)</f>
-        <v>-272694.54000000004</v>
-      </c>
-      <c r="C123" s="82"/>
-    </row>
-    <row r="124" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="C124" s="83"/>
-      <c r="D124" s="170"/>
-    </row>
-    <row r="125" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="B125" s="80"/>
-      <c r="C125" s="76"/>
-    </row>
-    <row r="127" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="N127" s="12"/>
-    </row>
-    <row r="130" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B130" s="200"/>
-      <c r="C130" s="200"/>
-      <c r="D130" s="200"/>
-      <c r="E130" s="200"/>
-    </row>
-    <row r="131" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B131" s="200"/>
-      <c r="C131" s="200"/>
-      <c r="D131" s="200"/>
-      <c r="E131" s="200"/>
-    </row>
-    <row r="132" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B132" s="200"/>
-      <c r="C132" s="200"/>
-      <c r="D132" s="200"/>
-      <c r="E132" s="200"/>
-    </row>
-    <row r="133" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B133" s="200"/>
-      <c r="C133" s="200"/>
-      <c r="D133" s="200"/>
-      <c r="E133" s="200"/>
-    </row>
-    <row r="134" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B134" s="200"/>
-      <c r="C134" s="200"/>
-      <c r="D134" s="200"/>
-      <c r="E134" s="200"/>
+    </row>
+    <row r="120" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="C120" s="83"/>
+      <c r="D120" s="168"/>
+    </row>
+    <row r="121" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="B121" s="80"/>
+      <c r="C121" s="76"/>
+    </row>
+    <row r="123" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="N123" s="12"/>
+    </row>
+    <row r="126" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="B126" s="192"/>
+      <c r="C126" s="192"/>
+      <c r="D126" s="192"/>
+      <c r="E126" s="192"/>
+    </row>
+    <row r="127" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="B127" s="192"/>
+      <c r="C127" s="192"/>
+      <c r="D127" s="192"/>
+      <c r="E127" s="192"/>
+    </row>
+    <row r="128" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="B128" s="192"/>
+      <c r="C128" s="192"/>
+      <c r="D128" s="192"/>
+      <c r="E128" s="192"/>
+    </row>
+    <row r="129" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B129" s="192"/>
+      <c r="C129" s="192"/>
+      <c r="D129" s="192"/>
+      <c r="E129" s="192"/>
+    </row>
+    <row r="130" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B130" s="192"/>
+      <c r="C130" s="192"/>
+      <c r="D130" s="192"/>
+      <c r="E130" s="192"/>
     </row>
   </sheetData>
-  <mergeCells count="9">
-    <mergeCell ref="B130:E134"/>
-    <mergeCell ref="D105:E110"/>
+  <mergeCells count="8">
+    <mergeCell ref="B126:E130"/>
+    <mergeCell ref="D101:E106"/>
     <mergeCell ref="B14:D17"/>
-    <mergeCell ref="A100:C100"/>
-    <mergeCell ref="A98:C98"/>
-    <mergeCell ref="A97:D97"/>
-    <mergeCell ref="A58:C58"/>
+    <mergeCell ref="A96:C96"/>
+    <mergeCell ref="A94:C94"/>
+    <mergeCell ref="A93:D93"/>
     <mergeCell ref="A59:C59"/>
-    <mergeCell ref="A99:C99"/>
+    <mergeCell ref="A95:C95"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="landscape" r:id="rId1"/>
@@ -4013,27 +3874,28 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:Q63"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:R63"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="4.5546875" customWidth="1"/>
-    <col min="2" max="2" width="5.88671875" hidden="1" customWidth="1"/>
-    <col min="3" max="3" width="5.33203125" customWidth="1"/>
-    <col min="4" max="4" width="21.6640625" customWidth="1"/>
-    <col min="5" max="5" width="6.109375" customWidth="1"/>
-    <col min="6" max="7" width="12.44140625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="9.88671875" customWidth="1"/>
+    <col min="1" max="1" width="4.5703125" customWidth="1"/>
+    <col min="2" max="2" width="5.85546875" hidden="1" customWidth="1"/>
+    <col min="3" max="3" width="5.28515625" customWidth="1"/>
+    <col min="4" max="4" width="21.7109375" customWidth="1"/>
+    <col min="5" max="5" width="6.140625" customWidth="1"/>
+    <col min="6" max="7" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.85546875" customWidth="1"/>
     <col min="9" max="9" width="6" customWidth="1"/>
-    <col min="10" max="10" width="13.6640625" customWidth="1"/>
-    <col min="11" max="11" width="13.33203125" customWidth="1"/>
-    <col min="12" max="12" width="10.44140625" customWidth="1"/>
-    <col min="13" max="13" width="14.33203125" customWidth="1"/>
-    <col min="14" max="14" width="13.6640625" customWidth="1"/>
-    <col min="15" max="15" width="11.44140625" customWidth="1"/>
-    <col min="16" max="16" width="14.5546875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13.7109375" customWidth="1"/>
+    <col min="11" max="11" width="13.28515625" customWidth="1"/>
+    <col min="12" max="12" width="11.5703125" customWidth="1"/>
+    <col min="13" max="13" width="14.28515625" customWidth="1"/>
+    <col min="14" max="14" width="13.7109375" customWidth="1"/>
+    <col min="15" max="15" width="11.42578125" customWidth="1"/>
+    <col min="16" max="16" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A1" s="8"/>
       <c r="B1" s="8"/>
       <c r="C1" s="8"/>
@@ -4049,18 +3911,18 @@
       <c r="K1" s="8" t="s">
         <v>124</v>
       </c>
-      <c r="L1" s="232">
-        <f>RESUMEN!D89</f>
-        <v>6538226.8999999994</v>
-      </c>
-      <c r="M1" s="233"/>
+      <c r="L1" s="220">
+        <f>RESUMEN!D85</f>
+        <v>7515676.040000001</v>
+      </c>
+      <c r="M1" s="221"/>
       <c r="N1" s="148"/>
       <c r="O1" s="134">
         <f>L1*8.09%</f>
-        <v>528942.55620999995</v>
-      </c>
-    </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.3">
+        <v>608018.19163600006</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" s="8"/>
       <c r="B2" s="8"/>
       <c r="C2" s="8"/>
@@ -4081,10 +3943,10 @@
       <c r="N2" s="149"/>
       <c r="O2" s="134">
         <f>O1-K7-553-50-86-8</f>
-        <v>37922.306618999923</v>
-      </c>
-    </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.3">
+        <v>116997.94204500003</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" s="8" t="str">
         <f>RESUMEN!C5</f>
         <v>VTO: 14/11</v>
@@ -4103,13 +3965,13 @@
       </c>
       <c r="L3" s="8"/>
       <c r="M3" s="127">
-        <f>RESUMEN!D100</f>
-        <v>427050.4</v>
+        <f>RESUMEN!D96</f>
+        <v>2900000</v>
       </c>
       <c r="N3" s="147"/>
       <c r="O3" s="73"/>
     </row>
-    <row r="4" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="8"/>
       <c r="B4" s="8"/>
       <c r="C4" s="8"/>
@@ -4132,67 +3994,67 @@
       </c>
       <c r="N4" s="123"/>
     </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A5" s="225" t="s">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A5" s="217" t="s">
         <v>19</v>
       </c>
-      <c r="B5" s="227" t="s">
+      <c r="B5" s="231" t="s">
         <v>20</v>
       </c>
-      <c r="C5" s="225" t="s">
+      <c r="C5" s="217" t="s">
         <v>21</v>
       </c>
       <c r="D5" s="229" t="s">
         <v>22</v>
       </c>
-      <c r="E5" s="225" t="s">
+      <c r="E5" s="217" t="s">
         <v>97</v>
       </c>
-      <c r="F5" s="225" t="s">
+      <c r="F5" s="217" t="s">
         <v>23</v>
       </c>
-      <c r="G5" s="225" t="s">
+      <c r="G5" s="217" t="s">
         <v>24</v>
       </c>
-      <c r="H5" s="236" t="s">
+      <c r="H5" s="224" t="s">
         <v>25</v>
       </c>
       <c r="I5" s="229" t="s">
         <v>108</v>
       </c>
-      <c r="J5" s="234" t="s">
+      <c r="J5" s="222" t="s">
         <v>26</v>
       </c>
-      <c r="K5" s="234" t="s">
+      <c r="K5" s="222" t="s">
         <v>69</v>
       </c>
-      <c r="L5" s="239" t="s">
+      <c r="L5" s="227" t="s">
         <v>123</v>
       </c>
-      <c r="M5" s="234" t="s">
+      <c r="M5" s="222" t="s">
         <v>67</v>
       </c>
-      <c r="N5" s="234" t="s">
+      <c r="N5" s="222" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A6" s="226"/>
-      <c r="B6" s="228"/>
-      <c r="C6" s="226"/>
-      <c r="D6" s="230"/>
-      <c r="E6" s="226"/>
-      <c r="F6" s="226"/>
-      <c r="G6" s="226"/>
-      <c r="H6" s="237"/>
-      <c r="I6" s="241"/>
-      <c r="J6" s="235"/>
-      <c r="K6" s="238"/>
-      <c r="L6" s="240"/>
-      <c r="M6" s="238"/>
-      <c r="N6" s="235"/>
-    </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A6" s="218"/>
+      <c r="B6" s="232"/>
+      <c r="C6" s="218"/>
+      <c r="D6" s="233"/>
+      <c r="E6" s="218"/>
+      <c r="F6" s="218"/>
+      <c r="G6" s="218"/>
+      <c r="H6" s="225"/>
+      <c r="I6" s="230"/>
+      <c r="J6" s="223"/>
+      <c r="K6" s="226"/>
+      <c r="L6" s="228"/>
+      <c r="M6" s="226"/>
+      <c r="N6" s="223"/>
+    </row>
+    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
         <v>33</v>
       </c>
@@ -4207,11 +4069,11 @@
         <v>8.09</v>
       </c>
       <c r="F7" s="88">
-        <v>957025.20554</v>
-      </c>
-      <c r="G7" s="192">
+        <v>524871.62695100007</v>
+      </c>
+      <c r="G7" s="187">
         <f>F7</f>
-        <v>957025.20554</v>
+        <v>524871.62695100007</v>
       </c>
       <c r="H7" s="130">
         <f>F7-G7</f>
@@ -4236,7 +4098,7 @@
         <v>556363.92456806009</v>
       </c>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A8" s="7" t="s">
         <v>35</v>
       </c>
@@ -4251,14 +4113,14 @@
         <v>2.21</v>
       </c>
       <c r="F8" s="88">
-        <v>282561.27016451582</v>
-      </c>
-      <c r="G8" s="192">
-        <v>283000</v>
+        <v>164206.27016451582</v>
+      </c>
+      <c r="G8" s="187">
+        <v>165000</v>
       </c>
       <c r="H8" s="130">
         <f t="shared" ref="H8:H51" si="0">F8-G8</f>
-        <v>-438.72983548417687</v>
+        <v>-793.72983548417687</v>
       </c>
       <c r="I8" s="106">
         <v>11</v>
@@ -4271,17 +4133,17 @@
         <f>M$2*E8 /100</f>
         <v>154700</v>
       </c>
-      <c r="L8" s="159"/>
+      <c r="L8" s="158"/>
       <c r="M8" s="6">
         <f>K8+J8+H8+L8</f>
-        <v>164206.27016451582</v>
+        <v>163851.27016451582</v>
       </c>
       <c r="N8" s="11">
         <f t="shared" ref="N8:N51" si="1">M8*6% + M8</f>
-        <v>174058.64637438676</v>
-      </c>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.3">
+        <v>173682.34637438678</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A9" s="7" t="s">
         <v>35</v>
       </c>
@@ -4296,18 +4158,18 @@
         <v>4.21</v>
       </c>
       <c r="F9" s="88">
-        <v>536856.25143426331</v>
-      </c>
-      <c r="G9" s="193">
-        <f>605642-G34</f>
-        <v>536855.98190000001</v>
+        <v>333645.26953426329</v>
+      </c>
+      <c r="G9" s="188">
+        <f>373875-G34</f>
+        <v>333645</v>
       </c>
       <c r="H9" s="130">
         <f t="shared" si="0"/>
         <v>0.26953426329419017</v>
       </c>
       <c r="I9" s="106">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="J9" s="88">
         <f t="shared" ref="J9:J51" si="2">M$4*E9%</f>
@@ -4317,19 +4179,19 @@
         <f t="shared" ref="K9:K51" si="3">M$2*E9 /100</f>
         <v>294700</v>
       </c>
-      <c r="L9" s="159">
-        <v>20000</v>
+      <c r="L9" s="245">
+        <v>10000</v>
       </c>
       <c r="M9" s="6">
         <f t="shared" ref="M9:M51" si="4">K9+J9+H9+L9</f>
-        <v>333645.26953426329</v>
+        <v>323645.26953426329</v>
       </c>
       <c r="N9" s="11">
         <f t="shared" si="1"/>
-        <v>353663.9857063191</v>
-      </c>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.3">
+        <v>343063.9857063191</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A10" s="7" t="s">
         <v>38</v>
       </c>
@@ -4344,18 +4206,18 @@
         <v>2.84</v>
       </c>
       <c r="F10" s="88">
-        <v>427318.61680596869</v>
-      </c>
-      <c r="G10" s="192">
+        <v>211580</v>
+      </c>
+      <c r="G10" s="187">
         <f>F10</f>
-        <v>427318.61680596869</v>
+        <v>211580</v>
       </c>
       <c r="H10" s="130">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="I10" s="106">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="J10" s="88">
         <f t="shared" si="2"/>
@@ -4365,7 +4227,7 @@
         <f t="shared" si="3"/>
         <v>198800</v>
       </c>
-      <c r="L10" s="159"/>
+      <c r="L10" s="158"/>
       <c r="M10" s="6">
         <f t="shared" si="4"/>
         <v>211580</v>
@@ -4375,7 +4237,7 @@
         <v>224274.8</v>
       </c>
     </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A11" s="7" t="s">
         <v>38</v>
       </c>
@@ -4390,18 +4252,18 @@
         <v>3.43</v>
       </c>
       <c r="F11" s="88">
-        <v>436918.59645000001</v>
-      </c>
-      <c r="G11" s="192">
+        <v>255535</v>
+      </c>
+      <c r="G11" s="187">
         <f>F11</f>
-        <v>436918.59645000001</v>
+        <v>255535</v>
       </c>
       <c r="H11" s="130">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="I11" s="106">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="J11" s="88">
         <f t="shared" si="2"/>
@@ -4411,7 +4273,7 @@
         <f t="shared" si="3"/>
         <v>240100</v>
       </c>
-      <c r="L11" s="159"/>
+      <c r="L11" s="158"/>
       <c r="M11" s="6">
         <f t="shared" si="4"/>
         <v>255535</v>
@@ -4422,7 +4284,7 @@
       </c>
       <c r="P11" s="108"/>
     </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A12" s="7" t="s">
         <v>41</v>
       </c>
@@ -4437,18 +4299,18 @@
         <v>2.84</v>
       </c>
       <c r="F12" s="88">
-        <v>361763.50260000001</v>
-      </c>
-      <c r="G12" s="193">
+        <v>211580</v>
+      </c>
+      <c r="G12" s="188">
         <f>F12</f>
-        <v>361763.50260000001</v>
+        <v>211580</v>
       </c>
       <c r="H12" s="130">
         <f>F12-G12</f>
         <v>0</v>
       </c>
       <c r="I12" s="106">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="J12" s="88">
         <f t="shared" si="2"/>
@@ -4458,7 +4320,7 @@
         <f t="shared" si="3"/>
         <v>198800</v>
       </c>
-      <c r="L12" s="159"/>
+      <c r="L12" s="158"/>
       <c r="M12" s="6">
         <f t="shared" si="4"/>
         <v>211580</v>
@@ -4468,7 +4330,7 @@
         <v>224274.8</v>
       </c>
     </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A13" s="7" t="s">
         <v>41</v>
       </c>
@@ -4483,18 +4345,18 @@
         <v>3.43</v>
       </c>
       <c r="F13" s="88">
-        <v>446919.27356924175</v>
-      </c>
-      <c r="G13" s="193">
-        <f>444533-G50</f>
-        <v>369377.90615</v>
+        <v>343076.36741924175</v>
+      </c>
+      <c r="G13" s="188">
+        <f>309490-G50</f>
+        <v>265535</v>
       </c>
       <c r="H13" s="130">
         <f t="shared" si="0"/>
         <v>77541.367419241753</v>
       </c>
       <c r="I13" s="106">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="J13" s="88">
         <f t="shared" si="2"/>
@@ -4504,19 +4366,17 @@
         <f t="shared" si="3"/>
         <v>240100</v>
       </c>
-      <c r="L13" s="159">
-        <v>10000</v>
-      </c>
+      <c r="L13" s="158"/>
       <c r="M13" s="6">
         <f t="shared" si="4"/>
-        <v>343076.36741924175</v>
+        <v>333076.36741924175</v>
       </c>
       <c r="N13" s="11">
         <f t="shared" si="1"/>
-        <v>363660.94946439628</v>
-      </c>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.3">
+        <v>353060.94946439628</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A14" s="7" t="s">
         <v>43</v>
       </c>
@@ -4531,18 +4391,17 @@
         <v>2.84</v>
       </c>
       <c r="F14" s="88">
-        <v>385558.89592799998</v>
-      </c>
-      <c r="G14" s="192">
-        <f>F14</f>
-        <v>385558.89592799998</v>
+        <v>224274.8</v>
+      </c>
+      <c r="G14" s="187">
+        <v>211580</v>
       </c>
       <c r="H14" s="130">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>12694.799999999988</v>
       </c>
       <c r="I14" s="106">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="J14" s="88">
         <f t="shared" si="2"/>
@@ -4552,17 +4411,19 @@
         <f t="shared" si="3"/>
         <v>198800</v>
       </c>
-      <c r="L14" s="159"/>
+      <c r="L14" s="245">
+        <v>10000</v>
+      </c>
       <c r="M14" s="6">
         <f t="shared" si="4"/>
-        <v>211580</v>
+        <v>234274.8</v>
       </c>
       <c r="N14" s="11">
         <f t="shared" si="1"/>
-        <v>224274.8</v>
-      </c>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.3">
+        <v>248331.288</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A15" s="7" t="s">
         <v>43</v>
       </c>
@@ -4577,18 +4438,18 @@
         <v>3.43</v>
       </c>
       <c r="F15" s="88">
-        <v>436919.11349653394</v>
-      </c>
-      <c r="G15" s="193">
-        <f>500609-G35</f>
-        <v>436918.24249999999</v>
+        <v>255535.87099653395</v>
+      </c>
+      <c r="G15" s="188">
+        <f>292786-G35</f>
+        <v>255536</v>
       </c>
       <c r="H15" s="130">
         <f t="shared" si="0"/>
-        <v>0.87099653395125642</v>
+        <v>-0.12900346604874358</v>
       </c>
       <c r="I15" s="106">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="J15" s="88">
         <f t="shared" si="2"/>
@@ -4598,17 +4459,17 @@
         <f t="shared" si="3"/>
         <v>240100</v>
       </c>
-      <c r="L15" s="159"/>
+      <c r="L15" s="158"/>
       <c r="M15" s="6">
         <f t="shared" si="4"/>
-        <v>255535.87099653395</v>
+        <v>255534.87099653395</v>
       </c>
       <c r="N15" s="11">
         <f t="shared" si="1"/>
-        <v>270868.02325632598</v>
-      </c>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.3">
+        <v>270866.96325632598</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A16" s="7" t="s">
         <v>46</v>
       </c>
@@ -4623,18 +4484,18 @@
         <v>2.84</v>
       </c>
       <c r="F16" s="88">
-        <v>361763.68560000003</v>
-      </c>
-      <c r="G16" s="193">
-        <f>424181-G49</f>
-        <v>361764.05764999997</v>
+        <v>211579.62795000005</v>
+      </c>
+      <c r="G16" s="188">
+        <f>262969.71-G49</f>
+        <v>226464.71000000002</v>
       </c>
       <c r="H16" s="130">
         <f t="shared" si="0"/>
-        <v>-0.37204999994719401</v>
+        <v>-14885.082049999968</v>
       </c>
       <c r="I16" s="106">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="J16" s="88">
         <f t="shared" si="2"/>
@@ -4644,17 +4505,17 @@
         <f t="shared" si="3"/>
         <v>198800</v>
       </c>
-      <c r="L16" s="159"/>
+      <c r="L16" s="158"/>
       <c r="M16" s="6">
         <f t="shared" si="4"/>
-        <v>211579.62795000005</v>
+        <v>196694.91795000003</v>
       </c>
       <c r="N16" s="11">
         <f t="shared" si="1"/>
-        <v>224274.40562700006</v>
-      </c>
-    </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.3">
+        <v>208496.61302700004</v>
+      </c>
+    </row>
+    <row r="17" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A17" s="7" t="s">
         <v>46</v>
       </c>
@@ -4669,11 +4530,11 @@
         <v>3.43</v>
       </c>
       <c r="F17" s="88">
-        <v>446918.27416111476</v>
-      </c>
-      <c r="G17" s="192">
-        <f>573026-G47-G48</f>
-        <v>446918.30015000002</v>
+        <v>265534.97401111474</v>
+      </c>
+      <c r="G17" s="187">
+        <f>339290-G47-G48</f>
+        <v>265535</v>
       </c>
       <c r="H17" s="130">
         <f t="shared" si="0"/>
@@ -4690,19 +4551,17 @@
         <f t="shared" si="3"/>
         <v>240100</v>
       </c>
-      <c r="L17" s="159">
-        <v>10000</v>
-      </c>
+      <c r="L17" s="158"/>
       <c r="M17" s="6">
         <f t="shared" si="4"/>
-        <v>265534.97401111474</v>
+        <v>255534.97401111474</v>
       </c>
       <c r="N17" s="11">
         <f t="shared" si="1"/>
-        <v>281467.0724517816</v>
-      </c>
-    </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.3">
+        <v>270867.0724517816</v>
+      </c>
+    </row>
+    <row r="18" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A18" s="7" t="s">
         <v>48</v>
       </c>
@@ -4717,18 +4576,18 @@
         <v>2.84</v>
       </c>
       <c r="F18" s="88">
-        <v>360516.96358325134</v>
-      </c>
-      <c r="G18" s="192">
-        <f>320000+114000-G51</f>
-        <v>361392.53645000001</v>
+        <v>210704.42713325133</v>
+      </c>
+      <c r="G18" s="187">
+        <f>260000-G51</f>
+        <v>217535</v>
       </c>
       <c r="H18" s="130">
         <f t="shared" si="0"/>
-        <v>-875.57286674866918</v>
+        <v>-6830.5728667486692</v>
       </c>
       <c r="I18" s="106">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="J18" s="88">
         <f t="shared" si="2"/>
@@ -4738,17 +4597,17 @@
         <f t="shared" si="3"/>
         <v>198800</v>
       </c>
-      <c r="L18" s="159"/>
+      <c r="L18" s="158"/>
       <c r="M18" s="6">
         <f t="shared" si="4"/>
-        <v>210704.42713325133</v>
+        <v>204749.42713325133</v>
       </c>
       <c r="N18" s="11">
         <f t="shared" si="1"/>
-        <v>223346.69276124641</v>
-      </c>
-    </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.3">
+        <v>217034.39276124642</v>
+      </c>
+    </row>
+    <row r="19" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A19" s="7" t="s">
         <v>48</v>
       </c>
@@ -4763,18 +4622,18 @@
         <v>3.43</v>
       </c>
       <c r="F19" s="88">
-        <v>436919.46821516805</v>
-      </c>
-      <c r="G19" s="193">
-        <f>505705-G41</f>
-        <v>436918.98190000001</v>
+        <v>255535.48631516803</v>
+      </c>
+      <c r="G19" s="188">
+        <f>295765-G41</f>
+        <v>255535</v>
       </c>
       <c r="H19" s="130">
         <f t="shared" si="0"/>
         <v>0.48631516803288832</v>
       </c>
       <c r="I19" s="106">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="J19" s="88">
         <f t="shared" si="2"/>
@@ -4784,7 +4643,7 @@
         <f t="shared" si="3"/>
         <v>240100</v>
       </c>
-      <c r="L19" s="159"/>
+      <c r="L19" s="158"/>
       <c r="M19" s="6">
         <f t="shared" si="4"/>
         <v>255535.48631516803</v>
@@ -4794,7 +4653,7 @@
         <v>270867.61549407814</v>
       </c>
     </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A20" s="7" t="s">
         <v>51</v>
       </c>
@@ -4809,18 +4668,18 @@
         <v>2.84</v>
       </c>
       <c r="F20" s="88">
-        <v>373009.71350707469</v>
-      </c>
-      <c r="G20" s="192">
-        <f>435427-G38</f>
-        <v>373010.05764999997</v>
+        <v>211579.65585707471</v>
+      </c>
+      <c r="G20" s="187">
+        <f>248085-G38</f>
+        <v>211580</v>
       </c>
       <c r="H20" s="130">
         <f t="shared" si="0"/>
         <v>-0.34414292528526857</v>
       </c>
       <c r="I20" s="106">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="J20" s="88">
         <f t="shared" si="2"/>
@@ -4830,7 +4689,7 @@
         <f t="shared" si="3"/>
         <v>198800</v>
       </c>
-      <c r="L20" s="159"/>
+      <c r="L20" s="158"/>
       <c r="M20" s="6">
         <f t="shared" si="4"/>
         <v>211579.65585707471</v>
@@ -4840,7 +4699,7 @@
         <v>224274.4352084992</v>
       </c>
     </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A21" s="7" t="s">
         <v>51</v>
       </c>
@@ -4855,18 +4714,18 @@
         <v>3.43</v>
       </c>
       <c r="F21" s="88">
-        <v>436918.87054179591</v>
-      </c>
-      <c r="G21" s="192">
-        <f>505705-G45</f>
-        <v>436918.98190000001</v>
+        <v>255534.8886417959</v>
+      </c>
+      <c r="G21" s="187">
+        <f>295765-G45</f>
+        <v>255535</v>
       </c>
       <c r="H21" s="130">
         <f t="shared" si="0"/>
         <v>-0.11135820409981534</v>
       </c>
       <c r="I21" s="106">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="J21" s="88">
         <f t="shared" si="2"/>
@@ -4876,7 +4735,7 @@
         <f t="shared" si="3"/>
         <v>240100</v>
       </c>
-      <c r="L21" s="159"/>
+      <c r="L21" s="158"/>
       <c r="M21" s="6">
         <f t="shared" si="4"/>
         <v>255534.8886417959</v>
@@ -4886,7 +4745,7 @@
         <v>270866.98196030367</v>
       </c>
     </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A22" s="7" t="s">
         <v>54</v>
       </c>
@@ -4894,25 +4753,25 @@
       <c r="C22" s="7">
         <v>38</v>
       </c>
-      <c r="D22" s="160" t="s">
+      <c r="D22" s="159" t="s">
         <v>128</v>
       </c>
       <c r="E22" s="7">
         <v>2.84</v>
       </c>
       <c r="F22" s="88">
-        <v>361763.50260000001</v>
-      </c>
-      <c r="G22" s="192">
+        <v>211580</v>
+      </c>
+      <c r="G22" s="187">
         <f>F22</f>
-        <v>361763.50260000001</v>
+        <v>211580</v>
       </c>
       <c r="H22" s="130">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="I22" s="106">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J22" s="88">
         <f t="shared" si="2"/>
@@ -4922,7 +4781,7 @@
         <f t="shared" si="3"/>
         <v>198800</v>
       </c>
-      <c r="L22" s="159"/>
+      <c r="L22" s="158"/>
       <c r="M22" s="6">
         <f t="shared" si="4"/>
         <v>211580</v>
@@ -4932,7 +4791,7 @@
         <v>224274.8</v>
       </c>
     </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A23" s="7" t="s">
         <v>54</v>
       </c>
@@ -4947,15 +4806,15 @@
         <v>3.43</v>
       </c>
       <c r="F23" s="88">
-        <v>494287.98306212929</v>
-      </c>
-      <c r="G23" s="193">
-        <f>525000-G46</f>
-        <v>457487.79704999999</v>
+        <v>320475.29717285704</v>
+      </c>
+      <c r="G23" s="188">
+        <f>361000-G46</f>
+        <v>323750</v>
       </c>
       <c r="H23" s="130">
         <f t="shared" si="0"/>
-        <v>36800.186012129299</v>
+        <v>-3274.702827142959</v>
       </c>
       <c r="I23" s="106">
         <v>23</v>
@@ -4968,19 +4827,17 @@
         <f t="shared" si="3"/>
         <v>240100</v>
       </c>
-      <c r="L23" s="159">
-        <v>10000</v>
-      </c>
+      <c r="L23" s="158"/>
       <c r="M23" s="6">
         <f t="shared" si="4"/>
-        <v>302335.1860121293</v>
+        <v>252260.29717285704</v>
       </c>
       <c r="N23" s="11">
         <f t="shared" si="1"/>
-        <v>320475.29717285704</v>
-      </c>
-    </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.3">
+        <v>267395.91500322847</v>
+      </c>
+    </row>
+    <row r="24" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A24" s="7" t="s">
         <v>56</v>
       </c>
@@ -4995,18 +4852,18 @@
         <v>2.84</v>
       </c>
       <c r="F24" s="88">
-        <v>365701.43107107468</v>
-      </c>
-      <c r="G24" s="192">
-        <f>428118-G37</f>
-        <v>365701.05764999997</v>
+        <v>221580.37342107471</v>
+      </c>
+      <c r="G24" s="187">
+        <f>259000-G37</f>
+        <v>222495</v>
       </c>
       <c r="H24" s="130">
         <f t="shared" si="0"/>
-        <v>0.37342107470612973</v>
-      </c>
-      <c r="I24" s="171">
-        <v>2</v>
+        <v>-914.62657892529387</v>
+      </c>
+      <c r="I24" s="169">
+        <v>9</v>
       </c>
       <c r="J24" s="88">
         <f t="shared" si="2"/>
@@ -5016,19 +4873,17 @@
         <f t="shared" si="3"/>
         <v>198800</v>
       </c>
-      <c r="L24" s="159">
-        <v>10000</v>
-      </c>
+      <c r="L24" s="158"/>
       <c r="M24" s="6">
         <f t="shared" si="4"/>
-        <v>221580.37342107471</v>
+        <v>210665.37342107471</v>
       </c>
       <c r="N24" s="11">
         <f t="shared" si="1"/>
-        <v>234875.19582633919</v>
-      </c>
-    </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.3">
+        <v>223305.29582633919</v>
+      </c>
+    </row>
+    <row r="25" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A25" s="7" t="s">
         <v>56</v>
       </c>
@@ -5043,11 +4898,11 @@
         <v>3.43</v>
       </c>
       <c r="F25" s="88">
-        <v>436918.59645000001</v>
-      </c>
-      <c r="G25" s="192">
+        <v>255535</v>
+      </c>
+      <c r="G25" s="187">
         <f>F25</f>
-        <v>436918.59645000001</v>
+        <v>255535</v>
       </c>
       <c r="H25" s="130">
         <f t="shared" si="0"/>
@@ -5064,17 +4919,23 @@
         <f t="shared" si="3"/>
         <v>240100</v>
       </c>
-      <c r="L25" s="159"/>
+      <c r="L25" s="246">
+        <f>77229+250000+38000+(((K25+J25)*0.5))*6</f>
+        <v>1131834</v>
+      </c>
       <c r="M25" s="6">
         <f t="shared" si="4"/>
-        <v>255535</v>
+        <v>1387369</v>
       </c>
       <c r="N25" s="11">
         <f t="shared" si="1"/>
-        <v>270867.09999999998</v>
-      </c>
-    </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.3">
+        <v>1470611.14</v>
+      </c>
+      <c r="P25" s="137"/>
+      <c r="Q25" s="137"/>
+      <c r="R25" s="137"/>
+    </row>
+    <row r="26" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A26" s="7" t="s">
         <v>59</v>
       </c>
@@ -5089,15 +4950,15 @@
         <v>6</v>
       </c>
       <c r="F26" s="88">
-        <v>715630.38381603709</v>
-      </c>
-      <c r="G26" s="193">
-        <f>1800000-G30-G31-G36</f>
-        <v>1597463.39115</v>
+        <v>-434833.00733396295</v>
+      </c>
+      <c r="G26" s="188">
+        <f>-G36-G30-G31</f>
+        <v>-118455</v>
       </c>
       <c r="H26" s="131">
         <f t="shared" si="0"/>
-        <v>-881833.00733396295</v>
+        <v>-316378.00733396295</v>
       </c>
       <c r="I26" s="106">
         <v>2</v>
@@ -5110,17 +4971,17 @@
         <f t="shared" si="3"/>
         <v>420000</v>
       </c>
-      <c r="L26" s="159"/>
+      <c r="L26" s="158"/>
       <c r="M26" s="6">
         <f t="shared" si="4"/>
-        <v>-434833.00733396295</v>
+        <v>130621.99266603705</v>
       </c>
       <c r="N26" s="11">
         <f t="shared" si="1"/>
-        <v>-460922.98777400074</v>
-      </c>
-    </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.3">
+        <v>138459.31222599928</v>
+      </c>
+    </row>
+    <row r="27" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A27" s="7" t="s">
         <v>61</v>
       </c>
@@ -5135,18 +4996,18 @@
         <v>5.89</v>
       </c>
       <c r="F27" s="88">
-        <v>750276.8138852655</v>
-      </c>
-      <c r="G27" s="192">
-        <f>898039-G39-G40</f>
-        <v>750276.44260000007</v>
+        <v>438805.37128526543</v>
+      </c>
+      <c r="G27" s="187">
+        <f>520005-G39-G40</f>
+        <v>433585</v>
       </c>
       <c r="H27" s="130">
         <f t="shared" si="0"/>
-        <v>0.3712852654280141</v>
+        <v>5220.371285265428</v>
       </c>
       <c r="I27" s="106">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="J27" s="88">
         <f t="shared" si="2"/>
@@ -5156,17 +5017,18 @@
         <f t="shared" si="3"/>
         <v>412300</v>
       </c>
-      <c r="L27" s="159"/>
+      <c r="L27" s="158"/>
       <c r="M27" s="6">
         <f t="shared" si="4"/>
-        <v>438805.37128526543</v>
+        <v>444025.37128526543</v>
       </c>
       <c r="N27" s="11">
         <f t="shared" si="1"/>
-        <v>465133.69356238138</v>
-      </c>
-    </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.3">
+        <v>470666.89356238133</v>
+      </c>
+      <c r="R27" s="137"/>
+    </row>
+    <row r="28" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A28" s="7" t="s">
         <v>63</v>
       </c>
@@ -5181,18 +5043,18 @@
         <v>5.89</v>
       </c>
       <c r="F28" s="88">
-        <v>750210.10192654096</v>
-      </c>
-      <c r="G28" s="192">
-        <f>885235-G32-G33</f>
-        <v>750210.59409999999</v>
+        <v>438804.50782654097</v>
+      </c>
+      <c r="G28" s="187">
+        <f>518000-G32-G33</f>
+        <v>439030</v>
       </c>
       <c r="H28" s="130">
         <f t="shared" si="0"/>
-        <v>-0.49217345903161913</v>
+        <v>-225.49217345903162</v>
       </c>
       <c r="I28" s="106">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J28" s="88">
         <f t="shared" si="2"/>
@@ -5202,17 +5064,17 @@
         <f t="shared" si="3"/>
         <v>412300</v>
       </c>
-      <c r="L28" s="159"/>
+      <c r="L28" s="158"/>
       <c r="M28" s="6">
         <f t="shared" si="4"/>
-        <v>438804.50782654097</v>
+        <v>438579.50782654097</v>
       </c>
       <c r="N28" s="11">
         <f t="shared" si="1"/>
-        <v>465132.77829613345</v>
-      </c>
-    </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.3">
+        <v>464894.27829613345</v>
+      </c>
+    </row>
+    <row r="29" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A29" s="7" t="s">
         <v>65</v>
       </c>
@@ -5227,18 +5089,18 @@
         <v>5.89</v>
       </c>
       <c r="F29" s="88">
-        <v>748720.46480670001</v>
-      </c>
-      <c r="G29" s="193">
-        <f>954000-G42-G43-G44</f>
-        <v>748915.76084999996</v>
+        <v>438609.70395670005</v>
+      </c>
+      <c r="G29" s="188">
+        <f>558645-G42-G43-G44</f>
+        <v>438700</v>
       </c>
       <c r="H29" s="131">
         <f t="shared" si="0"/>
-        <v>-195.29604329995345</v>
+        <v>-90.296043299953453</v>
       </c>
       <c r="I29" s="106">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="J29" s="88">
         <f t="shared" si="2"/>
@@ -5248,17 +5110,17 @@
         <f t="shared" si="3"/>
         <v>412300</v>
       </c>
-      <c r="L29" s="159"/>
+      <c r="L29" s="158"/>
       <c r="M29" s="6">
         <f t="shared" si="4"/>
-        <v>438609.70395670005</v>
+        <v>438714.70395670005</v>
       </c>
       <c r="N29" s="11">
         <f t="shared" si="1"/>
-        <v>464926.28619410202</v>
-      </c>
-    </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.3">
+        <v>465037.58619410207</v>
+      </c>
+    </row>
+    <row r="30" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A30" s="125" t="s">
         <v>96</v>
       </c>
@@ -5273,11 +5135,11 @@
         <v>0.54</v>
       </c>
       <c r="F30" s="88">
-        <v>68786.018100000016</v>
-      </c>
-      <c r="G30" s="192">
-        <f t="shared" ref="G30:G34" si="5">F30</f>
-        <v>68786.018100000016</v>
+        <v>40230.000000000007</v>
+      </c>
+      <c r="G30" s="187">
+        <f>F30</f>
+        <v>40230.000000000007</v>
       </c>
       <c r="H30" s="130">
         <f t="shared" si="0"/>
@@ -5292,7 +5154,7 @@
         <f t="shared" si="3"/>
         <v>37800.000000000007</v>
       </c>
-      <c r="L30" s="159"/>
+      <c r="L30" s="158"/>
       <c r="M30" s="6">
         <f t="shared" si="4"/>
         <v>40230.000000000007</v>
@@ -5302,7 +5164,7 @@
         <v>42643.80000000001</v>
       </c>
     </row>
-    <row r="31" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A31" s="125" t="s">
         <v>96</v>
       </c>
@@ -5317,11 +5179,11 @@
         <v>0.55000000000000004</v>
       </c>
       <c r="F31" s="88">
-        <v>70059.833250000011</v>
-      </c>
-      <c r="G31" s="192">
-        <f t="shared" si="5"/>
-        <v>70059.833250000011</v>
+        <v>40975.000000000007</v>
+      </c>
+      <c r="G31" s="187">
+        <f>F31</f>
+        <v>40975.000000000007</v>
       </c>
       <c r="H31" s="130">
         <f t="shared" si="0"/>
@@ -5336,7 +5198,7 @@
         <f t="shared" si="3"/>
         <v>38500.000000000007</v>
       </c>
-      <c r="L31" s="159"/>
+      <c r="L31" s="158"/>
       <c r="M31" s="6">
         <f t="shared" si="4"/>
         <v>40975.000000000007</v>
@@ -5346,7 +5208,7 @@
         <v>43433.500000000007</v>
       </c>
     </row>
-    <row r="32" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A32" s="125" t="s">
         <v>96</v>
       </c>
@@ -5361,11 +5223,11 @@
         <v>0.45</v>
       </c>
       <c r="F32" s="88">
-        <v>57321.681750000003</v>
-      </c>
-      <c r="G32" s="192">
+        <v>33525</v>
+      </c>
+      <c r="G32" s="187">
         <f>F32</f>
-        <v>57321.681750000003</v>
+        <v>33525</v>
       </c>
       <c r="H32" s="130">
         <f t="shared" si="0"/>
@@ -5380,7 +5242,7 @@
         <f t="shared" si="3"/>
         <v>31500</v>
       </c>
-      <c r="L32" s="159"/>
+      <c r="L32" s="158"/>
       <c r="M32" s="6">
         <f t="shared" si="4"/>
         <v>33525</v>
@@ -5390,7 +5252,7 @@
         <v>35536.5</v>
       </c>
     </row>
-    <row r="33" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A33" s="125" t="s">
         <v>96</v>
       </c>
@@ -5405,11 +5267,11 @@
         <v>0.61</v>
       </c>
       <c r="F33" s="88">
-        <v>77702.724149999995</v>
-      </c>
-      <c r="G33" s="192">
-        <f t="shared" si="5"/>
-        <v>77702.724149999995</v>
+        <v>45445</v>
+      </c>
+      <c r="G33" s="187">
+        <f t="shared" ref="G30:G34" si="5">F33</f>
+        <v>45445</v>
       </c>
       <c r="H33" s="130">
         <f t="shared" si="0"/>
@@ -5424,7 +5286,7 @@
         <f t="shared" si="3"/>
         <v>42700</v>
       </c>
-      <c r="L33" s="159"/>
+      <c r="L33" s="158"/>
       <c r="M33" s="6">
         <f t="shared" si="4"/>
         <v>45445</v>
@@ -5434,7 +5296,7 @@
         <v>48171.7</v>
       </c>
     </row>
-    <row r="34" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A34" s="125" t="s">
         <v>96</v>
       </c>
@@ -5449,11 +5311,11 @@
         <v>0.54</v>
       </c>
       <c r="F34" s="88">
-        <v>68786.018100000016</v>
-      </c>
-      <c r="G34" s="192">
+        <v>40230.000000000007</v>
+      </c>
+      <c r="G34" s="187">
         <f t="shared" si="5"/>
-        <v>68786.018100000016</v>
+        <v>40230.000000000007</v>
       </c>
       <c r="H34" s="130">
         <f t="shared" si="0"/>
@@ -5468,7 +5330,7 @@
         <f t="shared" si="3"/>
         <v>37800.000000000007</v>
       </c>
-      <c r="L34" s="159"/>
+      <c r="L34" s="158"/>
       <c r="M34" s="6">
         <f t="shared" si="4"/>
         <v>40230.000000000007</v>
@@ -5478,7 +5340,7 @@
         <v>42643.80000000001</v>
       </c>
     </row>
-    <row r="35" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A35" s="125" t="s">
         <v>96</v>
       </c>
@@ -5493,11 +5355,11 @@
         <v>0.5</v>
       </c>
       <c r="F35" s="11">
-        <v>63690.757500000007</v>
-      </c>
-      <c r="G35" s="193">
+        <v>37250</v>
+      </c>
+      <c r="G35" s="188">
         <f>F35</f>
-        <v>63690.757500000007</v>
+        <v>37250</v>
       </c>
       <c r="H35" s="130">
         <f t="shared" si="0"/>
@@ -5512,7 +5374,7 @@
         <f t="shared" si="3"/>
         <v>35000</v>
       </c>
-      <c r="L35" s="159"/>
+      <c r="L35" s="158"/>
       <c r="M35" s="6">
         <f t="shared" si="4"/>
         <v>37250</v>
@@ -5522,7 +5384,7 @@
         <v>39485</v>
       </c>
     </row>
-    <row r="36" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A36" s="125" t="s">
         <v>96</v>
       </c>
@@ -5537,11 +5399,11 @@
         <v>0.5</v>
       </c>
       <c r="F36" s="88">
-        <v>63690.757500000007</v>
-      </c>
-      <c r="G36" s="192">
-        <f t="shared" ref="G36:G41" si="6">F36</f>
-        <v>63690.757500000007</v>
+        <v>37250</v>
+      </c>
+      <c r="G36" s="187">
+        <f>F36</f>
+        <v>37250</v>
       </c>
       <c r="H36" s="130">
         <f t="shared" si="0"/>
@@ -5556,7 +5418,7 @@
         <f t="shared" si="3"/>
         <v>35000</v>
       </c>
-      <c r="L36" s="159"/>
+      <c r="L36" s="158"/>
       <c r="M36" s="6">
         <f t="shared" si="4"/>
         <v>37250</v>
@@ -5566,7 +5428,7 @@
         <v>39485</v>
       </c>
     </row>
-    <row r="37" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A37" s="125" t="s">
         <v>96</v>
       </c>
@@ -5581,11 +5443,11 @@
         <v>0.49</v>
       </c>
       <c r="F37" s="88">
-        <v>62416.942349999998</v>
-      </c>
-      <c r="G37" s="192">
-        <f t="shared" si="6"/>
-        <v>62416.942349999998</v>
+        <v>36505</v>
+      </c>
+      <c r="G37" s="187">
+        <f t="shared" ref="G36:G41" si="6">F37</f>
+        <v>36505</v>
       </c>
       <c r="H37" s="130">
         <f t="shared" si="0"/>
@@ -5600,7 +5462,7 @@
         <f t="shared" si="3"/>
         <v>34300</v>
       </c>
-      <c r="L37" s="159"/>
+      <c r="L37" s="158"/>
       <c r="M37" s="6">
         <f t="shared" si="4"/>
         <v>36505</v>
@@ -5610,7 +5472,7 @@
         <v>38695.300000000003</v>
       </c>
     </row>
-    <row r="38" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A38" s="125" t="s">
         <v>96</v>
       </c>
@@ -5625,11 +5487,11 @@
         <v>0.49</v>
       </c>
       <c r="F38" s="88">
-        <v>62416.942349999998</v>
-      </c>
-      <c r="G38" s="192">
+        <v>36505</v>
+      </c>
+      <c r="G38" s="187">
         <f t="shared" si="6"/>
-        <v>62416.942349999998</v>
+        <v>36505</v>
       </c>
       <c r="H38" s="130">
         <f t="shared" si="0"/>
@@ -5644,7 +5506,7 @@
         <f t="shared" si="3"/>
         <v>34300</v>
       </c>
-      <c r="L38" s="159"/>
+      <c r="L38" s="158"/>
       <c r="M38" s="6">
         <f t="shared" si="4"/>
         <v>36505</v>
@@ -5654,7 +5516,7 @@
         <v>38695.300000000003</v>
       </c>
     </row>
-    <row r="39" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A39" s="125" t="s">
         <v>96</v>
       </c>
@@ -5669,11 +5531,11 @@
         <v>0.59</v>
       </c>
       <c r="F39" s="88">
-        <v>75155.09384999999</v>
-      </c>
-      <c r="G39" s="192">
+        <v>43955</v>
+      </c>
+      <c r="G39" s="187">
         <f t="shared" si="6"/>
-        <v>75155.09384999999</v>
+        <v>43955</v>
       </c>
       <c r="H39" s="130">
         <f t="shared" si="0"/>
@@ -5688,7 +5550,7 @@
         <f t="shared" si="3"/>
         <v>41300</v>
       </c>
-      <c r="L39" s="159"/>
+      <c r="L39" s="158"/>
       <c r="M39" s="6">
         <f t="shared" si="4"/>
         <v>43955</v>
@@ -5698,7 +5560,7 @@
         <v>46592.3</v>
       </c>
     </row>
-    <row r="40" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A40" s="125" t="s">
         <v>96</v>
       </c>
@@ -5713,11 +5575,11 @@
         <v>0.56999999999999995</v>
       </c>
       <c r="F40" s="88">
-        <v>72607.463549999986</v>
-      </c>
-      <c r="G40" s="192">
+        <v>42464.999999999993</v>
+      </c>
+      <c r="G40" s="187">
         <f t="shared" si="6"/>
-        <v>72607.463549999986</v>
+        <v>42464.999999999993</v>
       </c>
       <c r="H40" s="130">
         <f t="shared" si="0"/>
@@ -5732,7 +5594,7 @@
         <f t="shared" si="3"/>
         <v>39899.999999999993</v>
       </c>
-      <c r="L40" s="159"/>
+      <c r="L40" s="158"/>
       <c r="M40" s="6">
         <f t="shared" si="4"/>
         <v>42464.999999999993</v>
@@ -5742,7 +5604,7 @@
         <v>45012.899999999994</v>
       </c>
     </row>
-    <row r="41" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A41" s="125" t="s">
         <v>96</v>
       </c>
@@ -5757,11 +5619,11 @@
         <v>0.54</v>
       </c>
       <c r="F41" s="88">
-        <v>68786.018100000016</v>
-      </c>
-      <c r="G41" s="192">
+        <v>40230.000000000007</v>
+      </c>
+      <c r="G41" s="187">
         <f t="shared" si="6"/>
-        <v>68786.018100000016</v>
+        <v>40230.000000000007</v>
       </c>
       <c r="H41" s="130">
         <f t="shared" si="0"/>
@@ -5776,7 +5638,7 @@
         <f t="shared" si="3"/>
         <v>37800.000000000007</v>
       </c>
-      <c r="L41" s="159"/>
+      <c r="L41" s="158"/>
       <c r="M41" s="6">
         <f t="shared" si="4"/>
         <v>40230.000000000007</v>
@@ -5786,7 +5648,7 @@
         <v>42643.80000000001</v>
       </c>
     </row>
-    <row r="42" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A42" s="125" t="s">
         <v>96</v>
       </c>
@@ -5801,11 +5663,11 @@
         <v>0.55000000000000004</v>
       </c>
       <c r="F42" s="88">
-        <v>70059.833250000011</v>
-      </c>
-      <c r="G42" s="192">
+        <v>40975.000000000007</v>
+      </c>
+      <c r="G42" s="187">
         <f>F42</f>
-        <v>70059.833250000011</v>
+        <v>40975.000000000007</v>
       </c>
       <c r="H42" s="130">
         <f t="shared" si="0"/>
@@ -5820,7 +5682,7 @@
         <f t="shared" si="3"/>
         <v>38500.000000000007</v>
       </c>
-      <c r="L42" s="159"/>
+      <c r="L42" s="158"/>
       <c r="M42" s="6">
         <f t="shared" si="4"/>
         <v>40975.000000000007</v>
@@ -5830,7 +5692,7 @@
         <v>43433.500000000007</v>
       </c>
     </row>
-    <row r="43" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A43" s="125" t="s">
         <v>96</v>
       </c>
@@ -5845,11 +5707,11 @@
         <v>0.45</v>
       </c>
       <c r="F43" s="88">
-        <v>57321.681750000003</v>
-      </c>
-      <c r="G43" s="192">
+        <v>33525</v>
+      </c>
+      <c r="G43" s="187">
         <f t="shared" ref="G43:G44" si="7">F43</f>
-        <v>57321.681750000003</v>
+        <v>33525</v>
       </c>
       <c r="H43" s="130">
         <f t="shared" si="0"/>
@@ -5864,7 +5726,7 @@
         <f t="shared" si="3"/>
         <v>31500</v>
       </c>
-      <c r="L43" s="159"/>
+      <c r="L43" s="158"/>
       <c r="M43" s="6">
         <f t="shared" si="4"/>
         <v>33525</v>
@@ -5875,10 +5737,10 @@
       </c>
       <c r="P43" s="108">
         <f>L1-K52</f>
-        <v>-385796.34959100094</v>
-      </c>
-    </row>
-    <row r="44" spans="1:17" x14ac:dyDescent="0.3">
+        <v>591652.79040900059</v>
+      </c>
+    </row>
+    <row r="44" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A44" s="125" t="s">
         <v>96</v>
       </c>
@@ -5893,11 +5755,11 @@
         <v>0.61</v>
       </c>
       <c r="F44" s="88">
-        <v>77702.724149999995</v>
-      </c>
-      <c r="G44" s="192">
+        <v>45445</v>
+      </c>
+      <c r="G44" s="187">
         <f t="shared" si="7"/>
-        <v>77702.724149999995</v>
+        <v>45445</v>
       </c>
       <c r="H44" s="130">
         <f t="shared" si="0"/>
@@ -5912,7 +5774,7 @@
         <f t="shared" si="3"/>
         <v>42700</v>
       </c>
-      <c r="L44" s="159"/>
+      <c r="L44" s="158"/>
       <c r="M44" s="6">
         <f t="shared" si="4"/>
         <v>45445</v>
@@ -5922,7 +5784,7 @@
         <v>48171.7</v>
       </c>
     </row>
-    <row r="45" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A45" s="125" t="s">
         <v>96</v>
       </c>
@@ -5937,11 +5799,11 @@
         <v>0.54</v>
       </c>
       <c r="F45" s="88">
-        <v>68786.018100000016</v>
-      </c>
-      <c r="G45" s="192">
+        <v>40230.000000000007</v>
+      </c>
+      <c r="G45" s="187">
         <f t="shared" ref="G45:G51" si="8">F45</f>
-        <v>68786.018100000016</v>
+        <v>40230.000000000007</v>
       </c>
       <c r="H45" s="130">
         <f t="shared" si="0"/>
@@ -5956,7 +5818,7 @@
         <f t="shared" si="3"/>
         <v>37800.000000000007</v>
       </c>
-      <c r="L45" s="159"/>
+      <c r="L45" s="158"/>
       <c r="M45" s="6">
         <f t="shared" si="4"/>
         <v>40230.000000000007</v>
@@ -5966,7 +5828,7 @@
         <v>42643.80000000001</v>
       </c>
     </row>
-    <row r="46" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A46" s="125" t="s">
         <v>96</v>
       </c>
@@ -5981,11 +5843,11 @@
         <v>0.5</v>
       </c>
       <c r="F46" s="88">
-        <v>67512.202950000006</v>
-      </c>
-      <c r="G46" s="192">
+        <v>37250</v>
+      </c>
+      <c r="G46" s="187">
         <f>F46</f>
-        <v>67512.202950000006</v>
+        <v>37250</v>
       </c>
       <c r="H46" s="130">
         <f t="shared" si="0"/>
@@ -6000,7 +5862,7 @@
         <f t="shared" si="3"/>
         <v>35000</v>
       </c>
-      <c r="L46" s="159"/>
+      <c r="L46" s="158"/>
       <c r="M46" s="6">
         <f t="shared" si="4"/>
         <v>37250</v>
@@ -6013,7 +5875,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="47" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A47" s="125" t="s">
         <v>96</v>
       </c>
@@ -6028,11 +5890,11 @@
         <v>0.5</v>
       </c>
       <c r="F47" s="88">
-        <v>63690.757500000007</v>
-      </c>
-      <c r="G47" s="192">
+        <v>37250</v>
+      </c>
+      <c r="G47" s="187">
         <f t="shared" si="8"/>
-        <v>63690.757500000007</v>
+        <v>37250</v>
       </c>
       <c r="H47" s="130">
         <f t="shared" si="0"/>
@@ -6047,7 +5909,7 @@
         <f t="shared" si="3"/>
         <v>35000</v>
       </c>
-      <c r="L47" s="159"/>
+      <c r="L47" s="158"/>
       <c r="M47" s="6">
         <f t="shared" si="4"/>
         <v>37250</v>
@@ -6059,10 +5921,10 @@
       <c r="O47" s="137"/>
       <c r="Q47" s="134">
         <f>M3-J52</f>
-        <v>13455.400000000023</v>
-      </c>
-    </row>
-    <row r="48" spans="1:17" x14ac:dyDescent="0.3">
+        <v>2486405</v>
+      </c>
+    </row>
+    <row r="48" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A48" s="125" t="s">
         <v>96</v>
       </c>
@@ -6077,11 +5939,11 @@
         <v>0.49</v>
       </c>
       <c r="F48" s="88">
-        <v>62416.942349999998</v>
-      </c>
-      <c r="G48" s="192">
+        <v>36505</v>
+      </c>
+      <c r="G48" s="187">
         <f t="shared" si="8"/>
-        <v>62416.942349999998</v>
+        <v>36505</v>
       </c>
       <c r="H48" s="130">
         <f t="shared" si="0"/>
@@ -6096,7 +5958,7 @@
         <f t="shared" si="3"/>
         <v>34300</v>
       </c>
-      <c r="L48" s="159"/>
+      <c r="L48" s="158"/>
       <c r="M48" s="6">
         <f t="shared" si="4"/>
         <v>36505</v>
@@ -6106,7 +5968,7 @@
         <v>38695.300000000003</v>
       </c>
     </row>
-    <row r="49" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A49" s="125" t="s">
         <v>96</v>
       </c>
@@ -6122,11 +5984,11 @@
         <v>0.49</v>
       </c>
       <c r="F49" s="88">
-        <v>62416.942349999998</v>
-      </c>
-      <c r="G49" s="192">
+        <v>36505</v>
+      </c>
+      <c r="G49" s="187">
         <f>F49</f>
-        <v>62416.942349999998</v>
+        <v>36505</v>
       </c>
       <c r="H49" s="130">
         <f t="shared" si="0"/>
@@ -6141,7 +6003,7 @@
         <f t="shared" si="3"/>
         <v>34300</v>
       </c>
-      <c r="L49" s="159"/>
+      <c r="L49" s="158"/>
       <c r="M49" s="6">
         <f t="shared" si="4"/>
         <v>36505</v>
@@ -6151,7 +6013,7 @@
         <v>38695.300000000003</v>
       </c>
     </row>
-    <row r="50" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A50" s="125" t="s">
         <v>96</v>
       </c>
@@ -6166,11 +6028,11 @@
         <v>0.59</v>
       </c>
       <c r="F50" s="88">
-        <v>75155.09384999999</v>
-      </c>
-      <c r="G50" s="193">
+        <v>43955</v>
+      </c>
+      <c r="G50" s="188">
         <f>F50</f>
-        <v>75155.09384999999</v>
+        <v>43955</v>
       </c>
       <c r="H50" s="130">
         <f t="shared" si="0"/>
@@ -6185,7 +6047,7 @@
         <f t="shared" si="3"/>
         <v>41300</v>
       </c>
-      <c r="L50" s="159"/>
+      <c r="L50" s="158"/>
       <c r="M50" s="6">
         <f t="shared" si="4"/>
         <v>43955</v>
@@ -6195,7 +6057,7 @@
         <v>46592.3</v>
       </c>
     </row>
-    <row r="51" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A51" s="125" t="s">
         <v>96</v>
       </c>
@@ -6210,11 +6072,11 @@
         <v>0.56999999999999995</v>
       </c>
       <c r="F51" s="88">
-        <v>72607.463549999986</v>
-      </c>
-      <c r="G51" s="192">
-        <f t="shared" si="8"/>
-        <v>72607.463549999986</v>
+        <v>42464.999999999993</v>
+      </c>
+      <c r="G51" s="187">
+        <f>F51</f>
+        <v>42464.999999999993</v>
       </c>
       <c r="H51" s="130">
         <f t="shared" si="0"/>
@@ -6229,7 +6091,7 @@
         <f t="shared" si="3"/>
         <v>39899.999999999993</v>
       </c>
-      <c r="L51" s="159"/>
+      <c r="L51" s="158"/>
       <c r="M51" s="6">
         <f t="shared" si="4"/>
         <v>42464.999999999993</v>
@@ -6239,7 +6101,7 @@
         <v>45012.899999999994</v>
       </c>
     </row>
-    <row r="52" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="89"/>
       <c r="B52" s="89"/>
       <c r="C52" s="89"/>
@@ -6248,13 +6110,13 @@
         <f>SUM(E7:E51)</f>
         <v>99.999999999999986</v>
       </c>
-      <c r="F52" s="195">
+      <c r="F52" s="190">
         <f>SUM(F7:F51)</f>
-        <v>12800486.88956468</v>
-      </c>
-      <c r="G52" s="195">
+        <v>6694001.5113024348</v>
+      </c>
+      <c r="G52" s="190">
         <f>SUM(G7:G51)</f>
-        <v>13569486.916373972</v>
+        <v>6941937.3369510006</v>
       </c>
       <c r="H52" s="89"/>
       <c r="I52" s="89"/>
@@ -6266,170 +6128,175 @@
         <f>SUM(K7:K51)</f>
         <v>6924023.2495910004</v>
       </c>
-      <c r="L52" s="166">
+      <c r="L52" s="247">
         <f>SUM(L7:L51)</f>
-        <v>60000</v>
+        <v>1151834</v>
       </c>
       <c r="M52" s="91">
         <f>SUM(M7:M51)</f>
-        <v>6663166.6001417069</v>
+        <v>8276064.8013024349</v>
       </c>
       <c r="N52" s="90">
         <f>SUM(N7:N51)</f>
-        <v>7062956.5961502092</v>
+        <v>8772628.6893805824</v>
       </c>
       <c r="P52" s="134"/>
     </row>
-    <row r="53" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="K53" s="137">
         <f>K52-L1</f>
-        <v>385796.34959100094</v>
-      </c>
-    </row>
-    <row r="54" spans="1:16" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C54" s="231"/>
-      <c r="D54" s="231"/>
-      <c r="E54" s="231"/>
-      <c r="F54" s="231"/>
-      <c r="G54" s="231"/>
-      <c r="H54" s="231"/>
-      <c r="I54" s="231"/>
-      <c r="J54" s="231"/>
-      <c r="K54" s="231"/>
-      <c r="L54" s="231"/>
-      <c r="M54" s="231"/>
-      <c r="N54" s="231"/>
-    </row>
-    <row r="55" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
-      <c r="C55" s="231"/>
-      <c r="D55" s="231"/>
-      <c r="E55" s="231"/>
-      <c r="F55" s="231"/>
-      <c r="G55" s="231"/>
-      <c r="H55" s="231"/>
-      <c r="I55" s="231"/>
-      <c r="J55" s="231"/>
-      <c r="K55" s="231"/>
-      <c r="L55" s="231"/>
-      <c r="M55" s="231"/>
-      <c r="N55" s="231"/>
-    </row>
-    <row r="56" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="C56" s="161"/>
-      <c r="D56" s="161"/>
-      <c r="E56" s="161"/>
-      <c r="F56" s="161"/>
-      <c r="G56" s="161"/>
-      <c r="H56" s="161"/>
-      <c r="I56" s="161"/>
-      <c r="J56" s="161"/>
-      <c r="K56" s="161"/>
-      <c r="L56" s="161"/>
-      <c r="M56" s="161"/>
-      <c r="N56" s="161"/>
-    </row>
-    <row r="57" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="C57" s="231" t="s">
+        <v>-591652.79040900059</v>
+      </c>
+    </row>
+    <row r="54" spans="1:16" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C54" s="219"/>
+      <c r="D54" s="219"/>
+      <c r="E54" s="219"/>
+      <c r="F54" s="219"/>
+      <c r="G54" s="219"/>
+      <c r="H54" s="219"/>
+      <c r="I54" s="219"/>
+      <c r="J54" s="219"/>
+      <c r="K54" s="219"/>
+      <c r="L54" s="219"/>
+      <c r="M54" s="219"/>
+      <c r="N54" s="219"/>
+    </row>
+    <row r="55" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+      <c r="C55" s="219"/>
+      <c r="D55" s="219"/>
+      <c r="E55" s="219"/>
+      <c r="F55" s="219"/>
+      <c r="G55" s="219"/>
+      <c r="H55" s="219"/>
+      <c r="I55" s="219"/>
+      <c r="J55" s="219"/>
+      <c r="K55" s="219"/>
+      <c r="L55" s="219"/>
+      <c r="M55" s="219"/>
+      <c r="N55" s="219"/>
+    </row>
+    <row r="56" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="C56" s="160"/>
+      <c r="D56" s="160"/>
+      <c r="E56" s="160"/>
+      <c r="F56" s="160"/>
+      <c r="G56" s="160"/>
+      <c r="H56" s="160"/>
+      <c r="I56" s="160"/>
+      <c r="J56" s="160"/>
+      <c r="K56" s="160"/>
+      <c r="L56" s="160"/>
+      <c r="M56" s="160"/>
+      <c r="N56" s="160"/>
+    </row>
+    <row r="57" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="C57" s="219" t="s">
         <v>129</v>
       </c>
-      <c r="D57" s="231"/>
-      <c r="E57" s="231"/>
-      <c r="F57" s="231"/>
-      <c r="G57" s="231"/>
-      <c r="H57" s="231"/>
-      <c r="I57" s="231"/>
-      <c r="J57" s="231"/>
-      <c r="K57" s="231"/>
-      <c r="L57" s="231"/>
-      <c r="M57" s="231"/>
-      <c r="N57" s="231"/>
-    </row>
-    <row r="58" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="C58" s="231"/>
-      <c r="D58" s="231"/>
-      <c r="E58" s="231"/>
-      <c r="F58" s="231"/>
-      <c r="G58" s="231"/>
-      <c r="H58" s="231"/>
-      <c r="I58" s="231"/>
-      <c r="J58" s="231"/>
-      <c r="K58" s="231"/>
-      <c r="L58" s="231"/>
-      <c r="M58" s="231"/>
-      <c r="N58" s="231"/>
-    </row>
-    <row r="59" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="C59" s="231"/>
-      <c r="D59" s="231"/>
-      <c r="E59" s="231"/>
-      <c r="F59" s="231"/>
-      <c r="G59" s="231"/>
-      <c r="H59" s="231"/>
-      <c r="I59" s="231"/>
-      <c r="J59" s="231"/>
-      <c r="K59" s="231"/>
-      <c r="L59" s="231"/>
-      <c r="M59" s="231"/>
-      <c r="N59" s="231"/>
-    </row>
-    <row r="60" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="C60" s="231"/>
-      <c r="D60" s="231"/>
-      <c r="E60" s="231"/>
-      <c r="F60" s="231"/>
-      <c r="G60" s="231"/>
-      <c r="H60" s="231"/>
-      <c r="I60" s="231"/>
-      <c r="J60" s="231"/>
-      <c r="K60" s="231"/>
-      <c r="L60" s="231"/>
-      <c r="M60" s="231"/>
-      <c r="N60" s="231"/>
-    </row>
-    <row r="61" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="C61" s="231"/>
-      <c r="D61" s="231"/>
-      <c r="E61" s="231"/>
-      <c r="F61" s="231"/>
-      <c r="G61" s="231"/>
-      <c r="H61" s="231"/>
-      <c r="I61" s="231"/>
-      <c r="J61" s="231"/>
-      <c r="K61" s="231"/>
-      <c r="L61" s="231"/>
-      <c r="M61" s="231"/>
-      <c r="N61" s="231"/>
-    </row>
-    <row r="62" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="C62" s="231"/>
-      <c r="D62" s="231"/>
-      <c r="E62" s="231"/>
-      <c r="F62" s="231"/>
-      <c r="G62" s="231"/>
-      <c r="H62" s="231"/>
-      <c r="I62" s="231"/>
-      <c r="J62" s="231"/>
-      <c r="K62" s="231"/>
-      <c r="L62" s="231"/>
-      <c r="M62" s="231"/>
-      <c r="N62" s="231"/>
-    </row>
-    <row r="63" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="C63" s="231"/>
-      <c r="D63" s="231"/>
-      <c r="E63" s="231"/>
-      <c r="F63" s="231"/>
-      <c r="G63" s="231"/>
-      <c r="H63" s="231"/>
-      <c r="I63" s="231"/>
-      <c r="J63" s="231"/>
-      <c r="K63" s="231"/>
-      <c r="L63" s="231"/>
-      <c r="M63" s="231"/>
-      <c r="N63" s="231"/>
+      <c r="D57" s="219"/>
+      <c r="E57" s="219"/>
+      <c r="F57" s="219"/>
+      <c r="G57" s="219"/>
+      <c r="H57" s="219"/>
+      <c r="I57" s="219"/>
+      <c r="J57" s="219"/>
+      <c r="K57" s="219"/>
+      <c r="L57" s="219"/>
+      <c r="M57" s="219"/>
+      <c r="N57" s="219"/>
+    </row>
+    <row r="58" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="C58" s="219"/>
+      <c r="D58" s="219"/>
+      <c r="E58" s="219"/>
+      <c r="F58" s="219"/>
+      <c r="G58" s="219"/>
+      <c r="H58" s="219"/>
+      <c r="I58" s="219"/>
+      <c r="J58" s="219"/>
+      <c r="K58" s="219"/>
+      <c r="L58" s="219"/>
+      <c r="M58" s="219"/>
+      <c r="N58" s="219"/>
+    </row>
+    <row r="59" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="C59" s="219"/>
+      <c r="D59" s="219"/>
+      <c r="E59" s="219"/>
+      <c r="F59" s="219"/>
+      <c r="G59" s="219"/>
+      <c r="H59" s="219"/>
+      <c r="I59" s="219"/>
+      <c r="J59" s="219"/>
+      <c r="K59" s="219"/>
+      <c r="L59" s="219"/>
+      <c r="M59" s="219"/>
+      <c r="N59" s="219"/>
+    </row>
+    <row r="60" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="C60" s="219"/>
+      <c r="D60" s="219"/>
+      <c r="E60" s="219"/>
+      <c r="F60" s="219"/>
+      <c r="G60" s="219"/>
+      <c r="H60" s="219"/>
+      <c r="I60" s="219"/>
+      <c r="J60" s="219"/>
+      <c r="K60" s="219"/>
+      <c r="L60" s="219"/>
+      <c r="M60" s="219"/>
+      <c r="N60" s="219"/>
+    </row>
+    <row r="61" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="C61" s="219"/>
+      <c r="D61" s="219"/>
+      <c r="E61" s="219"/>
+      <c r="F61" s="219"/>
+      <c r="G61" s="219"/>
+      <c r="H61" s="219"/>
+      <c r="I61" s="219"/>
+      <c r="J61" s="219"/>
+      <c r="K61" s="219"/>
+      <c r="L61" s="219"/>
+      <c r="M61" s="219"/>
+      <c r="N61" s="219"/>
+    </row>
+    <row r="62" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="C62" s="219"/>
+      <c r="D62" s="219"/>
+      <c r="E62" s="219"/>
+      <c r="F62" s="219"/>
+      <c r="G62" s="219"/>
+      <c r="H62" s="219"/>
+      <c r="I62" s="219"/>
+      <c r="J62" s="219"/>
+      <c r="K62" s="219"/>
+      <c r="L62" s="219"/>
+      <c r="M62" s="219"/>
+      <c r="N62" s="219"/>
+    </row>
+    <row r="63" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="C63" s="219"/>
+      <c r="D63" s="219"/>
+      <c r="E63" s="219"/>
+      <c r="F63" s="219"/>
+      <c r="G63" s="219"/>
+      <c r="H63" s="219"/>
+      <c r="I63" s="219"/>
+      <c r="J63" s="219"/>
+      <c r="K63" s="219"/>
+      <c r="L63" s="219"/>
+      <c r="M63" s="219"/>
+      <c r="N63" s="219"/>
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="A5:A6"/>
+    <mergeCell ref="B5:B6"/>
+    <mergeCell ref="C5:C6"/>
+    <mergeCell ref="D5:D6"/>
+    <mergeCell ref="E5:E6"/>
     <mergeCell ref="F5:F6"/>
     <mergeCell ref="C57:N63"/>
     <mergeCell ref="C54:N55"/>
@@ -6442,11 +6309,6 @@
     <mergeCell ref="L5:L6"/>
     <mergeCell ref="M5:M6"/>
     <mergeCell ref="I5:I6"/>
-    <mergeCell ref="A5:A6"/>
-    <mergeCell ref="B5:B6"/>
-    <mergeCell ref="C5:C6"/>
-    <mergeCell ref="D5:D6"/>
-    <mergeCell ref="E5:E6"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="3" orientation="landscape" r:id="rId1"/>
@@ -6456,86 +6318,86 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{596D2FF5-218B-41A1-9BCB-F43114942886}">
   <dimension ref="C4:H25"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="4" max="4" width="14.88671875" customWidth="1"/>
+    <col min="4" max="4" width="14.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="4" spans="3:8" x14ac:dyDescent="0.3">
+    <row r="4" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C4" s="3" t="s">
         <v>143</v>
       </c>
     </row>
-    <row r="5" spans="3:8" x14ac:dyDescent="0.3">
+    <row r="5" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C5" t="s">
         <v>144</v>
       </c>
-      <c r="D5" s="183">
+      <c r="D5" s="181">
         <v>-447223.45918396302</v>
       </c>
     </row>
-    <row r="6" spans="3:8" x14ac:dyDescent="0.3">
+    <row r="6" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C6" t="s">
         <v>145</v>
       </c>
-      <c r="D6" s="183">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="D6" s="181">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C7" t="s">
         <v>146</v>
       </c>
-      <c r="D7" s="183">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="D7" s="181">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C8" t="s">
         <v>147</v>
       </c>
-      <c r="D8" s="183">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="D8" s="181">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C10" s="3" t="s">
         <v>149</v>
       </c>
     </row>
-    <row r="11" spans="3:8" x14ac:dyDescent="0.3">
+    <row r="11" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C11" t="s">
         <v>144</v>
       </c>
-      <c r="D11" s="183">
+      <c r="D11" s="181">
         <v>451182</v>
       </c>
     </row>
-    <row r="12" spans="3:8" x14ac:dyDescent="0.3">
+    <row r="12" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C12" t="s">
         <v>145</v>
       </c>
-      <c r="D12" s="183">
+      <c r="D12" s="181">
         <v>40606.380000000005</v>
       </c>
     </row>
-    <row r="13" spans="3:8" x14ac:dyDescent="0.3">
+    <row r="13" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C13" t="s">
         <v>146</v>
       </c>
-      <c r="D13" s="183">
+      <c r="D13" s="181">
         <v>41358.350000000006</v>
       </c>
     </row>
-    <row r="14" spans="3:8" x14ac:dyDescent="0.3">
+    <row r="14" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C14" t="s">
         <v>147</v>
       </c>
-      <c r="D14" s="183">
+      <c r="D14" s="181">
         <v>37598.5</v>
       </c>
     </row>
-    <row r="16" spans="3:8" x14ac:dyDescent="0.3">
+    <row r="16" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C16" s="3" t="s">
         <v>148</v>
       </c>
@@ -6545,67 +6407,67 @@
       <c r="G16" s="3"/>
       <c r="H16" s="3"/>
     </row>
-    <row r="17" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="17" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C17" t="s">
         <v>144</v>
       </c>
-      <c r="D17" s="183">
+      <c r="D17" s="181">
         <f>D11+D5</f>
         <v>3958.5408160369843</v>
       </c>
     </row>
-    <row r="18" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="18" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C18" t="s">
         <v>145</v>
       </c>
-      <c r="D18" s="183">
+      <c r="D18" s="181">
         <v>40606.380000000005</v>
       </c>
     </row>
-    <row r="19" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="19" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C19" t="s">
         <v>146</v>
       </c>
-      <c r="D19" s="183">
+      <c r="D19" s="181">
         <v>41358.350000000006</v>
       </c>
     </row>
-    <row r="20" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="20" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C20" t="s">
         <v>147</v>
       </c>
-      <c r="D20" s="183">
+      <c r="D20" s="181">
         <v>37598.5</v>
       </c>
     </row>
-    <row r="21" spans="3:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="3:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C21" t="s">
         <v>151</v>
       </c>
-      <c r="D21" s="183">
+      <c r="D21" s="181">
         <v>-25000</v>
       </c>
     </row>
-    <row r="22" spans="3:4" x14ac:dyDescent="0.3">
-      <c r="C22" s="242" t="s">
+    <row r="22" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C22" s="234" t="s">
         <v>150</v>
       </c>
-      <c r="D22" s="245">
+      <c r="D22" s="237">
         <f>SUM(D17:D21)</f>
         <v>98521.770816036995</v>
       </c>
     </row>
-    <row r="23" spans="3:4" x14ac:dyDescent="0.3">
-      <c r="C23" s="243"/>
-      <c r="D23" s="246"/>
-    </row>
-    <row r="24" spans="3:4" x14ac:dyDescent="0.3">
-      <c r="C24" s="243"/>
-      <c r="D24" s="246"/>
-    </row>
-    <row r="25" spans="3:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C25" s="244"/>
-      <c r="D25" s="247"/>
+    <row r="23" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C23" s="235"/>
+      <c r="D23" s="238"/>
+    </row>
+    <row r="24" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C24" s="235"/>
+      <c r="D24" s="238"/>
+    </row>
+    <row r="25" spans="3:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C25" s="236"/>
+      <c r="D25" s="239"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -6620,16 +6482,16 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:O33"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="8.44140625" customWidth="1"/>
-    <col min="2" max="2" width="17.6640625" customWidth="1"/>
-    <col min="3" max="3" width="8.88671875" customWidth="1"/>
-    <col min="12" max="12" width="13.6640625" customWidth="1"/>
-    <col min="13" max="13" width="11.44140625" hidden="1" customWidth="1"/>
+    <col min="1" max="1" width="8.42578125" customWidth="1"/>
+    <col min="2" max="2" width="17.7109375" customWidth="1"/>
+    <col min="3" max="3" width="8.85546875" customWidth="1"/>
+    <col min="12" max="12" width="13.7109375" customWidth="1"/>
+    <col min="13" max="13" width="11.42578125" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1" s="48"/>
       <c r="B1" s="49"/>
       <c r="C1" s="49"/>
@@ -6653,7 +6515,7 @@
       </c>
       <c r="O1" s="52"/>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" s="49"/>
       <c r="B2" s="51"/>
       <c r="C2" s="51"/>
@@ -6672,7 +6534,7 @@
       <c r="N2" s="49"/>
       <c r="O2" s="49"/>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3" s="49"/>
       <c r="B3" s="51"/>
       <c r="C3" s="51"/>
@@ -6695,7 +6557,7 @@
       </c>
       <c r="O3" s="54"/>
     </row>
-    <row r="4" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="49"/>
       <c r="B4" s="51"/>
       <c r="C4" s="51"/>
@@ -6716,11 +6578,11 @@
       <c r="N4" s="49"/>
       <c r="O4" s="49"/>
     </row>
-    <row r="5" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A5" s="248" t="s">
+    <row r="5" spans="1:15" ht="30" x14ac:dyDescent="0.25">
+      <c r="A5" s="240" t="s">
         <v>73</v>
       </c>
-      <c r="B5" s="248" t="s">
+      <c r="B5" s="240" t="s">
         <v>22</v>
       </c>
       <c r="C5" s="55" t="s">
@@ -6732,7 +6594,7 @@
       <c r="E5" s="35" t="s">
         <v>24</v>
       </c>
-      <c r="F5" s="248" t="s">
+      <c r="F5" s="240" t="s">
         <v>75</v>
       </c>
       <c r="G5" s="37" t="s">
@@ -6754,16 +6616,16 @@
         <v>29</v>
       </c>
       <c r="M5" s="41"/>
-      <c r="N5" s="248" t="s">
+      <c r="N5" s="240" t="s">
         <v>78</v>
       </c>
-      <c r="O5" s="248" t="s">
+      <c r="O5" s="240" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A6" s="249"/>
-      <c r="B6" s="249"/>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A6" s="241"/>
+      <c r="B6" s="241"/>
       <c r="C6" s="56" t="s">
         <v>80</v>
       </c>
@@ -6773,7 +6635,7 @@
       <c r="E6" s="42" t="s">
         <v>31</v>
       </c>
-      <c r="F6" s="249"/>
+      <c r="F6" s="241"/>
       <c r="G6" s="44" t="s">
         <v>81</v>
       </c>
@@ -6793,10 +6655,10 @@
         <v>84</v>
       </c>
       <c r="M6" s="47"/>
-      <c r="N6" s="249"/>
-      <c r="O6" s="249"/>
-    </row>
-    <row r="7" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N6" s="241"/>
+      <c r="O6" s="241"/>
+    </row>
+    <row r="7" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="15">
         <v>1</v>
       </c>
@@ -6842,7 +6704,7 @@
         <v>12304.692124880721</v>
       </c>
     </row>
-    <row r="8" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="15">
         <v>2</v>
       </c>
@@ -6888,7 +6750,7 @@
         <v>12569.682901267399</v>
       </c>
     </row>
-    <row r="9" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="15">
         <v>3</v>
       </c>
@@ -6934,7 +6796,7 @@
         <v>9919.7751374005984</v>
       </c>
     </row>
-    <row r="10" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="15">
         <v>4</v>
       </c>
@@ -6980,7 +6842,7 @@
         <v>14159.627559587479</v>
       </c>
     </row>
-    <row r="11" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="15">
         <v>5</v>
       </c>
@@ -7026,7 +6888,7 @@
         <v>12304.692124880721</v>
       </c>
     </row>
-    <row r="12" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="15">
         <v>6</v>
       </c>
@@ -7072,7 +6934,7 @@
         <v>11244.729019334</v>
       </c>
     </row>
-    <row r="13" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="15">
         <v>7</v>
       </c>
@@ -7118,7 +6980,7 @@
         <v>11244.729019334</v>
       </c>
     </row>
-    <row r="14" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="15">
         <v>8</v>
       </c>
@@ -7164,7 +7026,7 @@
         <v>10979.738242947318</v>
       </c>
     </row>
-    <row r="15" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="15">
         <v>9</v>
       </c>
@@ -7210,7 +7072,7 @@
         <v>10979.738242947318</v>
       </c>
     </row>
-    <row r="16" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="15">
         <v>10</v>
       </c>
@@ -7256,7 +7118,7 @@
         <v>13629.64600681412</v>
       </c>
     </row>
-    <row r="17" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="15">
         <v>11</v>
       </c>
@@ -7302,7 +7164,7 @@
         <v>13099.66445404076</v>
       </c>
     </row>
-    <row r="18" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="15">
         <v>12</v>
       </c>
@@ -7348,7 +7210,7 @@
         <v>12304.692124880721</v>
       </c>
     </row>
-    <row r="19" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="15">
         <v>13</v>
       </c>
@@ -7394,7 +7256,7 @@
         <v>12569.682901267399</v>
       </c>
     </row>
-    <row r="20" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="15">
         <v>14</v>
       </c>
@@ -7440,7 +7302,7 @@
         <v>9919.7751374005984</v>
       </c>
     </row>
-    <row r="21" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="15">
         <v>15</v>
       </c>
@@ -7486,7 +7348,7 @@
         <v>14159.627559587479</v>
       </c>
     </row>
-    <row r="22" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="15">
         <v>16</v>
       </c>
@@ -7532,7 +7394,7 @@
         <v>12304.692124880721</v>
       </c>
     </row>
-    <row r="23" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="15">
         <v>17</v>
       </c>
@@ -7578,7 +7440,7 @@
         <v>11244.729019334</v>
       </c>
     </row>
-    <row r="24" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="15">
         <v>18</v>
       </c>
@@ -7624,7 +7486,7 @@
         <v>11244.729019334</v>
       </c>
     </row>
-    <row r="25" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="15">
         <v>19</v>
       </c>
@@ -7670,7 +7532,7 @@
         <v>10979.738242947318</v>
       </c>
     </row>
-    <row r="26" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="15">
         <v>20</v>
       </c>
@@ -7716,7 +7578,7 @@
         <v>10979.738242947318</v>
       </c>
     </row>
-    <row r="27" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="15">
         <v>21</v>
       </c>
@@ -7762,7 +7624,7 @@
         <v>13629.64600681412</v>
       </c>
     </row>
-    <row r="28" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="15">
         <v>22</v>
       </c>
@@ -7808,7 +7670,7 @@
         <v>13099.66445404076</v>
       </c>
     </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A29" s="15"/>
       <c r="B29" s="34"/>
       <c r="C29" s="34"/>
@@ -7825,7 +7687,7 @@
       <c r="N29" s="6"/>
       <c r="O29" s="6"/>
     </row>
-    <row r="30" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A30" s="13"/>
       <c r="B30" s="14"/>
       <c r="C30" s="57">
@@ -7866,7 +7728,7 @@
         <v>264873.42966686888</v>
       </c>
     </row>
-    <row r="33" spans="5:6" x14ac:dyDescent="0.3">
+    <row r="33" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E33" s="33"/>
       <c r="F33" s="33"/>
     </row>

--- a/BELGRANO 1646/Octubre/Octubre-BLG1646.xlsx
+++ b/BELGRANO 1646/Octubre/Octubre-BLG1646.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\RC CONSORCIO 2025\BELGRANO 1646\Octubre\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2BD8B6A-6E5B-466C-99CF-6CEA2744A355}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33C4985F-A88B-42E5-AB8D-2C1151D8EE5B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="266" uniqueCount="173">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="266" uniqueCount="174">
   <si>
     <t>consorciobelgrano1640@gmail.com</t>
   </si>
@@ -582,6 +582,10 @@
   <si>
     <t>Envios cartas documento</t>
   </si>
+  <si>
+    <t>Las expensas extraordinarias ascendieron a un total de $2.900.000. Sin embargo, considerando que pasar de un prorrateo de $450.000 a dicho monto implicaría un incremento significativo en el valor final de las expensas, se resolvió distribuir este importe en tres cuotas.
+Por lo tanto, en el presente período se prorratea una tercera parte del monto total correspondiente a las extraordinarias, con el fin de mantener un equilibrio en los valores a abonar.</t>
+  </si>
 </sst>
 </file>
 
@@ -598,7 +602,7 @@
     <numFmt numFmtId="167" formatCode="_-&quot;$&quot;\ * #,##0_-;\-&quot;$&quot;\ * #,##0_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="168" formatCode="_-[$$-2C0A]\ * #,##0.00_-;\-[$$-2C0A]\ * #,##0.00_-;_-[$$-2C0A]\ * &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="25" x14ac:knownFonts="1">
+  <fonts count="24" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -720,13 +724,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="8"/>
-      <color theme="4" tint="0.59999389629810485"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color theme="4" tint="0.59999389629810485"/>
       <name val="Calibri"/>
@@ -772,7 +769,6 @@
     </font>
     <font>
       <sz val="9"/>
-      <color rgb="FFFF0000"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -1316,7 +1312,7 @@
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="248">
+  <cellXfs count="259">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="34" xfId="0" applyBorder="1"/>
@@ -1326,7 +1322,6 @@
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="8" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1"/>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
@@ -1491,18 +1486,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="1" fontId="17" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="18" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="44" fontId="6" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="167" fontId="0" fillId="9" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="6" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="12" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="167" fontId="15" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="19" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="18" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="6" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1519,18 +1509,13 @@
     <xf numFmtId="44" fontId="2" fillId="6" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="2" fillId="7" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="6" fontId="6" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="44" fontId="6" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="6" fontId="6" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="44" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="44" fontId="14" fillId="6" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="2" fillId="6" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="44" fontId="20" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="44" fontId="19" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="16" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -1548,7 +1533,7 @@
     <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="21" fillId="3" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="20" fillId="3" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1569,7 +1554,7 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="11" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="20" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="19" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="11" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
@@ -1586,7 +1571,8 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="167" fontId="4" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="20" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="4" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="15" fillId="9" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1668,15 +1654,21 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="31" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="33" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="44" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="6" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="35" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1692,27 +1684,15 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="37" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="5" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="5" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="5" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="5" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="5" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="31" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="33" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="11" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1737,12 +1717,59 @@
     <xf numFmtId="0" fontId="2" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="44" fontId="20" fillId="3" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="6" fillId="11" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="4" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="6" fontId="24" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="21" fillId="3" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="15" fillId="9" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="6" fontId="23" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="9" fillId="3" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="31" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="32" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="33" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="34" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="38" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="31" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="0" fillId="5" borderId="29" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="6" fontId="0" fillId="5" borderId="29" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="44" fontId="6" fillId="5" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="33" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="6" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="6" fontId="6" fillId="5" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="6" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="6" fontId="6" fillId="5" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="38" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="21" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="6" fontId="0" fillId="5" borderId="21" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="5" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Millares" xfId="3" builtinId="3"/>
@@ -2127,7 +2154,7 @@
   <sheetData>
     <row r="1" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="8"/>
-      <c r="B1" s="97" t="s">
+      <c r="B1" s="96" t="s">
         <v>118</v>
       </c>
       <c r="C1" s="8"/>
@@ -2135,305 +2162,305 @@
       <c r="E1" s="8"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="64"/>
-      <c r="B2" s="65" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="65"/>
-      <c r="D2" s="65"/>
-      <c r="E2" s="66"/>
+      <c r="A2" s="63"/>
+      <c r="B2" s="64" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="64"/>
+      <c r="D2" s="64"/>
+      <c r="E2" s="65"/>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" s="67"/>
-      <c r="B3" s="68" t="s">
+      <c r="A3" s="66"/>
+      <c r="B3" s="67" t="s">
         <v>88</v>
       </c>
-      <c r="C3" s="68"/>
-      <c r="D3" s="68"/>
-      <c r="E3" s="69"/>
+      <c r="C3" s="67"/>
+      <c r="D3" s="67"/>
+      <c r="E3" s="68"/>
     </row>
     <row r="4" spans="1:5" ht="33.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="67"/>
-      <c r="B4" s="68" t="s">
+      <c r="A4" s="66"/>
+      <c r="B4" s="67" t="s">
         <v>89</v>
       </c>
-      <c r="C4" s="68"/>
-      <c r="D4" s="68"/>
-      <c r="E4" s="69"/>
+      <c r="C4" s="67"/>
+      <c r="D4" s="67"/>
+      <c r="E4" s="68"/>
     </row>
     <row r="5" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="70" t="s">
+      <c r="A5" s="69" t="s">
         <v>1</v>
       </c>
-      <c r="B5" s="71" t="s">
+      <c r="B5" s="70" t="s">
         <v>157</v>
       </c>
-      <c r="C5" s="71" t="s">
+      <c r="C5" s="70" t="s">
         <v>153</v>
       </c>
-      <c r="D5" s="71"/>
-      <c r="E5" s="72"/>
+      <c r="D5" s="70"/>
+      <c r="E5" s="71"/>
     </row>
     <row r="6" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="67" t="s">
+      <c r="A6" s="66" t="s">
         <v>99</v>
       </c>
-      <c r="B6" s="68"/>
-      <c r="C6" s="68"/>
-      <c r="D6" s="68"/>
-      <c r="E6" s="69"/>
+      <c r="B6" s="67"/>
+      <c r="C6" s="67"/>
+      <c r="D6" s="67"/>
+      <c r="E6" s="68"/>
     </row>
     <row r="7" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="70" t="s">
+      <c r="A7" s="69" t="s">
         <v>98</v>
       </c>
-      <c r="B7" s="71"/>
-      <c r="C7" s="71"/>
-      <c r="D7" s="71"/>
-      <c r="E7" s="72"/>
+      <c r="B7" s="70"/>
+      <c r="C7" s="70"/>
+      <c r="D7" s="70"/>
+      <c r="E7" s="71"/>
     </row>
     <row r="9" spans="1:5" hidden="1" x14ac:dyDescent="0.25"/>
     <row r="10" spans="1:5" hidden="1" x14ac:dyDescent="0.25"/>
     <row r="11" spans="1:5" hidden="1" x14ac:dyDescent="0.25"/>
     <row r="12" spans="1:5" hidden="1" x14ac:dyDescent="0.25"/>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B14" s="194" t="s">
+      <c r="B14" s="188" t="s">
         <v>134</v>
       </c>
-      <c r="C14" s="195"/>
-      <c r="D14" s="196"/>
+      <c r="C14" s="189"/>
+      <c r="D14" s="190"/>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B15" s="197"/>
-      <c r="C15" s="198"/>
-      <c r="D15" s="199"/>
+      <c r="B15" s="191"/>
+      <c r="C15" s="192"/>
+      <c r="D15" s="193"/>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B16" s="197"/>
-      <c r="C16" s="198"/>
-      <c r="D16" s="199"/>
+      <c r="B16" s="191"/>
+      <c r="C16" s="192"/>
+      <c r="D16" s="193"/>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B17" s="200"/>
-      <c r="C17" s="201"/>
-      <c r="D17" s="202"/>
+      <c r="B17" s="194"/>
+      <c r="C17" s="195"/>
+      <c r="D17" s="196"/>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" s="3"/>
     </row>
     <row r="20" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="21" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="61" t="s">
+      <c r="A21" s="60" t="s">
         <v>86</v>
       </c>
-      <c r="B21" s="62"/>
-      <c r="C21" s="63"/>
-      <c r="D21" s="59"/>
-      <c r="E21" s="184" t="s">
+      <c r="B21" s="61"/>
+      <c r="C21" s="62"/>
+      <c r="D21" s="58"/>
+      <c r="E21" s="177" t="s">
         <v>121</v>
       </c>
-      <c r="F21" s="185" t="s">
+      <c r="F21" s="178" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A22" s="120" t="s">
+      <c r="A22" s="119" t="s">
         <v>142</v>
       </c>
       <c r="B22" s="7" t="s">
         <v>158</v>
       </c>
       <c r="C22" s="7"/>
-      <c r="D22" s="129"/>
-      <c r="E22" s="183"/>
-      <c r="F22" s="183"/>
+      <c r="D22" s="125"/>
+      <c r="E22" s="176"/>
+      <c r="F22" s="176"/>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A23" s="120" t="s">
+      <c r="A23" s="119" t="s">
         <v>126</v>
       </c>
       <c r="B23" s="7"/>
       <c r="C23" s="7"/>
-      <c r="D23" s="242">
+      <c r="D23" s="163">
         <v>1376395.8</v>
       </c>
-      <c r="E23" s="133">
+      <c r="E23" s="129">
         <f>D23*91.91%</f>
         <v>1265045.3797799998</v>
       </c>
-      <c r="F23" s="133">
+      <c r="F23" s="129">
         <f>D23*8.09%</f>
         <v>111350.42022</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A24" s="120" t="s">
+      <c r="A24" s="119" t="s">
         <v>2</v>
       </c>
       <c r="B24" s="7"/>
       <c r="C24" s="7"/>
-      <c r="D24" s="242">
+      <c r="D24" s="163">
         <v>-299366.09000000003</v>
       </c>
-      <c r="E24" s="133">
+      <c r="E24" s="129">
         <f t="shared" ref="E24:E25" si="0">D24*91.91%</f>
         <v>-275147.37331900001</v>
       </c>
-      <c r="F24" s="133">
+      <c r="F24" s="129">
         <f t="shared" ref="F24:F25" si="1">D24*8.09%</f>
         <v>-24218.716681000002</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A25" s="120" t="s">
+      <c r="A25" s="119" t="s">
         <v>112</v>
       </c>
       <c r="B25" s="7"/>
       <c r="C25" s="7"/>
-      <c r="D25" s="242">
+      <c r="D25" s="163">
         <v>0.28999999999999998</v>
       </c>
-      <c r="E25" s="133">
+      <c r="E25" s="129">
         <f t="shared" si="0"/>
         <v>0.26653899999999997</v>
       </c>
-      <c r="F25" s="133">
+      <c r="F25" s="129">
         <f t="shared" si="1"/>
         <v>2.3460999999999999E-2</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A26" s="120"/>
+      <c r="A26" s="119"/>
       <c r="B26" s="7"/>
       <c r="C26" s="7"/>
-      <c r="D26" s="170"/>
-      <c r="E26" s="133"/>
+      <c r="D26" s="163"/>
+      <c r="E26" s="129"/>
       <c r="F26" s="7"/>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A27" s="95" t="s">
+      <c r="A27" s="94" t="s">
         <v>3</v>
       </c>
-      <c r="B27" s="95"/>
-      <c r="C27" s="95"/>
-      <c r="D27" s="107">
+      <c r="B27" s="94"/>
+      <c r="C27" s="94"/>
+      <c r="D27" s="106">
         <f>SUM(D23:D26)</f>
         <v>1077030</v>
       </c>
-      <c r="E27" s="107">
+      <c r="E27" s="106">
         <f>SUM(E23:E26)</f>
         <v>989898.27299999981</v>
       </c>
-      <c r="F27" s="107">
+      <c r="F27" s="106">
         <f>SUM(F23:F26)</f>
         <v>87131.726999999999</v>
       </c>
-      <c r="G27" s="108">
+      <c r="G27" s="107">
         <f>E27+F27</f>
         <v>1077029.9999999998</v>
       </c>
-      <c r="H27" s="146" t="str">
+      <c r="H27" s="142" t="str">
         <f>IF(D27=G27, "", "Error")</f>
         <v/>
       </c>
     </row>
     <row r="28" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="94" t="s">
+      <c r="A28" s="93" t="s">
         <v>109</v>
       </c>
       <c r="B28" s="7"/>
       <c r="C28" s="7"/>
-      <c r="D28" s="171">
-        <v>0</v>
-      </c>
-      <c r="E28" s="133">
+      <c r="D28" s="164">
+        <v>0</v>
+      </c>
+      <c r="E28" s="129">
         <f>D28*91.91%</f>
         <v>0</v>
       </c>
-      <c r="F28" s="133">
+      <c r="F28" s="129">
         <f>D28*8.09%</f>
         <v>0</v>
       </c>
-      <c r="H28" s="146"/>
+      <c r="H28" s="142"/>
     </row>
     <row r="29" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="94"/>
+      <c r="A29" s="93"/>
       <c r="B29" s="7"/>
       <c r="C29" s="7"/>
-      <c r="D29" s="170">
-        <v>0</v>
-      </c>
-      <c r="E29" s="133">
+      <c r="D29" s="163">
+        <v>0</v>
+      </c>
+      <c r="E29" s="129">
         <f>D29*91.91%</f>
         <v>0</v>
       </c>
-      <c r="F29" s="133">
+      <c r="F29" s="129">
         <f>D29*8.09%</f>
         <v>0</v>
       </c>
-      <c r="H29" s="146"/>
+      <c r="H29" s="142"/>
     </row>
     <row r="30" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="94"/>
+      <c r="A30" s="93"/>
       <c r="B30" s="7"/>
       <c r="C30" s="7"/>
-      <c r="D30" s="170"/>
+      <c r="D30" s="163"/>
       <c r="E30" s="7"/>
       <c r="F30" s="7"/>
-      <c r="H30" s="146"/>
+      <c r="H30" s="142"/>
     </row>
     <row r="31" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="94"/>
+      <c r="A31" s="93"/>
       <c r="B31" s="7"/>
       <c r="C31" s="7"/>
-      <c r="D31" s="170"/>
+      <c r="D31" s="163"/>
       <c r="E31" s="7"/>
       <c r="F31" s="7"/>
-      <c r="H31" s="146"/>
+      <c r="H31" s="142"/>
     </row>
     <row r="32" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="95" t="s">
+      <c r="A32" s="94" t="s">
         <v>117</v>
       </c>
-      <c r="B32" s="95"/>
-      <c r="C32" s="95"/>
-      <c r="D32" s="107">
+      <c r="B32" s="94"/>
+      <c r="C32" s="94"/>
+      <c r="D32" s="106">
         <f>SUM(D28:D30)</f>
         <v>0</v>
       </c>
-      <c r="E32" s="107">
+      <c r="E32" s="106">
         <f t="shared" ref="E32:F32" si="2">SUM(E28:E30)</f>
         <v>0</v>
       </c>
-      <c r="F32" s="107">
+      <c r="F32" s="106">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="G32" s="108">
+      <c r="G32" s="107">
         <f>E32+F32</f>
         <v>0</v>
       </c>
-      <c r="H32" s="146" t="str">
+      <c r="H32" s="142" t="str">
         <f>IF(D32=G32, "", "Error")</f>
         <v/>
       </c>
     </row>
     <row r="33" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="94" t="s">
+      <c r="A33" s="93" t="s">
         <v>109</v>
       </c>
       <c r="B33" s="7"/>
       <c r="C33" s="7"/>
-      <c r="D33" s="171"/>
-      <c r="E33" s="133">
+      <c r="D33" s="164"/>
+      <c r="E33" s="129">
         <f>D33*91.91%</f>
         <v>0</v>
       </c>
-      <c r="F33" s="133">
+      <c r="F33" s="129">
         <f>D33*8.09%</f>
         <v>0</v>
       </c>
-      <c r="H33" s="146"/>
+      <c r="H33" s="142"/>
     </row>
     <row r="34" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A34" s="7" t="s">
@@ -2441,264 +2468,264 @@
       </c>
       <c r="B34" s="7"/>
       <c r="C34" s="7"/>
-      <c r="D34" s="170"/>
-      <c r="E34" s="133">
+      <c r="D34" s="163"/>
+      <c r="E34" s="129">
         <f t="shared" ref="E34:E35" si="3">D34*91.91%</f>
         <v>0</v>
       </c>
-      <c r="F34" s="133">
+      <c r="F34" s="129">
         <f t="shared" ref="F34:F35" si="4">D34*8.09%</f>
         <v>0</v>
       </c>
-      <c r="H34" s="146"/>
+      <c r="H34" s="142"/>
     </row>
     <row r="35" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="94" t="s">
+      <c r="A35" s="93" t="s">
         <v>2</v>
       </c>
       <c r="B35" s="7"/>
       <c r="C35" s="7"/>
-      <c r="D35" s="170"/>
-      <c r="E35" s="133">
+      <c r="D35" s="163"/>
+      <c r="E35" s="129">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="F35" s="133">
+      <c r="F35" s="129">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="H35" s="146"/>
+      <c r="H35" s="142"/>
     </row>
     <row r="36" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="95" t="s">
+      <c r="A36" s="94" t="s">
         <v>110</v>
       </c>
-      <c r="B36" s="95"/>
-      <c r="C36" s="95"/>
-      <c r="D36" s="107">
+      <c r="B36" s="94"/>
+      <c r="C36" s="94"/>
+      <c r="D36" s="106">
         <f>SUM(D29:D35)</f>
         <v>0</v>
       </c>
-      <c r="E36" s="107">
+      <c r="E36" s="106">
         <f t="shared" ref="E36" si="5">SUM(E29:E35)</f>
         <v>0</v>
       </c>
-      <c r="F36" s="118">
+      <c r="F36" s="117">
         <f>E36*8.09%</f>
         <v>0</v>
       </c>
-      <c r="H36" s="146"/>
+      <c r="H36" s="142"/>
     </row>
     <row r="37" spans="1:8" ht="0.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="128"/>
-      <c r="B37" s="98"/>
-      <c r="C37" s="98"/>
-      <c r="D37" s="170"/>
-      <c r="E37" s="119"/>
-      <c r="F37" s="119"/>
-      <c r="H37" s="146"/>
+      <c r="A37" s="124"/>
+      <c r="B37" s="97"/>
+      <c r="C37" s="97"/>
+      <c r="D37" s="163"/>
+      <c r="E37" s="118"/>
+      <c r="F37" s="118"/>
+      <c r="H37" s="142"/>
     </row>
     <row r="38" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="128"/>
-      <c r="B38" s="98"/>
-      <c r="C38" s="98"/>
-      <c r="D38" s="170"/>
-      <c r="E38" s="119"/>
-      <c r="F38" s="119"/>
-      <c r="H38" s="146"/>
+      <c r="A38" s="124"/>
+      <c r="B38" s="97"/>
+      <c r="C38" s="97"/>
+      <c r="D38" s="163"/>
+      <c r="E38" s="118"/>
+      <c r="F38" s="118"/>
+      <c r="H38" s="142"/>
     </row>
     <row r="39" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="98"/>
-      <c r="B39" s="98"/>
-      <c r="C39" s="110"/>
-      <c r="D39" s="170"/>
-      <c r="E39" s="119"/>
-      <c r="F39" s="119"/>
-      <c r="H39" s="146"/>
+      <c r="A39" s="97"/>
+      <c r="B39" s="97"/>
+      <c r="C39" s="109"/>
+      <c r="D39" s="163"/>
+      <c r="E39" s="118"/>
+      <c r="F39" s="118"/>
+      <c r="H39" s="142"/>
     </row>
     <row r="40" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="95" t="s">
+      <c r="A40" s="94" t="s">
         <v>117</v>
       </c>
-      <c r="B40" s="95"/>
-      <c r="C40" s="95"/>
-      <c r="D40" s="107"/>
-      <c r="E40" s="111">
+      <c r="B40" s="94"/>
+      <c r="C40" s="94"/>
+      <c r="D40" s="106"/>
+      <c r="E40" s="110">
         <f>SUM(D37:D39)</f>
         <v>0</v>
       </c>
-      <c r="F40" s="109">
+      <c r="F40" s="108">
         <f>(D37)*8.09%</f>
         <v>0</v>
       </c>
-      <c r="H40" s="146"/>
+      <c r="H40" s="142"/>
     </row>
     <row r="41" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="94"/>
+      <c r="A41" s="93"/>
       <c r="B41" s="7"/>
       <c r="C41" s="7"/>
-      <c r="D41" s="112"/>
-      <c r="E41" s="133">
+      <c r="D41" s="111"/>
+      <c r="E41" s="129">
         <f>D41*91.91%</f>
         <v>0</v>
       </c>
-      <c r="F41" s="133">
+      <c r="F41" s="129">
         <f>D41*8.09%</f>
         <v>0</v>
       </c>
-      <c r="H41" s="146"/>
+      <c r="H41" s="142"/>
     </row>
     <row r="42" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="94"/>
+      <c r="A42" s="93"/>
       <c r="B42" s="7"/>
       <c r="C42" s="7"/>
-      <c r="D42" s="112"/>
-      <c r="E42" s="133">
+      <c r="D42" s="111"/>
+      <c r="E42" s="129">
         <f>D42*91.91%</f>
         <v>0</v>
       </c>
-      <c r="F42" s="133">
+      <c r="F42" s="129">
         <f>D42*8.09%</f>
         <v>0</v>
       </c>
-      <c r="H42" s="146"/>
+      <c r="H42" s="142"/>
     </row>
     <row r="43" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="94"/>
+      <c r="A43" s="93"/>
       <c r="B43" s="7"/>
       <c r="C43" s="7"/>
-      <c r="D43" s="173"/>
-      <c r="E43" s="133">
+      <c r="D43" s="166"/>
+      <c r="E43" s="129">
         <f>D43*91.91%</f>
         <v>0</v>
       </c>
-      <c r="F43" s="133">
+      <c r="F43" s="129">
         <f>D43*8.09%</f>
         <v>0</v>
       </c>
-      <c r="H43" s="146"/>
+      <c r="H43" s="142"/>
     </row>
     <row r="44" spans="1:8" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="95" t="s">
+      <c r="A44" s="94" t="s">
         <v>127</v>
       </c>
-      <c r="B44" s="95"/>
-      <c r="C44" s="95"/>
-      <c r="D44" s="107">
+      <c r="B44" s="94"/>
+      <c r="C44" s="94"/>
+      <c r="D44" s="106">
         <f>SUM(D41:D43)</f>
         <v>0</v>
       </c>
-      <c r="E44" s="153">
+      <c r="E44" s="146">
         <f>SUM(E41:E43)</f>
         <v>0</v>
       </c>
-      <c r="F44" s="161">
+      <c r="F44" s="154">
         <f>SUM(F41:F43)</f>
         <v>0</v>
       </c>
-      <c r="G44" s="108">
+      <c r="G44" s="107">
         <f>E44+F44</f>
         <v>0</v>
       </c>
-      <c r="H44" s="146"/>
+      <c r="H44" s="142"/>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A45" s="94" t="s">
+      <c r="A45" s="93" t="s">
         <v>4</v>
       </c>
       <c r="B45" s="7"/>
       <c r="C45" s="7"/>
-      <c r="D45" s="173"/>
-      <c r="E45" s="113"/>
-      <c r="F45" s="100"/>
-      <c r="H45" s="146"/>
+      <c r="D45" s="166"/>
+      <c r="E45" s="112"/>
+      <c r="F45" s="99"/>
+      <c r="H45" s="142"/>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A46" s="94" t="s">
+      <c r="A46" s="93" t="s">
         <v>162</v>
       </c>
       <c r="B46" s="7"/>
-      <c r="C46" s="98"/>
-      <c r="D46" s="180">
+      <c r="C46" s="97"/>
+      <c r="D46" s="111">
         <v>5020</v>
       </c>
-      <c r="E46" s="133">
+      <c r="E46" s="129">
         <f>D46*91.91%</f>
         <v>4613.8819999999996</v>
       </c>
-      <c r="F46" s="133">
+      <c r="F46" s="129">
         <f>D46*8.09%</f>
         <v>406.11799999999999</v>
       </c>
-      <c r="H46" s="146"/>
+      <c r="H46" s="142"/>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A47" s="94" t="s">
+      <c r="A47" s="93" t="s">
         <v>5</v>
       </c>
       <c r="B47" s="7" t="s">
         <v>164</v>
       </c>
       <c r="C47" s="7"/>
-      <c r="D47" s="180">
+      <c r="D47" s="111">
         <f>113583.37+6781.8+61036.17</f>
         <v>181401.34</v>
       </c>
-      <c r="E47" s="133">
+      <c r="E47" s="129">
         <f>D47*91.91%</f>
         <v>166725.97159399997</v>
       </c>
-      <c r="F47" s="133">
+      <c r="F47" s="129">
         <f>D47*8.09%</f>
         <v>14675.368406</v>
       </c>
-      <c r="H47" s="146"/>
+      <c r="H47" s="142"/>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A48" s="94" t="s">
+      <c r="A48" s="93" t="s">
         <v>135</v>
       </c>
-      <c r="B48" s="98" t="s">
+      <c r="B48" s="97" t="s">
         <v>163</v>
       </c>
       <c r="C48" s="7"/>
-      <c r="D48" s="180">
+      <c r="D48" s="111">
         <f>600931.76+14011.05</f>
         <v>614942.81000000006</v>
       </c>
-      <c r="E48" s="133">
+      <c r="E48" s="129">
         <f>D48*91.91%</f>
         <v>565193.93667099997</v>
       </c>
-      <c r="F48" s="133">
+      <c r="F48" s="129">
         <f>D48*8.09%</f>
         <v>49748.873329000002</v>
       </c>
-      <c r="H48" s="146"/>
+      <c r="H48" s="142"/>
     </row>
     <row r="49" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A49" s="95" t="s">
+      <c r="A49" s="94" t="s">
         <v>6</v>
       </c>
-      <c r="B49" s="96"/>
-      <c r="C49" s="96"/>
-      <c r="D49" s="107">
+      <c r="B49" s="95"/>
+      <c r="C49" s="95"/>
+      <c r="D49" s="106">
         <f>SUM(D46:D48)</f>
         <v>801364.15</v>
       </c>
-      <c r="E49" s="107">
+      <c r="E49" s="106">
         <f t="shared" ref="E49:F49" si="6">SUM(E46:E48)</f>
         <v>736533.79026499996</v>
       </c>
-      <c r="F49" s="107">
+      <c r="F49" s="106">
         <f t="shared" si="6"/>
         <v>64830.359735000005</v>
       </c>
-      <c r="G49" s="108">
+      <c r="G49" s="107">
         <f>E49+F49</f>
         <v>801364.14999999991</v>
       </c>
-      <c r="H49" s="146" t="str">
+      <c r="H49" s="142" t="str">
         <f>IF(D49=G49, "", "Error")</f>
         <v/>
       </c>
@@ -2709,330 +2736,330 @@
       </c>
       <c r="B50" s="7"/>
       <c r="C50" s="7"/>
-      <c r="D50" s="173"/>
-      <c r="E50" s="114"/>
+      <c r="D50" s="166"/>
+      <c r="E50" s="113"/>
       <c r="F50" s="7"/>
-      <c r="H50" s="146"/>
+      <c r="H50" s="142"/>
     </row>
     <row r="51" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A51" s="177" t="s">
+      <c r="A51" s="170" t="s">
         <v>155</v>
       </c>
-      <c r="B51" s="166"/>
-      <c r="C51" s="167"/>
-      <c r="D51" s="191">
+      <c r="B51" s="159"/>
+      <c r="C51" s="160"/>
+      <c r="D51" s="166">
         <v>39000</v>
       </c>
-      <c r="E51" s="145">
+      <c r="E51" s="141">
         <f>D51</f>
         <v>39000</v>
       </c>
       <c r="F51" s="7"/>
-      <c r="G51" s="108">
+      <c r="G51" s="107">
         <f>D51</f>
         <v>39000</v>
       </c>
-      <c r="H51" s="155">
+      <c r="H51" s="148">
         <f>E51+F51</f>
         <v>39000</v>
       </c>
-      <c r="I51" s="168"/>
-      <c r="J51" s="168"/>
+      <c r="I51" s="161"/>
+      <c r="J51" s="161"/>
     </row>
     <row r="52" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="177" t="s">
+      <c r="A52" s="170" t="s">
         <v>138</v>
       </c>
-      <c r="B52" s="166"/>
-      <c r="C52" s="167"/>
-      <c r="D52" s="180">
+      <c r="B52" s="159"/>
+      <c r="C52" s="160"/>
+      <c r="D52" s="111">
         <v>372000</v>
       </c>
-      <c r="E52" s="145">
+      <c r="E52" s="141">
         <f>D52</f>
         <v>372000</v>
       </c>
       <c r="F52" s="7"/>
-      <c r="G52" s="108">
+      <c r="G52" s="107">
         <f>D52</f>
         <v>372000</v>
       </c>
-      <c r="H52" s="155">
+      <c r="H52" s="148">
         <f>E52+F52</f>
         <v>372000</v>
       </c>
-      <c r="I52" s="168">
+      <c r="I52" s="161">
         <f>H52-D52</f>
         <v>0</v>
       </c>
-      <c r="J52" s="168"/>
+      <c r="J52" s="161"/>
     </row>
     <row r="53" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A53" s="120" t="s">
+      <c r="A53" s="119" t="s">
         <v>8</v>
       </c>
-      <c r="B53" s="156"/>
+      <c r="B53" s="149"/>
       <c r="C53" s="7"/>
-      <c r="D53" s="112"/>
-      <c r="E53" s="145">
+      <c r="D53" s="111"/>
+      <c r="E53" s="141">
         <f t="shared" ref="E53:E58" si="7">D53*91.91%</f>
         <v>0</v>
       </c>
-      <c r="F53" s="133">
+      <c r="F53" s="129">
         <f t="shared" ref="F53:F58" si="8">D53*8.09%</f>
         <v>0</v>
       </c>
-      <c r="G53" s="108">
+      <c r="G53" s="107">
         <f t="shared" ref="G53:G63" si="9">D53</f>
         <v>0</v>
       </c>
-      <c r="H53" s="155">
+      <c r="H53" s="148">
         <f t="shared" ref="H53:H63" si="10">E53+F53</f>
         <v>0</v>
       </c>
-      <c r="I53" s="168"/>
-      <c r="J53" s="168"/>
+      <c r="I53" s="161"/>
+      <c r="J53" s="161"/>
     </row>
     <row r="54" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A54" s="94" t="s">
+      <c r="A54" s="93" t="s">
         <v>168</v>
       </c>
       <c r="B54" s="7"/>
       <c r="C54" s="7"/>
-      <c r="D54" s="180">
+      <c r="D54" s="111">
         <v>148200</v>
       </c>
-      <c r="E54" s="145">
+      <c r="E54" s="141">
         <f t="shared" si="7"/>
         <v>136210.62</v>
       </c>
-      <c r="F54" s="133">
+      <c r="F54" s="129">
         <f t="shared" si="8"/>
         <v>11989.38</v>
       </c>
-      <c r="G54" s="108">
+      <c r="G54" s="107">
         <f t="shared" si="9"/>
         <v>148200</v>
       </c>
-      <c r="H54" s="155">
+      <c r="H54" s="148">
         <f t="shared" si="10"/>
         <v>148200</v>
       </c>
-      <c r="I54" s="168">
+      <c r="I54" s="161">
         <f t="shared" ref="I54:I62" si="11">H54-D54</f>
         <v>0</v>
       </c>
-      <c r="J54" s="168">
+      <c r="J54" s="161">
         <f t="shared" ref="J54:J62" si="12">G54-D54</f>
         <v>0</v>
       </c>
     </row>
     <row r="55" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A55" s="94" t="s">
+      <c r="A55" s="93" t="s">
         <v>169</v>
       </c>
       <c r="B55" s="7"/>
       <c r="C55" s="7"/>
-      <c r="D55" s="180">
+      <c r="D55" s="111">
         <v>812358.3</v>
       </c>
-      <c r="E55" s="145">
+      <c r="E55" s="141">
         <f t="shared" si="7"/>
         <v>746638.51353</v>
       </c>
-      <c r="F55" s="133">
+      <c r="F55" s="129">
         <f t="shared" si="8"/>
         <v>65719.786470000006</v>
       </c>
-      <c r="G55" s="108">
+      <c r="G55" s="107">
         <f t="shared" si="9"/>
         <v>812358.3</v>
       </c>
-      <c r="H55" s="155">
+      <c r="H55" s="148">
         <f t="shared" si="10"/>
         <v>812358.3</v>
       </c>
-      <c r="I55" s="168"/>
-      <c r="J55" s="168"/>
+      <c r="I55" s="161"/>
+      <c r="J55" s="161"/>
     </row>
     <row r="56" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A56" s="94" t="s">
+      <c r="A56" s="93" t="s">
         <v>9</v>
       </c>
       <c r="B56" s="7" t="s">
         <v>160</v>
       </c>
       <c r="C56" s="7"/>
-      <c r="D56" s="180">
+      <c r="D56" s="111">
         <v>129320</v>
       </c>
-      <c r="E56" s="145">
+      <c r="E56" s="141">
         <f>D56*91.91%</f>
         <v>118858.01199999999</v>
       </c>
-      <c r="F56" s="133">
+      <c r="F56" s="129">
         <f t="shared" si="8"/>
         <v>10461.987999999999</v>
       </c>
-      <c r="G56" s="108">
+      <c r="G56" s="107">
         <f t="shared" si="9"/>
         <v>129320</v>
       </c>
-      <c r="H56" s="155">
+      <c r="H56" s="148">
         <f>E56+F56</f>
         <v>129319.99999999999</v>
       </c>
-      <c r="I56" s="168">
+      <c r="I56" s="161">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="J56" s="168">
+      <c r="J56" s="161">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
     </row>
     <row r="57" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A57" s="94" t="s">
+      <c r="A57" s="93" t="s">
         <v>11</v>
       </c>
-      <c r="B57" s="98" t="s">
+      <c r="B57" s="97" t="s">
         <v>161</v>
       </c>
       <c r="C57" s="7"/>
-      <c r="D57" s="180">
+      <c r="D57" s="111">
         <v>655067.86</v>
       </c>
-      <c r="E57" s="145">
+      <c r="E57" s="141">
         <f t="shared" si="7"/>
         <v>602072.87012599991</v>
       </c>
-      <c r="F57" s="133">
+      <c r="F57" s="129">
         <f t="shared" si="8"/>
         <v>52994.989873999999</v>
       </c>
-      <c r="G57" s="108">
+      <c r="G57" s="107">
         <f t="shared" si="9"/>
         <v>655067.86</v>
       </c>
-      <c r="H57" s="155">
+      <c r="H57" s="148">
         <f t="shared" si="10"/>
         <v>655067.85999999987</v>
       </c>
-      <c r="I57" s="168">
+      <c r="I57" s="161">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="J57" s="168">
+      <c r="J57" s="161">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
     </row>
     <row r="58" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A58" s="128" t="s">
+      <c r="A58" s="124" t="s">
         <v>10</v>
       </c>
-      <c r="B58" s="98" t="s">
+      <c r="B58" s="97" t="s">
         <v>166</v>
       </c>
-      <c r="C58" s="98"/>
-      <c r="D58" s="180">
+      <c r="C58" s="97"/>
+      <c r="D58" s="111">
         <v>1107047.99</v>
       </c>
-      <c r="E58" s="145">
+      <c r="E58" s="141">
         <f t="shared" si="7"/>
         <v>1017487.8076089999</v>
       </c>
-      <c r="F58" s="133">
+      <c r="F58" s="129">
         <f t="shared" si="8"/>
         <v>89560.182390999995</v>
       </c>
-      <c r="G58" s="108">
+      <c r="G58" s="107">
         <f t="shared" si="9"/>
         <v>1107047.99</v>
       </c>
-      <c r="H58" s="155">
+      <c r="H58" s="148">
         <f t="shared" si="10"/>
         <v>1107047.99</v>
       </c>
-      <c r="I58" s="168">
+      <c r="I58" s="161">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="J58" s="168">
+      <c r="J58" s="161">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
     </row>
     <row r="59" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A59" s="211" t="s">
+      <c r="A59" s="205" t="s">
         <v>167</v>
       </c>
-      <c r="B59" s="212"/>
-      <c r="C59" s="213"/>
-      <c r="D59" s="180">
+      <c r="B59" s="206"/>
+      <c r="C59" s="207"/>
+      <c r="D59" s="111">
         <v>51000</v>
       </c>
-      <c r="E59" s="145">
+      <c r="E59" s="141">
         <f t="shared" ref="E59" si="13">D59</f>
         <v>51000</v>
       </c>
-      <c r="F59" s="133"/>
-      <c r="G59" s="108">
+      <c r="F59" s="129"/>
+      <c r="G59" s="107">
         <f t="shared" si="9"/>
         <v>51000</v>
       </c>
-      <c r="H59" s="155">
+      <c r="H59" s="148">
         <f t="shared" si="10"/>
         <v>51000</v>
       </c>
-      <c r="I59" s="168">
+      <c r="I59" s="161">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="J59" s="168">
+      <c r="J59" s="161">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
     </row>
     <row r="60" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A60" s="186" t="s">
+      <c r="A60" s="179" t="s">
         <v>165</v>
       </c>
-      <c r="B60" s="98"/>
-      <c r="C60" s="98"/>
-      <c r="D60" s="180">
+      <c r="B60" s="97"/>
+      <c r="C60" s="97"/>
+      <c r="D60" s="111">
         <v>400000</v>
       </c>
-      <c r="E60" s="145">
+      <c r="E60" s="141">
         <f t="shared" ref="E60:E63" si="14">D60*91.91%</f>
         <v>367639.99999999994</v>
       </c>
-      <c r="F60" s="133">
+      <c r="F60" s="129">
         <f t="shared" ref="F60:F63" si="15">D60*8.09%</f>
         <v>32360</v>
       </c>
-      <c r="G60" s="108">
+      <c r="G60" s="107">
         <f t="shared" si="9"/>
         <v>400000</v>
       </c>
-      <c r="H60" s="155">
+      <c r="H60" s="148">
         <f t="shared" si="10"/>
         <v>399999.99999999994</v>
       </c>
-      <c r="I60" s="168">
+      <c r="I60" s="161">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="J60" s="168">
+      <c r="J60" s="161">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="M60" s="179" t="s">
+      <c r="M60" s="172" t="s">
         <v>137</v>
       </c>
       <c r="N60" s="7"/>
       <c r="O60" s="7"/>
-      <c r="P60" s="180">
+      <c r="P60" s="173">
         <v>358487.12</v>
       </c>
     </row>
@@ -3040,26 +3067,26 @@
       <c r="A61" s="7" t="s">
         <v>154</v>
       </c>
-      <c r="B61" s="98"/>
-      <c r="C61" s="98"/>
-      <c r="D61" s="180">
+      <c r="B61" s="97"/>
+      <c r="C61" s="97"/>
+      <c r="D61" s="111">
         <v>47279.57</v>
       </c>
-      <c r="E61" s="145">
+      <c r="E61" s="141">
         <f t="shared" ref="E61:E62" si="16">D61</f>
         <v>47279.57</v>
       </c>
-      <c r="F61" s="133"/>
-      <c r="G61" s="108">
+      <c r="F61" s="129"/>
+      <c r="G61" s="107">
         <f t="shared" si="9"/>
         <v>47279.57</v>
       </c>
-      <c r="H61" s="155">
+      <c r="H61" s="148">
         <f t="shared" si="10"/>
         <v>47279.57</v>
       </c>
-      <c r="I61" s="168"/>
-      <c r="J61" s="168"/>
+      <c r="I61" s="161"/>
+      <c r="J61" s="161"/>
     </row>
     <row r="62" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="7" t="s">
@@ -3067,86 +3094,86 @@
       </c>
       <c r="B62" s="7"/>
       <c r="C62" s="7"/>
-      <c r="D62" s="180">
+      <c r="D62" s="111">
         <v>88294</v>
       </c>
-      <c r="E62" s="145">
+      <c r="E62" s="141">
         <f t="shared" si="16"/>
         <v>88294</v>
       </c>
-      <c r="F62" s="133"/>
-      <c r="G62" s="108">
+      <c r="F62" s="129"/>
+      <c r="G62" s="107">
         <f t="shared" si="9"/>
         <v>88294</v>
       </c>
-      <c r="H62" s="155">
+      <c r="H62" s="148">
         <f t="shared" si="10"/>
         <v>88294</v>
       </c>
-      <c r="I62" s="168">
+      <c r="I62" s="161">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="J62" s="168">
+      <c r="J62" s="161">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
     </row>
     <row r="63" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A63" s="120" t="s">
+      <c r="A63" s="119" t="s">
         <v>156</v>
       </c>
-      <c r="B63" s="113"/>
+      <c r="B63" s="112"/>
       <c r="C63" s="7"/>
-      <c r="D63" s="180">
+      <c r="D63" s="111">
         <v>90143.44</v>
       </c>
-      <c r="E63" s="145">
+      <c r="E63" s="141">
         <f t="shared" si="14"/>
         <v>82850.835703999997</v>
       </c>
-      <c r="F63" s="133">
+      <c r="F63" s="129">
         <f t="shared" si="15"/>
         <v>7292.6042960000004</v>
       </c>
-      <c r="G63" s="108">
+      <c r="G63" s="107">
         <f t="shared" si="9"/>
         <v>90143.44</v>
       </c>
-      <c r="H63" s="155">
+      <c r="H63" s="148">
         <f t="shared" si="10"/>
         <v>90143.44</v>
       </c>
-      <c r="I63" s="168"/>
-      <c r="J63" s="168"/>
+      <c r="I63" s="161"/>
+      <c r="J63" s="161"/>
     </row>
     <row r="64" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A64" s="95" t="s">
+      <c r="A64" s="94" t="s">
         <v>12</v>
       </c>
-      <c r="B64" s="96"/>
-      <c r="C64" s="96"/>
-      <c r="D64" s="107">
+      <c r="B64" s="95"/>
+      <c r="C64" s="95"/>
+      <c r="D64" s="106">
         <f>SUM(D51:D63)</f>
         <v>3939711.16</v>
       </c>
-      <c r="E64" s="107">
+      <c r="E64" s="106">
         <f>SUM(E51:E63)</f>
         <v>3669332.2289689998</v>
       </c>
-      <c r="F64" s="107">
+      <c r="F64" s="106">
         <f>SUM(F51:F63)</f>
         <v>270378.93103099999</v>
       </c>
-      <c r="G64" s="108">
+      <c r="G64" s="107">
         <f>E64+F64</f>
         <v>3939711.1599999997</v>
       </c>
-      <c r="H64" s="146" t="str">
+      <c r="H64" s="142" t="str">
         <f>IF(D64=G64, "", "Error")</f>
         <v/>
       </c>
-      <c r="I64" s="168">
+      <c r="I64" s="161">
         <f>D64-G64</f>
         <v>0</v>
       </c>
@@ -3155,273 +3182,274 @@
       <c r="A65" s="7"/>
       <c r="B65" s="7"/>
       <c r="C65" s="7"/>
-      <c r="D65" s="173"/>
-      <c r="E65" s="114"/>
+      <c r="D65" s="166"/>
+      <c r="E65" s="113"/>
       <c r="F65" s="7"/>
-      <c r="H65" s="146"/>
+      <c r="H65" s="142"/>
     </row>
     <row r="66" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A66" s="7"/>
       <c r="B66" s="7"/>
       <c r="C66" s="7"/>
-      <c r="D66" s="173"/>
-      <c r="E66" s="113"/>
+      <c r="D66" s="166"/>
+      <c r="E66" s="112"/>
       <c r="F66" s="7"/>
-      <c r="H66" s="146"/>
+      <c r="H66" s="142"/>
     </row>
     <row r="67" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A67" s="7"/>
       <c r="B67" s="7"/>
       <c r="C67" s="7"/>
-      <c r="D67" s="173"/>
-      <c r="E67" s="113"/>
+      <c r="D67" s="166"/>
+      <c r="E67" s="112"/>
       <c r="F67" s="7"/>
-      <c r="H67" s="146"/>
+      <c r="H67" s="142"/>
     </row>
     <row r="68" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A68" s="94" t="s">
+      <c r="A68" s="93" t="s">
         <v>141</v>
       </c>
-      <c r="B68" s="98"/>
+      <c r="B68" s="97"/>
       <c r="C68" s="7"/>
-      <c r="D68" s="180">
+      <c r="D68" s="111">
         <v>112680</v>
       </c>
-      <c r="E68" s="145">
+      <c r="E68" s="141">
         <f>D68*91.91%</f>
         <v>103564.18799999999</v>
       </c>
-      <c r="F68" s="133">
+      <c r="F68" s="129">
         <f>D68*8.09%</f>
         <v>9115.8119999999999</v>
       </c>
-      <c r="G68" s="154"/>
-      <c r="H68" s="146"/>
+      <c r="G68" s="147"/>
+      <c r="H68" s="142"/>
     </row>
     <row r="69" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A69" s="7"/>
       <c r="B69" s="7"/>
       <c r="C69" s="7"/>
-      <c r="D69" s="112"/>
-      <c r="E69" s="157">
+      <c r="D69" s="111"/>
+      <c r="E69" s="150">
         <f>D69</f>
         <v>0</v>
       </c>
       <c r="F69" s="7"/>
-      <c r="H69" s="146"/>
-      <c r="I69" s="108"/>
+      <c r="H69" s="142"/>
+      <c r="I69" s="107"/>
     </row>
     <row r="70" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A70" s="95" t="s">
+      <c r="A70" s="94" t="s">
         <v>16</v>
       </c>
-      <c r="B70" s="95"/>
-      <c r="C70" s="95"/>
-      <c r="D70" s="107">
+      <c r="B70" s="94"/>
+      <c r="C70" s="94"/>
+      <c r="D70" s="106">
         <f>SUM(D68:D69)</f>
         <v>112680</v>
       </c>
-      <c r="E70" s="107">
+      <c r="E70" s="106">
         <f>SUM(E68:E69)</f>
         <v>103564.18799999999</v>
       </c>
-      <c r="F70" s="107">
+      <c r="F70" s="106">
         <f>SUM(F68:F69)</f>
         <v>9115.8119999999999</v>
       </c>
-      <c r="G70" s="108">
+      <c r="G70" s="107">
         <f>E70+F70</f>
         <v>112680</v>
       </c>
-      <c r="H70" s="146" t="str">
+      <c r="H70" s="142" t="str">
         <f>IF(D70=G70, "", "Error")</f>
         <v/>
       </c>
-      <c r="J70" s="108"/>
+      <c r="J70" s="107"/>
     </row>
     <row r="71" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A71" s="7"/>
       <c r="B71" s="7"/>
       <c r="C71" s="7"/>
-      <c r="D71" s="173"/>
-      <c r="E71" s="114"/>
+      <c r="D71" s="166"/>
+      <c r="E71" s="113"/>
       <c r="F71" s="7"/>
-      <c r="H71" s="146"/>
+      <c r="H71" s="142"/>
     </row>
     <row r="72" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A72" s="7"/>
       <c r="B72" s="7"/>
       <c r="C72" s="7"/>
-      <c r="D72" s="173"/>
-      <c r="E72" s="113"/>
+      <c r="D72" s="166"/>
+      <c r="E72" s="112"/>
       <c r="F72" s="7"/>
-      <c r="H72" s="146"/>
+      <c r="H72" s="142"/>
     </row>
     <row r="73" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A73" s="94" t="s">
+      <c r="A73" s="93" t="s">
         <v>13</v>
       </c>
       <c r="B73" s="7"/>
       <c r="C73" s="7"/>
-      <c r="D73" s="173"/>
-      <c r="E73" s="113"/>
+      <c r="D73" s="166"/>
+      <c r="E73" s="112"/>
       <c r="F73" s="7"/>
-      <c r="H73" s="146"/>
+      <c r="H73" s="142"/>
     </row>
     <row r="74" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A74" s="94" t="s">
+      <c r="A74" s="93" t="s">
         <v>14</v>
       </c>
       <c r="B74" s="7" t="s">
         <v>116</v>
       </c>
       <c r="C74" s="7"/>
-      <c r="D74" s="180">
+      <c r="D74" s="111">
         <v>246000</v>
       </c>
-      <c r="E74" s="145">
+      <c r="E74" s="141">
         <f>D74*91.91%</f>
         <v>226098.59999999998</v>
       </c>
-      <c r="F74" s="133">
+      <c r="F74" s="129">
         <f>D74*8.09%</f>
         <v>19901.400000000001</v>
       </c>
       <c r="G74" t="s">
         <v>139</v>
       </c>
-      <c r="H74" s="146"/>
+      <c r="H74" s="142"/>
     </row>
     <row r="75" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A75" s="94" t="s">
+      <c r="A75" s="93" t="s">
         <v>107</v>
       </c>
       <c r="B75" s="7"/>
       <c r="C75" s="7"/>
-      <c r="D75" s="180">
+      <c r="D75" s="111">
         <v>35000</v>
       </c>
-      <c r="E75" s="145">
+      <c r="E75" s="141">
         <f>D75*91.91%</f>
         <v>32168.499999999996</v>
       </c>
-      <c r="F75" s="133">
+      <c r="F75" s="129">
         <f>D75*8.09%</f>
         <v>2831.5</v>
       </c>
-      <c r="H75" s="146"/>
-      <c r="J75" s="112"/>
+      <c r="H75" s="142"/>
+      <c r="J75" s="111"/>
     </row>
     <row r="76" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A76" s="7"/>
       <c r="B76" s="7"/>
       <c r="C76" s="7"/>
-      <c r="D76" s="173"/>
-      <c r="E76" s="115"/>
+      <c r="D76" s="166"/>
+      <c r="E76" s="114"/>
       <c r="F76" s="7"/>
-      <c r="H76" s="146"/>
-      <c r="J76" s="108"/>
+      <c r="H76" s="142"/>
+      <c r="J76" s="107"/>
     </row>
     <row r="77" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A77" s="95" t="s">
+      <c r="A77" s="94" t="s">
         <v>100</v>
       </c>
-      <c r="B77" s="95"/>
-      <c r="C77" s="95"/>
-      <c r="D77" s="107">
+      <c r="B77" s="94"/>
+      <c r="C77" s="94"/>
+      <c r="D77" s="106">
         <f>SUM(D74:D76)</f>
         <v>281000</v>
       </c>
-      <c r="E77" s="107">
+      <c r="E77" s="106">
         <f>SUM(E74:E76)</f>
         <v>258267.09999999998</v>
       </c>
-      <c r="F77" s="107">
+      <c r="F77" s="106">
         <f>SUM(F74:F76)</f>
         <v>22732.9</v>
       </c>
-      <c r="G77" s="108">
+      <c r="G77" s="107">
         <f>E77+F77</f>
         <v>281000</v>
       </c>
-      <c r="H77" s="146" t="str">
+      <c r="H77" s="142" t="str">
         <f>IF(D77=G77, "", "Error")</f>
         <v/>
       </c>
-      <c r="J77" s="108"/>
+      <c r="J77" s="107"/>
     </row>
     <row r="78" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A78" s="94" t="s">
+      <c r="A78" s="93" t="s">
         <v>100</v>
       </c>
       <c r="B78" s="7"/>
       <c r="C78" s="7"/>
-      <c r="D78" s="112"/>
-      <c r="E78" s="116"/>
+      <c r="D78" s="111"/>
+      <c r="E78" s="115"/>
       <c r="F78" s="7"/>
-      <c r="H78" s="146"/>
+      <c r="H78" s="142"/>
     </row>
     <row r="79" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A79" s="94" t="s">
+      <c r="A79" s="93" t="s">
         <v>101</v>
       </c>
       <c r="B79" s="7"/>
       <c r="C79" s="7"/>
-      <c r="D79" s="243">
-        <v>230178.74</v>
-      </c>
-      <c r="E79" s="145">
+      <c r="D79" s="111">
+        <f>155582.25+151.2+3552+9324+348.88+1800</f>
+        <v>170758.33000000002</v>
+      </c>
+      <c r="E79" s="141">
         <f>D79*91.91%</f>
-        <v>211557.27993399996</v>
-      </c>
-      <c r="F79" s="133">
+        <v>156943.981103</v>
+      </c>
+      <c r="F79" s="129">
         <f>D79*8.09%</f>
-        <v>18621.460066</v>
-      </c>
-      <c r="H79" s="146"/>
+        <v>13814.348897000002</v>
+      </c>
+      <c r="H79" s="142"/>
     </row>
     <row r="80" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A80" s="94" t="s">
+      <c r="A80" s="93" t="s">
         <v>102</v>
       </c>
       <c r="B80" s="7"/>
-      <c r="C80" s="121"/>
-      <c r="D80" s="243">
+      <c r="C80" s="120"/>
+      <c r="D80" s="111">
         <v>44400</v>
       </c>
-      <c r="E80" s="145">
+      <c r="E80" s="141">
         <f>D80*91.91%</f>
         <v>40808.039999999994</v>
       </c>
-      <c r="F80" s="133">
+      <c r="F80" s="129">
         <f>D80*8.09%</f>
         <v>3591.96</v>
       </c>
-      <c r="H80" s="146"/>
+      <c r="H80" s="142"/>
     </row>
     <row r="81" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A81" s="95" t="s">
+      <c r="A81" s="94" t="s">
         <v>15</v>
       </c>
-      <c r="B81" s="95"/>
-      <c r="C81" s="95"/>
-      <c r="D81" s="152">
+      <c r="B81" s="94"/>
+      <c r="C81" s="94"/>
+      <c r="D81" s="145">
         <f>SUM(D79:D80)</f>
-        <v>274578.74</v>
-      </c>
-      <c r="E81" s="143">
+        <v>215158.33000000002</v>
+      </c>
+      <c r="E81" s="139">
         <f t="shared" ref="E81:F81" si="17">SUM(E79:E80)</f>
-        <v>252365.31993399997</v>
-      </c>
-      <c r="F81" s="143">
+        <v>197752.02110299998</v>
+      </c>
+      <c r="F81" s="139">
         <f t="shared" si="17"/>
-        <v>22213.420065999999</v>
-      </c>
-      <c r="G81" s="108">
+        <v>17406.308897000003</v>
+      </c>
+      <c r="G81" s="107">
         <f>E81+F81</f>
-        <v>274578.74</v>
-      </c>
-      <c r="H81" s="146" t="str">
+        <v>215158.33</v>
+      </c>
+      <c r="H81" s="142" t="str">
         <f>IF(D81=G81, "", "Error")</f>
         <v/>
       </c>
@@ -3430,430 +3458,430 @@
       <c r="A82" s="7"/>
       <c r="B82" s="7"/>
       <c r="C82" s="7"/>
-      <c r="D82" s="174"/>
-      <c r="E82" s="12"/>
+      <c r="D82" s="167"/>
+      <c r="E82" s="11"/>
       <c r="F82" s="7"/>
-      <c r="H82" s="146"/>
+      <c r="H82" s="142"/>
     </row>
     <row r="83" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A83" s="99" t="s">
+      <c r="A83" s="98" t="s">
         <v>133</v>
       </c>
-      <c r="B83" s="99"/>
-      <c r="C83" s="99"/>
-      <c r="D83" s="175">
-        <f>7000000-5970688.01</f>
-        <v>1029311.9900000002</v>
-      </c>
-      <c r="E83" s="117">
+      <c r="B83" s="98"/>
+      <c r="C83" s="98"/>
+      <c r="D83" s="168">
+        <f>7000000-6426943.64</f>
+        <v>573056.36000000034</v>
+      </c>
+      <c r="E83" s="116">
         <f>D83*91.91%</f>
-        <v>946040.65000900009</v>
-      </c>
-      <c r="F83" s="135">
+        <v>526696.10047600023</v>
+      </c>
+      <c r="F83" s="131">
         <f>D83*8.09%</f>
-        <v>83271.339991000015</v>
-      </c>
-      <c r="G83" s="108">
+        <v>46360.25952400003</v>
+      </c>
+      <c r="G83" s="107">
         <f>E83+F83</f>
-        <v>1029311.9900000001</v>
-      </c>
-      <c r="H83" s="146" t="str">
+        <v>573056.36000000022</v>
+      </c>
+      <c r="H83" s="142" t="str">
         <f>IF(D83=G83, "", "Error")</f>
         <v/>
       </c>
     </row>
     <row r="84" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A84" s="1"/>
-      <c r="D84" s="172"/>
+      <c r="D84" s="165"/>
       <c r="E84" s="2"/>
-      <c r="F84" s="10"/>
-      <c r="G84" s="151"/>
-      <c r="H84" s="146"/>
+      <c r="F84" s="9"/>
+      <c r="G84" s="144"/>
+      <c r="H84" s="142"/>
     </row>
     <row r="85" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A85" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="B85" s="60"/>
+      <c r="B85" s="59"/>
       <c r="C85" s="5"/>
-      <c r="D85" s="176">
+      <c r="D85" s="169">
         <f>SUM(D83+D81+D77+D70+D64+D49+D32+D27+D44)</f>
-        <v>7515676.040000001</v>
-      </c>
-      <c r="E85" s="144">
+        <v>7000000.0000000009</v>
+      </c>
+      <c r="E85" s="140">
         <f>SUM(E83+E81+E77+E70+E64+E49+E32+E27+E44)</f>
-        <v>6956001.5501770005</v>
-      </c>
-      <c r="F85" s="144">
+        <v>6482043.7018129993</v>
+      </c>
+      <c r="F85" s="140">
         <f>SUM(F83+F81+F77+F70+F64+F49+F32+F27+F44)</f>
-        <v>559674.48982300004</v>
-      </c>
-      <c r="G85" s="108">
+        <v>517956.29818700004</v>
+      </c>
+      <c r="G85" s="107">
         <f>E85+F85</f>
-        <v>7515676.040000001</v>
-      </c>
-      <c r="H85" s="146" t="str">
+        <v>6999999.9999999991</v>
+      </c>
+      <c r="H85" s="142" t="str">
         <f>IF(D85=G85, "", "Error")</f>
         <v/>
       </c>
-      <c r="I85" s="168">
+      <c r="I85" s="161">
         <f>D85-G85</f>
         <v>0</v>
       </c>
     </row>
     <row r="86" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D86" s="172"/>
-      <c r="E86" s="108"/>
+      <c r="D86" s="165"/>
+      <c r="E86" s="107"/>
     </row>
     <row r="87" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A87" s="182" t="s">
+      <c r="A87" s="175" t="s">
         <v>152</v>
       </c>
-      <c r="B87" s="140"/>
-      <c r="C87" s="140"/>
-      <c r="E87" s="108"/>
+      <c r="B87" s="136"/>
+      <c r="C87" s="136"/>
+      <c r="E87" s="107"/>
     </row>
     <row r="88" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A88" s="1"/>
-      <c r="C88" s="138"/>
-      <c r="E88" s="108"/>
+      <c r="C88" s="134"/>
+      <c r="E88" s="107"/>
     </row>
     <row r="89" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A89" s="1"/>
-      <c r="C89" s="138"/>
-      <c r="E89" s="108"/>
+      <c r="C89" s="134"/>
+      <c r="E89" s="107"/>
     </row>
     <row r="90" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A90" s="141" t="s">
+      <c r="A90" s="137" t="s">
         <v>29</v>
       </c>
-      <c r="B90" s="142"/>
-      <c r="C90" s="139">
+      <c r="B90" s="138"/>
+      <c r="C90" s="135">
         <f>SUM(C88:C89)</f>
         <v>0</v>
       </c>
-      <c r="E90" s="108"/>
+      <c r="E90" s="107"/>
     </row>
     <row r="91" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="E91" s="108"/>
+      <c r="E91" s="107"/>
     </row>
     <row r="92" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="E92" s="136"/>
+      <c r="E92" s="132"/>
     </row>
     <row r="93" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A93" s="209" t="s">
+      <c r="A93" s="203" t="s">
         <v>113</v>
       </c>
-      <c r="B93" s="210"/>
-      <c r="C93" s="210"/>
-      <c r="D93" s="210"/>
-      <c r="E93" s="163" t="s">
+      <c r="B93" s="204"/>
+      <c r="C93" s="204"/>
+      <c r="D93" s="204"/>
+      <c r="E93" s="156" t="s">
         <v>21</v>
       </c>
-      <c r="F93" s="164" t="s">
+      <c r="F93" s="157" t="s">
         <v>122</v>
       </c>
     </row>
     <row r="94" spans="1:9" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A94" s="206" t="s">
+      <c r="A94" s="200" t="s">
         <v>170</v>
       </c>
-      <c r="B94" s="207"/>
-      <c r="C94" s="208"/>
-      <c r="D94" s="180">
+      <c r="B94" s="201"/>
+      <c r="C94" s="202"/>
+      <c r="D94" s="111">
         <v>2900000</v>
       </c>
-      <c r="E94" s="145">
+      <c r="E94" s="141">
         <f t="shared" ref="E94:E95" si="18">D94*91.91%</f>
         <v>2665389.9999999995</v>
       </c>
-      <c r="F94" s="133">
+      <c r="F94" s="129">
         <f t="shared" ref="F94:F95" si="19">D94*8.09%</f>
         <v>234610</v>
       </c>
     </row>
     <row r="95" spans="1:9" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A95" s="214"/>
-      <c r="B95" s="215"/>
-      <c r="C95" s="216"/>
-      <c r="D95" s="112"/>
-      <c r="E95" s="145">
+      <c r="A95" s="208"/>
+      <c r="B95" s="209"/>
+      <c r="C95" s="210"/>
+      <c r="D95" s="111"/>
+      <c r="E95" s="141">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="F95" s="133">
+      <c r="F95" s="129">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
     </row>
     <row r="96" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A96" s="203" t="s">
+      <c r="A96" s="197" t="s">
         <v>29</v>
       </c>
-      <c r="B96" s="204"/>
-      <c r="C96" s="205"/>
-      <c r="D96" s="162">
+      <c r="B96" s="198"/>
+      <c r="C96" s="199"/>
+      <c r="D96" s="155">
         <f>SUM(D94:D95)</f>
         <v>2900000</v>
       </c>
-      <c r="E96" s="162">
+      <c r="E96" s="155">
         <f>SUM(E94:E95)</f>
         <v>2665389.9999999995</v>
       </c>
-      <c r="F96" s="162">
+      <c r="F96" s="155">
         <f>SUM(F94:F95)</f>
         <v>234610</v>
       </c>
-      <c r="H96" s="108">
+      <c r="H96" s="107">
         <f>E96+F96</f>
         <v>2899999.9999999995</v>
       </c>
-      <c r="I96" s="146" t="str">
+      <c r="I96" s="142" t="str">
         <f>IF(D96=H96, "", "Error")</f>
         <v/>
       </c>
     </row>
     <row r="98" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="E98" s="108"/>
+      <c r="E98" s="107"/>
     </row>
     <row r="99" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A99" s="102" t="s">
+      <c r="A99" s="101" t="s">
         <v>104</v>
       </c>
-      <c r="B99" s="103">
+      <c r="B99" s="102">
         <f>D85</f>
-        <v>7515676.040000001</v>
+        <v>7000000.0000000009</v>
       </c>
     </row>
     <row r="100" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A100" s="104" t="s">
+      <c r="A100" s="103" t="s">
         <v>106</v>
       </c>
-      <c r="B100" s="105">
+      <c r="B100" s="104">
         <f>D85-D83</f>
-        <v>6486364.0500000007</v>
+        <v>6426943.6400000006</v>
       </c>
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="D101" s="193"/>
-      <c r="E101" s="193"/>
+      <c r="D101" s="187"/>
+      <c r="E101" s="187"/>
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A102" s="74" t="s">
+      <c r="A102" s="73" t="s">
         <v>90</v>
       </c>
-      <c r="B102" s="75"/>
-      <c r="C102" s="76"/>
-      <c r="D102" s="193"/>
-      <c r="E102" s="193"/>
+      <c r="B102" s="74"/>
+      <c r="C102" s="75"/>
+      <c r="D102" s="187"/>
+      <c r="E102" s="187"/>
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A103" s="77" t="s">
+      <c r="A103" s="76" t="s">
         <v>91</v>
       </c>
-      <c r="B103" s="11">
+      <c r="B103" s="10">
         <v>3617497.2979896166</v>
       </c>
-      <c r="C103" s="78"/>
-      <c r="D103" s="193"/>
-      <c r="E103" s="193"/>
+      <c r="C103" s="77"/>
+      <c r="D103" s="187"/>
+      <c r="E103" s="187"/>
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A104" s="79" t="s">
+      <c r="A104" s="78" t="s">
         <v>92</v>
       </c>
-      <c r="B104" s="92">
+      <c r="B104" s="91">
         <f>PRORRATEO!G52</f>
         <v>6941937.3369510006</v>
       </c>
-      <c r="C104" s="78" t="s">
+      <c r="C104" s="77" t="s">
         <v>93</v>
       </c>
-      <c r="D104" s="193"/>
-      <c r="E104" s="193"/>
+      <c r="D104" s="187"/>
+      <c r="E104" s="187"/>
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A105" s="79" t="s">
+      <c r="A105" s="78" t="s">
         <v>115</v>
       </c>
-      <c r="B105" s="165">
+      <c r="B105" s="158">
         <f>-B100</f>
-        <v>-6486364.0500000007</v>
-      </c>
-      <c r="C105" s="76"/>
-      <c r="D105" s="193"/>
-      <c r="E105" s="193"/>
-      <c r="G105" s="112"/>
+        <v>-6426943.6400000006</v>
+      </c>
+      <c r="C105" s="75"/>
+      <c r="D105" s="187"/>
+      <c r="E105" s="187"/>
+      <c r="G105" s="111"/>
     </row>
     <row r="106" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A106" s="79" t="s">
+      <c r="A106" s="78" t="s">
         <v>114</v>
       </c>
-      <c r="B106" s="165">
+      <c r="B106" s="158">
         <f>-D96</f>
         <v>-2900000</v>
       </c>
-      <c r="C106" s="76"/>
-      <c r="D106" s="193"/>
-      <c r="E106" s="193"/>
-      <c r="G106" s="124"/>
+      <c r="C106" s="75"/>
+      <c r="D106" s="187"/>
+      <c r="E106" s="187"/>
+      <c r="G106" s="121"/>
     </row>
     <row r="107" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A107" s="79" t="s">
+      <c r="A107" s="78" t="s">
         <v>171</v>
       </c>
-      <c r="B107" s="165">
+      <c r="B107" s="158">
         <f>-77229-250000</f>
         <v>-327229</v>
       </c>
-      <c r="C107" s="76"/>
-      <c r="D107" s="189"/>
-      <c r="E107" s="189"/>
-      <c r="G107" s="124"/>
+      <c r="C107" s="75"/>
+      <c r="D107" s="182"/>
+      <c r="E107" s="182"/>
+      <c r="G107" s="121"/>
     </row>
     <row r="108" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A108" s="79" t="s">
+      <c r="A108" s="78" t="s">
         <v>172</v>
       </c>
-      <c r="B108" s="165">
+      <c r="B108" s="158">
         <f>-19000*2</f>
         <v>-38000</v>
       </c>
-      <c r="C108" s="76"/>
-      <c r="D108" s="189"/>
-      <c r="E108" s="189"/>
-      <c r="G108" s="124"/>
+      <c r="C108" s="75"/>
+      <c r="D108" s="182"/>
+      <c r="E108" s="182"/>
+      <c r="G108" s="121"/>
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A109" s="79" t="s">
+      <c r="A109" s="78" t="s">
         <v>105</v>
       </c>
-      <c r="B109" s="165">
+      <c r="B109" s="158">
         <f>-B116</f>
         <v>-60000</v>
       </c>
-      <c r="C109" s="80"/>
+      <c r="C109" s="79"/>
     </row>
     <row r="110" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A110" s="79" t="s">
+      <c r="A110" s="78" t="s">
         <v>120</v>
       </c>
-      <c r="B110" s="93">
+      <c r="B110" s="92">
         <f>-C90</f>
         <v>0</v>
       </c>
-      <c r="C110" s="80"/>
+      <c r="C110" s="79"/>
     </row>
     <row r="111" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A111" s="79"/>
-      <c r="B111" s="75"/>
-      <c r="C111" s="150"/>
+      <c r="A111" s="78"/>
+      <c r="B111" s="74"/>
+      <c r="C111" s="143"/>
     </row>
     <row r="112" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A112" s="77" t="s">
+      <c r="A112" s="76" t="s">
         <v>94</v>
       </c>
-      <c r="B112" s="81">
+      <c r="B112" s="80">
         <f>SUM(B103:B111)</f>
-        <v>747841.58494061604</v>
-      </c>
-      <c r="C112" s="150"/>
+        <v>807261.99494061619</v>
+      </c>
+      <c r="C112" s="143"/>
     </row>
     <row r="113" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A113" s="80"/>
-      <c r="C113" s="76"/>
-      <c r="D113" s="83"/>
+      <c r="A113" s="79"/>
+      <c r="C113" s="75"/>
+      <c r="D113" s="82"/>
     </row>
     <row r="114" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="C114" s="76"/>
-      <c r="D114" s="108"/>
-      <c r="E114" s="168"/>
+      <c r="C114" s="75"/>
+      <c r="D114" s="107"/>
+      <c r="E114" s="161"/>
     </row>
     <row r="115" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A115" s="74" t="s">
+      <c r="A115" s="73" t="s">
         <v>95</v>
       </c>
-      <c r="B115" s="244">
+      <c r="B115" s="184">
         <v>-272694.54000000004</v>
       </c>
-      <c r="C115" s="82"/>
-      <c r="D115" s="168"/>
-      <c r="E115" s="168"/>
-      <c r="F115" s="168"/>
+      <c r="C115" s="81"/>
+      <c r="D115" s="161"/>
+      <c r="E115" s="161"/>
+      <c r="F115" s="161"/>
     </row>
     <row r="116" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A116" s="77" t="s">
+      <c r="A116" s="76" t="s">
         <v>159</v>
       </c>
-      <c r="B116" s="93">
+      <c r="B116" s="92">
         <v>60000</v>
       </c>
-      <c r="C116" s="82"/>
-      <c r="D116" s="168"/>
-      <c r="E116" s="178"/>
+      <c r="C116" s="81"/>
+      <c r="D116" s="161"/>
+      <c r="E116" s="171"/>
     </row>
     <row r="117" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A117" s="77"/>
-      <c r="B117" s="165"/>
-      <c r="C117" s="82"/>
-      <c r="E117" s="108"/>
+      <c r="A117" s="76"/>
+      <c r="B117" s="158"/>
+      <c r="C117" s="81"/>
+      <c r="E117" s="107"/>
     </row>
     <row r="118" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A118" s="77"/>
-      <c r="B118" s="165"/>
-      <c r="C118" s="82"/>
-      <c r="E118" s="108"/>
+      <c r="A118" s="76"/>
+      <c r="B118" s="158"/>
+      <c r="C118" s="81"/>
+      <c r="E118" s="107"/>
     </row>
     <row r="119" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A119" s="100" t="s">
+      <c r="A119" s="99" t="s">
         <v>29</v>
       </c>
-      <c r="B119" s="101">
+      <c r="B119" s="100">
         <f>SUM(B115:B118)</f>
         <v>-212694.54000000004</v>
       </c>
-      <c r="C119" s="82"/>
+      <c r="C119" s="81"/>
     </row>
     <row r="120" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="C120" s="83"/>
-      <c r="D120" s="168"/>
+      <c r="C120" s="82"/>
+      <c r="D120" s="161"/>
     </row>
     <row r="121" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="B121" s="80"/>
-      <c r="C121" s="76"/>
+      <c r="B121" s="79"/>
+      <c r="C121" s="75"/>
     </row>
     <row r="123" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="N123" s="12"/>
+      <c r="N123" s="11"/>
     </row>
     <row r="126" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="B126" s="192"/>
-      <c r="C126" s="192"/>
-      <c r="D126" s="192"/>
-      <c r="E126" s="192"/>
+      <c r="B126" s="186"/>
+      <c r="C126" s="186"/>
+      <c r="D126" s="186"/>
+      <c r="E126" s="186"/>
     </row>
     <row r="127" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="B127" s="192"/>
-      <c r="C127" s="192"/>
-      <c r="D127" s="192"/>
-      <c r="E127" s="192"/>
+      <c r="B127" s="186"/>
+      <c r="C127" s="186"/>
+      <c r="D127" s="186"/>
+      <c r="E127" s="186"/>
     </row>
     <row r="128" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="B128" s="192"/>
-      <c r="C128" s="192"/>
-      <c r="D128" s="192"/>
-      <c r="E128" s="192"/>
+      <c r="B128" s="186"/>
+      <c r="C128" s="186"/>
+      <c r="D128" s="186"/>
+      <c r="E128" s="186"/>
     </row>
     <row r="129" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B129" s="192"/>
-      <c r="C129" s="192"/>
-      <c r="D129" s="192"/>
-      <c r="E129" s="192"/>
+      <c r="B129" s="186"/>
+      <c r="C129" s="186"/>
+      <c r="D129" s="186"/>
+      <c r="E129" s="186"/>
     </row>
     <row r="130" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B130" s="192"/>
-      <c r="C130" s="192"/>
-      <c r="D130" s="192"/>
-      <c r="E130" s="192"/>
+      <c r="B130" s="186"/>
+      <c r="C130" s="186"/>
+      <c r="D130" s="186"/>
+      <c r="E130" s="186"/>
     </row>
   </sheetData>
   <mergeCells count="8">
@@ -3895,164 +3923,163 @@
     <col min="18" max="18" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A1" s="8"/>
-      <c r="B1" s="8"/>
-      <c r="C1" s="8"/>
-      <c r="D1" s="8"/>
-      <c r="E1" s="8"/>
-      <c r="F1" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="G1" s="8"/>
-      <c r="H1" s="8"/>
-      <c r="I1" s="8"/>
-      <c r="J1" s="8"/>
-      <c r="K1" s="8" t="s">
+    <row r="1" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="237" t="s">
+        <v>173</v>
+      </c>
+      <c r="B1" s="238"/>
+      <c r="C1" s="238"/>
+      <c r="D1" s="238"/>
+      <c r="E1" s="238"/>
+      <c r="F1" s="238"/>
+      <c r="G1" s="238"/>
+      <c r="H1" s="238"/>
+      <c r="I1" s="238"/>
+      <c r="J1" s="239"/>
+      <c r="K1" s="245" t="s">
         <v>124</v>
       </c>
-      <c r="L1" s="220">
+      <c r="L1" s="246">
         <f>RESUMEN!D85</f>
-        <v>7515676.040000001</v>
-      </c>
-      <c r="M1" s="221"/>
-      <c r="N1" s="148"/>
-      <c r="O1" s="134">
+        <v>7000000.0000000009</v>
+      </c>
+      <c r="M1" s="247"/>
+      <c r="N1" s="248"/>
+      <c r="O1" s="130">
         <f>L1*8.09%</f>
-        <v>608018.19163600006</v>
+        <v>566300.00000000012</v>
       </c>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A2" s="8"/>
-      <c r="B2" s="8"/>
-      <c r="C2" s="8"/>
-      <c r="D2" s="8"/>
-      <c r="E2" s="8"/>
-      <c r="F2" s="8"/>
-      <c r="G2" s="8"/>
-      <c r="H2" s="8"/>
-      <c r="I2" s="8"/>
-      <c r="J2" s="8"/>
-      <c r="K2" s="8" t="s">
+      <c r="A2" s="240"/>
+      <c r="B2" s="241"/>
+      <c r="C2" s="241"/>
+      <c r="D2" s="241"/>
+      <c r="E2" s="241"/>
+      <c r="F2" s="241"/>
+      <c r="G2" s="241"/>
+      <c r="H2" s="241"/>
+      <c r="I2" s="241"/>
+      <c r="J2" s="242"/>
+      <c r="K2" s="249" t="s">
         <v>125</v>
       </c>
-      <c r="L2" s="8"/>
-      <c r="M2" s="148">
+      <c r="L2" s="250"/>
+      <c r="M2" s="251">
         <v>7000000</v>
       </c>
-      <c r="N2" s="149"/>
-      <c r="O2" s="134">
+      <c r="N2" s="252"/>
+      <c r="O2" s="130">
         <f>O1-K7-553-50-86-8</f>
-        <v>116997.94204500003</v>
+        <v>47646.70181300008</v>
       </c>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A3" s="8" t="str">
-        <f>RESUMEN!C5</f>
-        <v>VTO: 14/11</v>
-      </c>
-      <c r="B3" s="8"/>
-      <c r="C3" s="8"/>
-      <c r="D3" s="8"/>
-      <c r="E3" s="8"/>
-      <c r="F3" s="8"/>
-      <c r="G3" s="8"/>
-      <c r="H3" s="8"/>
-      <c r="I3" s="8"/>
-      <c r="J3" s="9"/>
-      <c r="K3" s="8" t="s">
+      <c r="A3" s="240"/>
+      <c r="B3" s="241"/>
+      <c r="C3" s="241"/>
+      <c r="D3" s="241"/>
+      <c r="E3" s="241"/>
+      <c r="F3" s="241"/>
+      <c r="G3" s="241"/>
+      <c r="H3" s="241"/>
+      <c r="I3" s="241"/>
+      <c r="J3" s="242"/>
+      <c r="K3" s="249" t="s">
         <v>131</v>
       </c>
-      <c r="L3" s="8"/>
-      <c r="M3" s="127">
+      <c r="L3" s="250"/>
+      <c r="M3" s="253">
         <f>RESUMEN!D96</f>
         <v>2900000</v>
       </c>
-      <c r="N3" s="147"/>
-      <c r="O3" s="73"/>
-    </row>
-    <row r="4" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="8"/>
-      <c r="B4" s="8"/>
-      <c r="C4" s="8"/>
-      <c r="D4" s="8"/>
-      <c r="E4" s="8"/>
-      <c r="F4" s="8"/>
-      <c r="G4" s="8"/>
-      <c r="H4" s="8"/>
-      <c r="I4" s="8"/>
-      <c r="J4" s="122">
-        <f>(J3*8.09%)/44</f>
-        <v>0</v>
-      </c>
-      <c r="K4" s="8" t="s">
+      <c r="N3" s="254"/>
+      <c r="O3" s="72"/>
+    </row>
+    <row r="4" spans="1:16" ht="51" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="243"/>
+      <c r="B4" s="236"/>
+      <c r="C4" s="236"/>
+      <c r="D4" s="236"/>
+      <c r="E4" s="236"/>
+      <c r="F4" s="236"/>
+      <c r="G4" s="236"/>
+      <c r="H4" s="236"/>
+      <c r="I4" s="236"/>
+      <c r="J4" s="244"/>
+      <c r="K4" s="255" t="s">
         <v>125</v>
       </c>
-      <c r="L4" s="8"/>
-      <c r="M4" s="127">
-        <v>450000</v>
-      </c>
-      <c r="N4" s="123"/>
+      <c r="L4" s="256"/>
+      <c r="M4" s="257">
+        <f>O4</f>
+        <v>966666.66666666663</v>
+      </c>
+      <c r="N4" s="258"/>
+      <c r="O4" s="130">
+        <f>M3/3</f>
+        <v>966666.66666666663</v>
+      </c>
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A5" s="217" t="s">
+      <c r="A5" s="211" t="s">
         <v>19</v>
       </c>
-      <c r="B5" s="231" t="s">
+      <c r="B5" s="213" t="s">
         <v>20</v>
       </c>
-      <c r="C5" s="217" t="s">
+      <c r="C5" s="211" t="s">
         <v>21</v>
       </c>
-      <c r="D5" s="229" t="s">
+      <c r="D5" s="215" t="s">
         <v>22</v>
       </c>
-      <c r="E5" s="217" t="s">
+      <c r="E5" s="211" t="s">
         <v>97</v>
       </c>
-      <c r="F5" s="217" t="s">
+      <c r="F5" s="211" t="s">
         <v>23</v>
       </c>
-      <c r="G5" s="217" t="s">
+      <c r="G5" s="211" t="s">
         <v>24</v>
       </c>
-      <c r="H5" s="224" t="s">
+      <c r="H5" s="220" t="s">
         <v>25</v>
       </c>
-      <c r="I5" s="229" t="s">
+      <c r="I5" s="215" t="s">
         <v>108</v>
       </c>
-      <c r="J5" s="222" t="s">
+      <c r="J5" s="218" t="s">
         <v>26</v>
       </c>
-      <c r="K5" s="222" t="s">
+      <c r="K5" s="218" t="s">
         <v>69</v>
       </c>
-      <c r="L5" s="227" t="s">
+      <c r="L5" s="223" t="s">
         <v>123</v>
       </c>
-      <c r="M5" s="222" t="s">
+      <c r="M5" s="218" t="s">
         <v>67</v>
       </c>
-      <c r="N5" s="222" t="s">
+      <c r="N5" s="218" t="s">
         <v>68</v>
       </c>
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A6" s="218"/>
-      <c r="B6" s="232"/>
-      <c r="C6" s="218"/>
-      <c r="D6" s="233"/>
-      <c r="E6" s="218"/>
-      <c r="F6" s="218"/>
-      <c r="G6" s="218"/>
-      <c r="H6" s="225"/>
-      <c r="I6" s="230"/>
-      <c r="J6" s="223"/>
-      <c r="K6" s="226"/>
-      <c r="L6" s="228"/>
-      <c r="M6" s="226"/>
-      <c r="N6" s="223"/>
+      <c r="A6" s="212"/>
+      <c r="B6" s="214"/>
+      <c r="C6" s="212"/>
+      <c r="D6" s="216"/>
+      <c r="E6" s="212"/>
+      <c r="F6" s="212"/>
+      <c r="G6" s="212"/>
+      <c r="H6" s="221"/>
+      <c r="I6" s="225"/>
+      <c r="J6" s="219"/>
+      <c r="K6" s="222"/>
+      <c r="L6" s="224"/>
+      <c r="M6" s="222"/>
+      <c r="N6" s="219"/>
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
@@ -4062,40 +4089,41 @@
       <c r="C7" s="7">
         <v>1</v>
       </c>
-      <c r="D7" s="132" t="s">
+      <c r="D7" s="128" t="s">
         <v>34</v>
       </c>
       <c r="E7" s="7">
         <v>8.09</v>
       </c>
-      <c r="F7" s="88">
+      <c r="F7" s="87">
         <v>524871.62695100007</v>
       </c>
-      <c r="G7" s="187">
+      <c r="G7" s="180">
         <f>F7</f>
         <v>524871.62695100007</v>
       </c>
-      <c r="H7" s="130">
+      <c r="H7" s="126">
         <f>F7-G7</f>
         <v>0</v>
       </c>
-      <c r="I7" s="106">
+      <c r="I7" s="105">
         <v>12</v>
       </c>
-      <c r="J7" s="88">
-        <v>34548.377359999999</v>
-      </c>
-      <c r="K7" s="88">
-        <v>490323.24959100003</v>
-      </c>
-      <c r="L7" s="98"/>
+      <c r="J7" s="87">
+        <f>234610/3</f>
+        <v>78203.333333333328</v>
+      </c>
+      <c r="K7" s="87">
+        <v>517956.29818700004</v>
+      </c>
+      <c r="L7" s="97"/>
       <c r="M7" s="6">
         <f>K7+J7+H7+L7</f>
-        <v>524871.62695100007</v>
-      </c>
-      <c r="N7" s="11">
+        <v>596159.63152033335</v>
+      </c>
+      <c r="N7" s="10">
         <f>M7*6% + M7</f>
-        <v>556363.92456806009</v>
+        <v>631929.20941155334</v>
       </c>
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.25">
@@ -4106,41 +4134,41 @@
       <c r="C8" s="7">
         <v>24</v>
       </c>
-      <c r="D8" s="132" t="s">
+      <c r="D8" s="128" t="s">
         <v>36</v>
       </c>
       <c r="E8" s="7">
         <v>2.21</v>
       </c>
-      <c r="F8" s="88">
+      <c r="F8" s="87">
         <v>164206.27016451582</v>
       </c>
-      <c r="G8" s="187">
+      <c r="G8" s="180">
         <v>165000</v>
       </c>
-      <c r="H8" s="130">
+      <c r="H8" s="126">
         <f t="shared" ref="H8:H51" si="0">F8-G8</f>
         <v>-793.72983548417687</v>
       </c>
-      <c r="I8" s="106">
+      <c r="I8" s="105">
         <v>11</v>
       </c>
-      <c r="J8" s="88">
+      <c r="J8" s="87">
         <f>M$4*E8%</f>
-        <v>9945</v>
-      </c>
-      <c r="K8" s="88">
+        <v>21363.333333333332</v>
+      </c>
+      <c r="K8" s="87">
         <f>M$2*E8 /100</f>
         <v>154700</v>
       </c>
-      <c r="L8" s="158"/>
+      <c r="L8" s="234"/>
       <c r="M8" s="6">
         <f>K8+J8+H8+L8</f>
-        <v>163851.27016451582</v>
-      </c>
-      <c r="N8" s="11">
+        <v>175269.60349784917</v>
+      </c>
+      <c r="N8" s="10">
         <f t="shared" ref="N8:N51" si="1">M8*6% + M8</f>
-        <v>173682.34637438678</v>
+        <v>185785.77970772012</v>
       </c>
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.25">
@@ -4151,44 +4179,44 @@
       <c r="C9" s="7">
         <v>25</v>
       </c>
-      <c r="D9" s="132" t="s">
+      <c r="D9" s="128" t="s">
         <v>37</v>
       </c>
       <c r="E9" s="7">
         <v>4.21</v>
       </c>
-      <c r="F9" s="88">
+      <c r="F9" s="87">
         <v>333645.26953426329</v>
       </c>
-      <c r="G9" s="188">
+      <c r="G9" s="181">
         <f>373875-G34</f>
         <v>333645</v>
       </c>
-      <c r="H9" s="130">
+      <c r="H9" s="126">
         <f t="shared" si="0"/>
         <v>0.26953426329419017</v>
       </c>
-      <c r="I9" s="106">
+      <c r="I9" s="105">
         <v>8</v>
       </c>
-      <c r="J9" s="88">
+      <c r="J9" s="87">
         <f t="shared" ref="J9:J51" si="2">M$4*E9%</f>
-        <v>18945</v>
-      </c>
-      <c r="K9" s="88">
+        <v>40696.666666666664</v>
+      </c>
+      <c r="K9" s="87">
         <f t="shared" ref="K9:K51" si="3">M$2*E9 /100</f>
         <v>294700</v>
       </c>
-      <c r="L9" s="245">
+      <c r="L9" s="234">
         <v>10000</v>
       </c>
       <c r="M9" s="6">
         <f t="shared" ref="M9:M51" si="4">K9+J9+H9+L9</f>
-        <v>323645.26953426329</v>
-      </c>
-      <c r="N9" s="11">
+        <v>345396.93620092998</v>
+      </c>
+      <c r="N9" s="10">
         <f t="shared" si="1"/>
-        <v>343063.9857063191</v>
+        <v>366120.75237298576</v>
       </c>
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.25">
@@ -4199,42 +4227,42 @@
       <c r="C10" s="7">
         <v>26</v>
       </c>
-      <c r="D10" s="132" t="s">
+      <c r="D10" s="128" t="s">
         <v>39</v>
       </c>
       <c r="E10" s="7">
         <v>2.84</v>
       </c>
-      <c r="F10" s="88">
+      <c r="F10" s="87">
         <v>211580</v>
       </c>
-      <c r="G10" s="187">
+      <c r="G10" s="180">
         <f>F10</f>
         <v>211580</v>
       </c>
-      <c r="H10" s="130">
+      <c r="H10" s="126">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I10" s="106">
+      <c r="I10" s="105">
         <v>14</v>
       </c>
-      <c r="J10" s="88">
+      <c r="J10" s="87">
         <f t="shared" si="2"/>
-        <v>12780</v>
-      </c>
-      <c r="K10" s="88">
+        <v>27453.333333333332</v>
+      </c>
+      <c r="K10" s="87">
         <f t="shared" si="3"/>
         <v>198800</v>
       </c>
-      <c r="L10" s="158"/>
+      <c r="L10" s="234"/>
       <c r="M10" s="6">
         <f t="shared" si="4"/>
-        <v>211580</v>
-      </c>
-      <c r="N10" s="11">
+        <v>226253.33333333334</v>
+      </c>
+      <c r="N10" s="10">
         <f t="shared" si="1"/>
-        <v>224274.8</v>
+        <v>239828.53333333335</v>
       </c>
     </row>
     <row r="11" spans="1:16" x14ac:dyDescent="0.25">
@@ -4245,44 +4273,44 @@
       <c r="C11" s="7">
         <v>27</v>
       </c>
-      <c r="D11" s="132" t="s">
+      <c r="D11" s="128" t="s">
         <v>40</v>
       </c>
       <c r="E11" s="7">
         <v>3.43</v>
       </c>
-      <c r="F11" s="88">
+      <c r="F11" s="87">
         <v>255535</v>
       </c>
-      <c r="G11" s="187">
+      <c r="G11" s="180">
         <f>F11</f>
         <v>255535</v>
       </c>
-      <c r="H11" s="130">
+      <c r="H11" s="126">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I11" s="106">
+      <c r="I11" s="105">
         <v>7</v>
       </c>
-      <c r="J11" s="88">
+      <c r="J11" s="87">
         <f t="shared" si="2"/>
-        <v>15435.000000000002</v>
-      </c>
-      <c r="K11" s="88">
+        <v>33156.666666666672</v>
+      </c>
+      <c r="K11" s="87">
         <f t="shared" si="3"/>
         <v>240100</v>
       </c>
-      <c r="L11" s="158"/>
+      <c r="L11" s="234"/>
       <c r="M11" s="6">
         <f t="shared" si="4"/>
-        <v>255535</v>
-      </c>
-      <c r="N11" s="11">
+        <v>273256.66666666669</v>
+      </c>
+      <c r="N11" s="10">
         <f t="shared" si="1"/>
-        <v>270867.09999999998</v>
-      </c>
-      <c r="P11" s="108"/>
+        <v>289652.06666666671</v>
+      </c>
+      <c r="P11" s="107"/>
     </row>
     <row r="12" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A12" s="7" t="s">
@@ -4292,42 +4320,42 @@
       <c r="C12" s="7">
         <v>28</v>
       </c>
-      <c r="D12" s="132" t="s">
+      <c r="D12" s="128" t="s">
         <v>111</v>
       </c>
       <c r="E12" s="7">
         <v>2.84</v>
       </c>
-      <c r="F12" s="88">
+      <c r="F12" s="87">
         <v>211580</v>
       </c>
-      <c r="G12" s="188">
+      <c r="G12" s="181">
         <f>F12</f>
         <v>211580</v>
       </c>
-      <c r="H12" s="130">
+      <c r="H12" s="126">
         <f>F12-G12</f>
         <v>0</v>
       </c>
-      <c r="I12" s="106">
+      <c r="I12" s="105">
         <v>13</v>
       </c>
-      <c r="J12" s="88">
+      <c r="J12" s="87">
         <f t="shared" si="2"/>
-        <v>12780</v>
-      </c>
-      <c r="K12" s="88">
+        <v>27453.333333333332</v>
+      </c>
+      <c r="K12" s="87">
         <f t="shared" si="3"/>
         <v>198800</v>
       </c>
-      <c r="L12" s="158"/>
+      <c r="L12" s="234"/>
       <c r="M12" s="6">
         <f t="shared" si="4"/>
-        <v>211580</v>
-      </c>
-      <c r="N12" s="11">
+        <v>226253.33333333334</v>
+      </c>
+      <c r="N12" s="10">
         <f t="shared" si="1"/>
-        <v>224274.8</v>
+        <v>239828.53333333335</v>
       </c>
     </row>
     <row r="13" spans="1:16" x14ac:dyDescent="0.25">
@@ -4338,42 +4366,42 @@
       <c r="C13" s="7">
         <v>29</v>
       </c>
-      <c r="D13" s="132" t="s">
+      <c r="D13" s="128" t="s">
         <v>42</v>
       </c>
       <c r="E13" s="7">
         <v>3.43</v>
       </c>
-      <c r="F13" s="88">
+      <c r="F13" s="87">
         <v>343076.36741924175</v>
       </c>
-      <c r="G13" s="188">
+      <c r="G13" s="181">
         <f>309490-G50</f>
         <v>265535</v>
       </c>
-      <c r="H13" s="130">
+      <c r="H13" s="126">
         <f t="shared" si="0"/>
         <v>77541.367419241753</v>
       </c>
-      <c r="I13" s="106">
+      <c r="I13" s="105">
         <v>9</v>
       </c>
-      <c r="J13" s="88">
+      <c r="J13" s="87">
         <f t="shared" si="2"/>
-        <v>15435.000000000002</v>
-      </c>
-      <c r="K13" s="88">
+        <v>33156.666666666672</v>
+      </c>
+      <c r="K13" s="87">
         <f t="shared" si="3"/>
         <v>240100</v>
       </c>
-      <c r="L13" s="158"/>
+      <c r="L13" s="234"/>
       <c r="M13" s="6">
         <f t="shared" si="4"/>
-        <v>333076.36741924175</v>
-      </c>
-      <c r="N13" s="11">
+        <v>350798.03408590844</v>
+      </c>
+      <c r="N13" s="10">
         <f t="shared" si="1"/>
-        <v>353060.94946439628</v>
+        <v>371845.91613106296</v>
       </c>
     </row>
     <row r="14" spans="1:16" x14ac:dyDescent="0.25">
@@ -4384,43 +4412,43 @@
       <c r="C14" s="7">
         <v>30</v>
       </c>
-      <c r="D14" s="132" t="s">
+      <c r="D14" s="128" t="s">
         <v>44</v>
       </c>
       <c r="E14" s="7">
         <v>2.84</v>
       </c>
-      <c r="F14" s="88">
+      <c r="F14" s="87">
         <v>224274.8</v>
       </c>
-      <c r="G14" s="187">
+      <c r="G14" s="180">
         <v>211580</v>
       </c>
-      <c r="H14" s="130">
+      <c r="H14" s="126">
         <f t="shared" si="0"/>
         <v>12694.799999999988</v>
       </c>
-      <c r="I14" s="106">
+      <c r="I14" s="105">
         <v>17</v>
       </c>
-      <c r="J14" s="88">
+      <c r="J14" s="87">
         <f t="shared" si="2"/>
-        <v>12780</v>
-      </c>
-      <c r="K14" s="88">
+        <v>27453.333333333332</v>
+      </c>
+      <c r="K14" s="87">
         <f t="shared" si="3"/>
         <v>198800</v>
       </c>
-      <c r="L14" s="245">
+      <c r="L14" s="234">
         <v>10000</v>
       </c>
       <c r="M14" s="6">
         <f t="shared" si="4"/>
-        <v>234274.8</v>
-      </c>
-      <c r="N14" s="11">
+        <v>248948.13333333333</v>
+      </c>
+      <c r="N14" s="10">
         <f t="shared" si="1"/>
-        <v>248331.288</v>
+        <v>263885.02133333334</v>
       </c>
     </row>
     <row r="15" spans="1:16" x14ac:dyDescent="0.25">
@@ -4431,42 +4459,42 @@
       <c r="C15" s="7">
         <v>31</v>
       </c>
-      <c r="D15" s="132" t="s">
+      <c r="D15" s="128" t="s">
         <v>140</v>
       </c>
       <c r="E15" s="7">
         <v>3.43</v>
       </c>
-      <c r="F15" s="88">
+      <c r="F15" s="87">
         <v>255535.87099653395</v>
       </c>
-      <c r="G15" s="188">
+      <c r="G15" s="181">
         <f>292786-G35</f>
         <v>255536</v>
       </c>
-      <c r="H15" s="130">
+      <c r="H15" s="126">
         <f t="shared" si="0"/>
         <v>-0.12900346604874358</v>
       </c>
-      <c r="I15" s="106">
+      <c r="I15" s="105">
         <v>6</v>
       </c>
-      <c r="J15" s="88">
+      <c r="J15" s="87">
         <f t="shared" si="2"/>
-        <v>15435.000000000002</v>
-      </c>
-      <c r="K15" s="88">
+        <v>33156.666666666672</v>
+      </c>
+      <c r="K15" s="87">
         <f t="shared" si="3"/>
         <v>240100</v>
       </c>
-      <c r="L15" s="158"/>
+      <c r="L15" s="234"/>
       <c r="M15" s="6">
         <f t="shared" si="4"/>
-        <v>255534.87099653395</v>
-      </c>
-      <c r="N15" s="11">
+        <v>273256.53766320064</v>
+      </c>
+      <c r="N15" s="10">
         <f t="shared" si="1"/>
-        <v>270866.96325632598</v>
+        <v>289651.92992299265</v>
       </c>
     </row>
     <row r="16" spans="1:16" x14ac:dyDescent="0.25">
@@ -4477,42 +4505,42 @@
       <c r="C16" s="7">
         <v>32</v>
       </c>
-      <c r="D16" s="132" t="s">
+      <c r="D16" s="128" t="s">
         <v>136</v>
       </c>
       <c r="E16" s="7">
         <v>2.84</v>
       </c>
-      <c r="F16" s="88">
+      <c r="F16" s="87">
         <v>211579.62795000005</v>
       </c>
-      <c r="G16" s="188">
+      <c r="G16" s="181">
         <f>262969.71-G49</f>
         <v>226464.71000000002</v>
       </c>
-      <c r="H16" s="130">
+      <c r="H16" s="126">
         <f t="shared" si="0"/>
         <v>-14885.082049999968</v>
       </c>
-      <c r="I16" s="106">
+      <c r="I16" s="105">
         <v>13</v>
       </c>
-      <c r="J16" s="88">
+      <c r="J16" s="87">
         <f t="shared" si="2"/>
-        <v>12780</v>
-      </c>
-      <c r="K16" s="88">
+        <v>27453.333333333332</v>
+      </c>
+      <c r="K16" s="87">
         <f t="shared" si="3"/>
         <v>198800</v>
       </c>
-      <c r="L16" s="158"/>
+      <c r="L16" s="234"/>
       <c r="M16" s="6">
         <f t="shared" si="4"/>
-        <v>196694.91795000003</v>
-      </c>
-      <c r="N16" s="11">
+        <v>211368.25128333337</v>
+      </c>
+      <c r="N16" s="10">
         <f t="shared" si="1"/>
-        <v>208496.61302700004</v>
+        <v>224050.34636033338</v>
       </c>
     </row>
     <row r="17" spans="1:18" x14ac:dyDescent="0.25">
@@ -4523,42 +4551,42 @@
       <c r="C17" s="7">
         <v>33</v>
       </c>
-      <c r="D17" s="132" t="s">
+      <c r="D17" s="128" t="s">
         <v>47</v>
       </c>
       <c r="E17" s="7">
         <v>3.43</v>
       </c>
-      <c r="F17" s="88">
+      <c r="F17" s="87">
         <v>265534.97401111474</v>
       </c>
-      <c r="G17" s="187">
+      <c r="G17" s="180">
         <f>339290-G47-G48</f>
         <v>265535</v>
       </c>
-      <c r="H17" s="130">
+      <c r="H17" s="126">
         <f t="shared" si="0"/>
         <v>-2.5988885259721428E-2</v>
       </c>
-      <c r="I17" s="106">
+      <c r="I17" s="105">
         <v>12</v>
       </c>
-      <c r="J17" s="88">
+      <c r="J17" s="87">
         <f t="shared" si="2"/>
-        <v>15435.000000000002</v>
-      </c>
-      <c r="K17" s="88">
+        <v>33156.666666666672</v>
+      </c>
+      <c r="K17" s="87">
         <f t="shared" si="3"/>
         <v>240100</v>
       </c>
-      <c r="L17" s="158"/>
+      <c r="L17" s="234"/>
       <c r="M17" s="6">
         <f t="shared" si="4"/>
-        <v>255534.97401111474</v>
-      </c>
-      <c r="N17" s="11">
+        <v>273256.64067778143</v>
+      </c>
+      <c r="N17" s="10">
         <f t="shared" si="1"/>
-        <v>270867.0724517816</v>
+        <v>289652.03911844833</v>
       </c>
     </row>
     <row r="18" spans="1:18" x14ac:dyDescent="0.25">
@@ -4569,42 +4597,42 @@
       <c r="C18" s="7">
         <v>34</v>
       </c>
-      <c r="D18" s="132" t="s">
+      <c r="D18" s="128" t="s">
         <v>49</v>
       </c>
       <c r="E18" s="7">
         <v>2.84</v>
       </c>
-      <c r="F18" s="88">
+      <c r="F18" s="87">
         <v>210704.42713325133</v>
       </c>
-      <c r="G18" s="187">
+      <c r="G18" s="180">
         <f>260000-G51</f>
         <v>217535</v>
       </c>
-      <c r="H18" s="130">
+      <c r="H18" s="126">
         <f t="shared" si="0"/>
         <v>-6830.5728667486692</v>
       </c>
-      <c r="I18" s="106">
+      <c r="I18" s="105">
         <v>14</v>
       </c>
-      <c r="J18" s="88">
+      <c r="J18" s="87">
         <f t="shared" si="2"/>
-        <v>12780</v>
-      </c>
-      <c r="K18" s="88">
+        <v>27453.333333333332</v>
+      </c>
+      <c r="K18" s="87">
         <f t="shared" si="3"/>
         <v>198800</v>
       </c>
-      <c r="L18" s="158"/>
+      <c r="L18" s="234"/>
       <c r="M18" s="6">
         <f t="shared" si="4"/>
-        <v>204749.42713325133</v>
-      </c>
-      <c r="N18" s="11">
+        <v>219422.76046658467</v>
+      </c>
+      <c r="N18" s="10">
         <f t="shared" si="1"/>
-        <v>217034.39276124642</v>
+        <v>232588.12609457975</v>
       </c>
     </row>
     <row r="19" spans="1:18" x14ac:dyDescent="0.25">
@@ -4615,42 +4643,42 @@
       <c r="C19" s="7">
         <v>35</v>
       </c>
-      <c r="D19" s="132" t="s">
+      <c r="D19" s="128" t="s">
         <v>50</v>
       </c>
       <c r="E19" s="7">
         <v>3.43</v>
       </c>
-      <c r="F19" s="88">
+      <c r="F19" s="87">
         <v>255535.48631516803</v>
       </c>
-      <c r="G19" s="188">
+      <c r="G19" s="181">
         <f>295765-G41</f>
         <v>255535</v>
       </c>
-      <c r="H19" s="130">
+      <c r="H19" s="126">
         <f t="shared" si="0"/>
         <v>0.48631516803288832</v>
       </c>
-      <c r="I19" s="106">
+      <c r="I19" s="105">
         <v>6</v>
       </c>
-      <c r="J19" s="88">
+      <c r="J19" s="87">
         <f t="shared" si="2"/>
-        <v>15435.000000000002</v>
-      </c>
-      <c r="K19" s="88">
+        <v>33156.666666666672</v>
+      </c>
+      <c r="K19" s="87">
         <f t="shared" si="3"/>
         <v>240100</v>
       </c>
-      <c r="L19" s="158"/>
+      <c r="L19" s="234"/>
       <c r="M19" s="6">
         <f t="shared" si="4"/>
-        <v>255535.48631516803</v>
-      </c>
-      <c r="N19" s="11">
+        <v>273257.15298183472</v>
+      </c>
+      <c r="N19" s="10">
         <f t="shared" si="1"/>
-        <v>270867.61549407814</v>
+        <v>289652.58216074482</v>
       </c>
     </row>
     <row r="20" spans="1:18" x14ac:dyDescent="0.25">
@@ -4661,42 +4689,42 @@
       <c r="C20" s="7">
         <v>36</v>
       </c>
-      <c r="D20" s="132" t="s">
+      <c r="D20" s="128" t="s">
         <v>52</v>
       </c>
       <c r="E20" s="7">
         <v>2.84</v>
       </c>
-      <c r="F20" s="88">
+      <c r="F20" s="87">
         <v>211579.65585707471</v>
       </c>
-      <c r="G20" s="187">
+      <c r="G20" s="180">
         <f>248085-G38</f>
         <v>211580</v>
       </c>
-      <c r="H20" s="130">
+      <c r="H20" s="126">
         <f t="shared" si="0"/>
         <v>-0.34414292528526857</v>
       </c>
-      <c r="I20" s="106">
+      <c r="I20" s="105">
         <v>6</v>
       </c>
-      <c r="J20" s="88">
+      <c r="J20" s="87">
         <f t="shared" si="2"/>
-        <v>12780</v>
-      </c>
-      <c r="K20" s="88">
+        <v>27453.333333333332</v>
+      </c>
+      <c r="K20" s="87">
         <f t="shared" si="3"/>
         <v>198800</v>
       </c>
-      <c r="L20" s="158"/>
+      <c r="L20" s="234"/>
       <c r="M20" s="6">
         <f t="shared" si="4"/>
-        <v>211579.65585707471</v>
-      </c>
-      <c r="N20" s="11">
+        <v>226252.98919040806</v>
+      </c>
+      <c r="N20" s="10">
         <f t="shared" si="1"/>
-        <v>224274.4352084992</v>
+        <v>239828.16854183254</v>
       </c>
     </row>
     <row r="21" spans="1:18" x14ac:dyDescent="0.25">
@@ -4707,42 +4735,42 @@
       <c r="C21" s="7">
         <v>37</v>
       </c>
-      <c r="D21" s="132" t="s">
+      <c r="D21" s="128" t="s">
         <v>53</v>
       </c>
       <c r="E21" s="7">
         <v>3.43</v>
       </c>
-      <c r="F21" s="88">
+      <c r="F21" s="87">
         <v>255534.8886417959</v>
       </c>
-      <c r="G21" s="187">
+      <c r="G21" s="180">
         <f>295765-G45</f>
         <v>255535</v>
       </c>
-      <c r="H21" s="130">
+      <c r="H21" s="126">
         <f t="shared" si="0"/>
         <v>-0.11135820409981534</v>
       </c>
-      <c r="I21" s="106">
+      <c r="I21" s="105">
         <v>6</v>
       </c>
-      <c r="J21" s="88">
+      <c r="J21" s="87">
         <f t="shared" si="2"/>
-        <v>15435.000000000002</v>
-      </c>
-      <c r="K21" s="88">
+        <v>33156.666666666672</v>
+      </c>
+      <c r="K21" s="87">
         <f t="shared" si="3"/>
         <v>240100</v>
       </c>
-      <c r="L21" s="158"/>
+      <c r="L21" s="234"/>
       <c r="M21" s="6">
         <f t="shared" si="4"/>
-        <v>255534.8886417959</v>
-      </c>
-      <c r="N21" s="11">
+        <v>273256.55530846259</v>
+      </c>
+      <c r="N21" s="10">
         <f t="shared" si="1"/>
-        <v>270866.98196030367</v>
+        <v>289651.94862697035</v>
       </c>
     </row>
     <row r="22" spans="1:18" x14ac:dyDescent="0.25">
@@ -4753,42 +4781,42 @@
       <c r="C22" s="7">
         <v>38</v>
       </c>
-      <c r="D22" s="159" t="s">
+      <c r="D22" s="152" t="s">
         <v>128</v>
       </c>
       <c r="E22" s="7">
         <v>2.84</v>
       </c>
-      <c r="F22" s="88">
+      <c r="F22" s="87">
         <v>211580</v>
       </c>
-      <c r="G22" s="187">
+      <c r="G22" s="180">
         <f>F22</f>
         <v>211580</v>
       </c>
-      <c r="H22" s="130">
+      <c r="H22" s="126">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I22" s="106">
+      <c r="I22" s="105">
         <v>6</v>
       </c>
-      <c r="J22" s="88">
+      <c r="J22" s="87">
         <f t="shared" si="2"/>
-        <v>12780</v>
-      </c>
-      <c r="K22" s="88">
+        <v>27453.333333333332</v>
+      </c>
+      <c r="K22" s="87">
         <f t="shared" si="3"/>
         <v>198800</v>
       </c>
-      <c r="L22" s="158"/>
+      <c r="L22" s="234"/>
       <c r="M22" s="6">
         <f t="shared" si="4"/>
-        <v>211580</v>
-      </c>
-      <c r="N22" s="11">
+        <v>226253.33333333334</v>
+      </c>
+      <c r="N22" s="10">
         <f t="shared" si="1"/>
-        <v>224274.8</v>
+        <v>239828.53333333335</v>
       </c>
     </row>
     <row r="23" spans="1:18" x14ac:dyDescent="0.25">
@@ -4799,42 +4827,42 @@
       <c r="C23" s="7">
         <v>39</v>
       </c>
-      <c r="D23" s="132" t="s">
+      <c r="D23" s="128" t="s">
         <v>55</v>
       </c>
       <c r="E23" s="7">
         <v>3.43</v>
       </c>
-      <c r="F23" s="88">
+      <c r="F23" s="87">
         <v>320475.29717285704</v>
       </c>
-      <c r="G23" s="188">
+      <c r="G23" s="181">
         <f>361000-G46</f>
         <v>323750</v>
       </c>
-      <c r="H23" s="130">
+      <c r="H23" s="126">
         <f t="shared" si="0"/>
         <v>-3274.702827142959</v>
       </c>
-      <c r="I23" s="106">
+      <c r="I23" s="105">
         <v>23</v>
       </c>
-      <c r="J23" s="88">
+      <c r="J23" s="87">
         <f t="shared" si="2"/>
-        <v>15435.000000000002</v>
-      </c>
-      <c r="K23" s="88">
+        <v>33156.666666666672</v>
+      </c>
+      <c r="K23" s="87">
         <f t="shared" si="3"/>
         <v>240100</v>
       </c>
-      <c r="L23" s="158"/>
+      <c r="L23" s="234"/>
       <c r="M23" s="6">
         <f t="shared" si="4"/>
-        <v>252260.29717285704</v>
-      </c>
-      <c r="N23" s="11">
+        <v>269981.96383952373</v>
+      </c>
+      <c r="N23" s="10">
         <f t="shared" si="1"/>
-        <v>267395.91500322847</v>
+        <v>286180.88166989514</v>
       </c>
     </row>
     <row r="24" spans="1:18" x14ac:dyDescent="0.25">
@@ -4845,42 +4873,42 @@
       <c r="C24" s="7">
         <v>40</v>
       </c>
-      <c r="D24" s="132" t="s">
+      <c r="D24" s="128" t="s">
         <v>57</v>
       </c>
       <c r="E24" s="7">
         <v>2.84</v>
       </c>
-      <c r="F24" s="88">
+      <c r="F24" s="87">
         <v>221580.37342107471</v>
       </c>
-      <c r="G24" s="187">
+      <c r="G24" s="180">
         <f>259000-G37</f>
         <v>222495</v>
       </c>
-      <c r="H24" s="130">
+      <c r="H24" s="126">
         <f t="shared" si="0"/>
         <v>-914.62657892529387</v>
       </c>
-      <c r="I24" s="169">
+      <c r="I24" s="162">
         <v>9</v>
       </c>
-      <c r="J24" s="88">
+      <c r="J24" s="87">
         <f t="shared" si="2"/>
-        <v>12780</v>
-      </c>
-      <c r="K24" s="88">
+        <v>27453.333333333332</v>
+      </c>
+      <c r="K24" s="87">
         <f t="shared" si="3"/>
         <v>198800</v>
       </c>
-      <c r="L24" s="158"/>
+      <c r="L24" s="234"/>
       <c r="M24" s="6">
         <f t="shared" si="4"/>
-        <v>210665.37342107471</v>
-      </c>
-      <c r="N24" s="11">
+        <v>225338.70675440805</v>
+      </c>
+      <c r="N24" s="10">
         <f t="shared" si="1"/>
-        <v>223305.29582633919</v>
+        <v>238859.02915967253</v>
       </c>
     </row>
     <row r="25" spans="1:18" x14ac:dyDescent="0.25">
@@ -4891,49 +4919,49 @@
       <c r="C25" s="7">
         <v>41</v>
       </c>
-      <c r="D25" s="132" t="s">
+      <c r="D25" s="128" t="s">
         <v>58</v>
       </c>
       <c r="E25" s="7">
         <v>3.43</v>
       </c>
-      <c r="F25" s="88">
+      <c r="F25" s="87">
         <v>255535</v>
       </c>
-      <c r="G25" s="187">
+      <c r="G25" s="180">
         <f>F25</f>
         <v>255535</v>
       </c>
-      <c r="H25" s="130">
+      <c r="H25" s="126">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I25" s="106">
+      <c r="I25" s="105">
         <v>11</v>
       </c>
-      <c r="J25" s="88">
+      <c r="J25" s="87">
         <f t="shared" si="2"/>
-        <v>15435.000000000002</v>
-      </c>
-      <c r="K25" s="88">
+        <v>33156.666666666672</v>
+      </c>
+      <c r="K25" s="87">
         <f t="shared" si="3"/>
         <v>240100</v>
       </c>
-      <c r="L25" s="246">
+      <c r="L25" s="235">
         <f>77229+250000+38000+(((K25+J25)*0.5))*6</f>
-        <v>1131834</v>
+        <v>1184999</v>
       </c>
       <c r="M25" s="6">
         <f t="shared" si="4"/>
-        <v>1387369</v>
-      </c>
-      <c r="N25" s="11">
+        <v>1458255.6666666667</v>
+      </c>
+      <c r="N25" s="10">
         <f t="shared" si="1"/>
-        <v>1470611.14</v>
-      </c>
-      <c r="P25" s="137"/>
-      <c r="Q25" s="137"/>
-      <c r="R25" s="137"/>
+        <v>1545751.0066666668</v>
+      </c>
+      <c r="P25" s="133"/>
+      <c r="Q25" s="133"/>
+      <c r="R25" s="133"/>
     </row>
     <row r="26" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A26" s="7" t="s">
@@ -4943,42 +4971,42 @@
       <c r="C26" s="7">
         <v>42</v>
       </c>
-      <c r="D26" s="132" t="s">
+      <c r="D26" s="128" t="s">
         <v>60</v>
       </c>
       <c r="E26" s="7">
         <v>6</v>
       </c>
-      <c r="F26" s="88">
+      <c r="F26" s="87">
         <v>-434833.00733396295</v>
       </c>
-      <c r="G26" s="188">
+      <c r="G26" s="181">
         <f>-G36-G30-G31</f>
         <v>-118455</v>
       </c>
-      <c r="H26" s="131">
+      <c r="H26" s="127">
         <f t="shared" si="0"/>
         <v>-316378.00733396295</v>
       </c>
-      <c r="I26" s="106">
+      <c r="I26" s="105">
         <v>2</v>
       </c>
-      <c r="J26" s="88">
+      <c r="J26" s="87">
         <f t="shared" si="2"/>
-        <v>27000</v>
-      </c>
-      <c r="K26" s="88">
+        <v>57999.999999999993</v>
+      </c>
+      <c r="K26" s="87">
         <f t="shared" si="3"/>
         <v>420000</v>
       </c>
-      <c r="L26" s="158"/>
+      <c r="L26" s="234"/>
       <c r="M26" s="6">
         <f t="shared" si="4"/>
-        <v>130621.99266603705</v>
-      </c>
-      <c r="N26" s="11">
+        <v>161621.99266603705</v>
+      </c>
+      <c r="N26" s="10">
         <f t="shared" si="1"/>
-        <v>138459.31222599928</v>
+        <v>171319.31222599928</v>
       </c>
     </row>
     <row r="27" spans="1:18" x14ac:dyDescent="0.25">
@@ -4989,44 +5017,44 @@
       <c r="C27" s="7">
         <v>43</v>
       </c>
-      <c r="D27" s="132" t="s">
+      <c r="D27" s="128" t="s">
         <v>62</v>
       </c>
       <c r="E27" s="7">
         <v>5.89</v>
       </c>
-      <c r="F27" s="88">
+      <c r="F27" s="87">
         <v>438805.37128526543</v>
       </c>
-      <c r="G27" s="187">
+      <c r="G27" s="180">
         <f>520005-G39-G40</f>
         <v>433585</v>
       </c>
-      <c r="H27" s="130">
+      <c r="H27" s="126">
         <f t="shared" si="0"/>
         <v>5220.371285265428</v>
       </c>
-      <c r="I27" s="106">
+      <c r="I27" s="105">
         <v>11</v>
       </c>
-      <c r="J27" s="88">
+      <c r="J27" s="87">
         <f t="shared" si="2"/>
-        <v>26504.999999999996</v>
-      </c>
-      <c r="K27" s="88">
+        <v>56936.666666666657</v>
+      </c>
+      <c r="K27" s="87">
         <f t="shared" si="3"/>
         <v>412300</v>
       </c>
-      <c r="L27" s="158"/>
+      <c r="L27" s="234"/>
       <c r="M27" s="6">
         <f t="shared" si="4"/>
-        <v>444025.37128526543</v>
-      </c>
-      <c r="N27" s="11">
+        <v>474457.03795193206</v>
+      </c>
+      <c r="N27" s="10">
         <f t="shared" si="1"/>
-        <v>470666.89356238133</v>
-      </c>
-      <c r="R27" s="137"/>
+        <v>502924.46022904798</v>
+      </c>
+      <c r="R27" s="133"/>
     </row>
     <row r="28" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A28" s="7" t="s">
@@ -5036,42 +5064,42 @@
       <c r="C28" s="7">
         <v>44</v>
       </c>
-      <c r="D28" s="132" t="s">
+      <c r="D28" s="128" t="s">
         <v>64</v>
       </c>
       <c r="E28" s="7">
         <v>5.89</v>
       </c>
-      <c r="F28" s="88">
+      <c r="F28" s="87">
         <v>438804.50782654097</v>
       </c>
-      <c r="G28" s="187">
+      <c r="G28" s="180">
         <f>518000-G32-G33</f>
         <v>439030</v>
       </c>
-      <c r="H28" s="130">
+      <c r="H28" s="126">
         <f t="shared" si="0"/>
         <v>-225.49217345903162</v>
       </c>
-      <c r="I28" s="106">
+      <c r="I28" s="105">
         <v>6</v>
       </c>
-      <c r="J28" s="88">
+      <c r="J28" s="87">
         <f t="shared" si="2"/>
-        <v>26504.999999999996</v>
-      </c>
-      <c r="K28" s="88">
+        <v>56936.666666666657</v>
+      </c>
+      <c r="K28" s="87">
         <f t="shared" si="3"/>
         <v>412300</v>
       </c>
-      <c r="L28" s="158"/>
+      <c r="L28" s="234"/>
       <c r="M28" s="6">
         <f t="shared" si="4"/>
-        <v>438579.50782654097</v>
-      </c>
-      <c r="N28" s="11">
+        <v>469011.1744932076</v>
+      </c>
+      <c r="N28" s="10">
         <f t="shared" si="1"/>
-        <v>464894.27829613345</v>
+        <v>497151.84496280004</v>
       </c>
     </row>
     <row r="29" spans="1:18" x14ac:dyDescent="0.25">
@@ -5082,1221 +5110,1216 @@
       <c r="C29" s="7">
         <v>45</v>
       </c>
-      <c r="D29" s="132" t="s">
+      <c r="D29" s="128" t="s">
         <v>66</v>
       </c>
       <c r="E29" s="7">
         <v>5.89</v>
       </c>
-      <c r="F29" s="88">
+      <c r="F29" s="87">
         <v>438609.70395670005</v>
       </c>
-      <c r="G29" s="188">
+      <c r="G29" s="181">
         <f>558645-G42-G43-G44</f>
         <v>438700</v>
       </c>
-      <c r="H29" s="131">
+      <c r="H29" s="127">
         <f t="shared" si="0"/>
         <v>-90.296043299953453</v>
       </c>
-      <c r="I29" s="106">
+      <c r="I29" s="105">
         <v>7</v>
       </c>
-      <c r="J29" s="88">
+      <c r="J29" s="87">
         <f t="shared" si="2"/>
-        <v>26504.999999999996</v>
-      </c>
-      <c r="K29" s="88">
+        <v>56936.666666666657</v>
+      </c>
+      <c r="K29" s="87">
         <f t="shared" si="3"/>
         <v>412300</v>
       </c>
-      <c r="L29" s="158"/>
+      <c r="L29" s="234"/>
       <c r="M29" s="6">
         <f t="shared" si="4"/>
-        <v>438714.70395670005</v>
-      </c>
-      <c r="N29" s="11">
+        <v>469146.37062336667</v>
+      </c>
+      <c r="N29" s="10">
         <f t="shared" si="1"/>
-        <v>465037.58619410207</v>
+        <v>497295.15286076866</v>
       </c>
     </row>
     <row r="30" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A30" s="125" t="s">
+      <c r="A30" s="122" t="s">
         <v>96</v>
       </c>
       <c r="B30" s="7"/>
       <c r="C30" s="7">
         <v>1</v>
       </c>
-      <c r="D30" s="132" t="s">
+      <c r="D30" s="128" t="s">
         <v>60</v>
       </c>
       <c r="E30" s="7">
         <v>0.54</v>
       </c>
-      <c r="F30" s="88">
+      <c r="F30" s="87">
         <v>40230.000000000007</v>
       </c>
-      <c r="G30" s="187">
+      <c r="G30" s="180">
         <f>F30</f>
         <v>40230.000000000007</v>
       </c>
-      <c r="H30" s="130">
+      <c r="H30" s="126">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I30" s="106"/>
-      <c r="J30" s="88">
+      <c r="I30" s="105"/>
+      <c r="J30" s="87">
         <f t="shared" si="2"/>
-        <v>2430</v>
-      </c>
-      <c r="K30" s="88">
+        <v>5220</v>
+      </c>
+      <c r="K30" s="87">
         <f t="shared" si="3"/>
         <v>37800.000000000007</v>
       </c>
-      <c r="L30" s="158"/>
+      <c r="L30" s="234"/>
       <c r="M30" s="6">
         <f t="shared" si="4"/>
-        <v>40230.000000000007</v>
-      </c>
-      <c r="N30" s="11">
+        <v>43020.000000000007</v>
+      </c>
+      <c r="N30" s="10">
         <f t="shared" si="1"/>
-        <v>42643.80000000001</v>
+        <v>45601.200000000004</v>
       </c>
     </row>
     <row r="31" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A31" s="125" t="s">
+      <c r="A31" s="122" t="s">
         <v>96</v>
       </c>
       <c r="B31" s="7"/>
       <c r="C31" s="7">
         <v>2</v>
       </c>
-      <c r="D31" s="132" t="s">
+      <c r="D31" s="128" t="s">
         <v>60</v>
       </c>
       <c r="E31" s="7">
         <v>0.55000000000000004</v>
       </c>
-      <c r="F31" s="88">
+      <c r="F31" s="87">
         <v>40975.000000000007</v>
       </c>
-      <c r="G31" s="187">
+      <c r="G31" s="180">
         <f>F31</f>
         <v>40975.000000000007</v>
       </c>
-      <c r="H31" s="130">
+      <c r="H31" s="126">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I31" s="106"/>
-      <c r="J31" s="88">
+      <c r="I31" s="105"/>
+      <c r="J31" s="87">
         <f t="shared" si="2"/>
-        <v>2475.0000000000005</v>
-      </c>
-      <c r="K31" s="88">
+        <v>5316.666666666667</v>
+      </c>
+      <c r="K31" s="87">
         <f t="shared" si="3"/>
         <v>38500.000000000007</v>
       </c>
-      <c r="L31" s="158"/>
+      <c r="L31" s="234"/>
       <c r="M31" s="6">
         <f t="shared" si="4"/>
-        <v>40975.000000000007</v>
-      </c>
-      <c r="N31" s="11">
+        <v>43816.666666666672</v>
+      </c>
+      <c r="N31" s="10">
         <f t="shared" si="1"/>
-        <v>43433.500000000007</v>
+        <v>46445.666666666672</v>
       </c>
     </row>
     <row r="32" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A32" s="125" t="s">
+      <c r="A32" s="122" t="s">
         <v>96</v>
       </c>
       <c r="B32" s="7"/>
       <c r="C32" s="7">
         <v>3</v>
       </c>
-      <c r="D32" s="132" t="s">
+      <c r="D32" s="128" t="s">
         <v>64</v>
       </c>
       <c r="E32" s="7">
         <v>0.45</v>
       </c>
-      <c r="F32" s="88">
+      <c r="F32" s="87">
         <v>33525</v>
       </c>
-      <c r="G32" s="187">
+      <c r="G32" s="180">
         <f>F32</f>
         <v>33525</v>
       </c>
-      <c r="H32" s="130">
+      <c r="H32" s="126">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I32" s="106"/>
-      <c r="J32" s="88">
+      <c r="I32" s="105"/>
+      <c r="J32" s="87">
         <f t="shared" si="2"/>
-        <v>2025.0000000000002</v>
-      </c>
-      <c r="K32" s="88">
+        <v>4350</v>
+      </c>
+      <c r="K32" s="87">
         <f t="shared" si="3"/>
         <v>31500</v>
       </c>
-      <c r="L32" s="158"/>
+      <c r="L32" s="151"/>
       <c r="M32" s="6">
         <f t="shared" si="4"/>
-        <v>33525</v>
-      </c>
-      <c r="N32" s="11">
+        <v>35850</v>
+      </c>
+      <c r="N32" s="10">
         <f t="shared" si="1"/>
-        <v>35536.5</v>
+        <v>38001</v>
       </c>
     </row>
     <row r="33" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A33" s="125" t="s">
+      <c r="A33" s="122" t="s">
         <v>96</v>
       </c>
       <c r="B33" s="7"/>
       <c r="C33" s="7">
         <v>4</v>
       </c>
-      <c r="D33" s="132" t="s">
+      <c r="D33" s="128" t="s">
         <v>64</v>
       </c>
       <c r="E33" s="7">
         <v>0.61</v>
       </c>
-      <c r="F33" s="88">
+      <c r="F33" s="87">
         <v>45445</v>
       </c>
-      <c r="G33" s="187">
-        <f t="shared" ref="G30:G34" si="5">F33</f>
+      <c r="G33" s="180">
+        <f t="shared" ref="G33:G34" si="5">F33</f>
         <v>45445</v>
       </c>
-      <c r="H33" s="130">
+      <c r="H33" s="126">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I33" s="106"/>
-      <c r="J33" s="88">
+      <c r="I33" s="105"/>
+      <c r="J33" s="87">
         <f t="shared" si="2"/>
-        <v>2745</v>
-      </c>
-      <c r="K33" s="88">
+        <v>5896.6666666666661</v>
+      </c>
+      <c r="K33" s="87">
         <f t="shared" si="3"/>
         <v>42700</v>
       </c>
-      <c r="L33" s="158"/>
+      <c r="L33" s="151"/>
       <c r="M33" s="6">
         <f t="shared" si="4"/>
-        <v>45445</v>
-      </c>
-      <c r="N33" s="11">
+        <v>48596.666666666664</v>
+      </c>
+      <c r="N33" s="10">
         <f t="shared" si="1"/>
-        <v>48171.7</v>
+        <v>51512.466666666667</v>
       </c>
     </row>
     <row r="34" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A34" s="125" t="s">
+      <c r="A34" s="122" t="s">
         <v>96</v>
       </c>
       <c r="B34" s="7"/>
       <c r="C34" s="7">
         <v>5</v>
       </c>
-      <c r="D34" s="132" t="s">
+      <c r="D34" s="128" t="s">
         <v>37</v>
       </c>
       <c r="E34" s="7">
         <v>0.54</v>
       </c>
-      <c r="F34" s="88">
+      <c r="F34" s="87">
         <v>40230.000000000007</v>
       </c>
-      <c r="G34" s="187">
+      <c r="G34" s="180">
         <f t="shared" si="5"/>
         <v>40230.000000000007</v>
       </c>
-      <c r="H34" s="130">
+      <c r="H34" s="126">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I34" s="106"/>
-      <c r="J34" s="88">
+      <c r="I34" s="105"/>
+      <c r="J34" s="87">
         <f t="shared" si="2"/>
-        <v>2430</v>
-      </c>
-      <c r="K34" s="88">
+        <v>5220</v>
+      </c>
+      <c r="K34" s="87">
         <f t="shared" si="3"/>
         <v>37800.000000000007</v>
       </c>
-      <c r="L34" s="158"/>
+      <c r="L34" s="151"/>
       <c r="M34" s="6">
         <f t="shared" si="4"/>
-        <v>40230.000000000007</v>
-      </c>
-      <c r="N34" s="11">
+        <v>43020.000000000007</v>
+      </c>
+      <c r="N34" s="10">
         <f t="shared" si="1"/>
-        <v>42643.80000000001</v>
+        <v>45601.200000000004</v>
       </c>
     </row>
     <row r="35" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A35" s="125" t="s">
+      <c r="A35" s="122" t="s">
         <v>96</v>
       </c>
       <c r="B35" s="7"/>
       <c r="C35" s="7">
         <v>6</v>
       </c>
-      <c r="D35" s="132" t="s">
+      <c r="D35" s="128" t="s">
         <v>140</v>
       </c>
       <c r="E35" s="7">
         <v>0.5</v>
       </c>
-      <c r="F35" s="11">
+      <c r="F35" s="10">
         <v>37250</v>
       </c>
-      <c r="G35" s="188">
+      <c r="G35" s="181">
         <f>F35</f>
         <v>37250</v>
       </c>
-      <c r="H35" s="130">
+      <c r="H35" s="126">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I35" s="106"/>
-      <c r="J35" s="88">
+      <c r="I35" s="105"/>
+      <c r="J35" s="87">
         <f t="shared" si="2"/>
-        <v>2250</v>
-      </c>
-      <c r="K35" s="88">
+        <v>4833.333333333333</v>
+      </c>
+      <c r="K35" s="87">
         <f t="shared" si="3"/>
         <v>35000</v>
       </c>
-      <c r="L35" s="158"/>
+      <c r="L35" s="151"/>
       <c r="M35" s="6">
         <f t="shared" si="4"/>
-        <v>37250</v>
-      </c>
-      <c r="N35" s="11">
+        <v>39833.333333333336</v>
+      </c>
+      <c r="N35" s="10">
         <f t="shared" si="1"/>
-        <v>39485</v>
+        <v>42223.333333333336</v>
       </c>
     </row>
     <row r="36" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A36" s="125" t="s">
+      <c r="A36" s="122" t="s">
         <v>96</v>
       </c>
       <c r="B36" s="7"/>
       <c r="C36" s="7">
         <v>7</v>
       </c>
-      <c r="D36" s="132" t="s">
+      <c r="D36" s="128" t="s">
         <v>60</v>
       </c>
       <c r="E36" s="7">
         <v>0.5</v>
       </c>
-      <c r="F36" s="88">
+      <c r="F36" s="87">
         <v>37250</v>
       </c>
-      <c r="G36" s="187">
+      <c r="G36" s="180">
         <f>F36</f>
         <v>37250</v>
       </c>
-      <c r="H36" s="130">
+      <c r="H36" s="126">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I36" s="106"/>
-      <c r="J36" s="88">
+      <c r="I36" s="105"/>
+      <c r="J36" s="87">
         <f t="shared" si="2"/>
-        <v>2250</v>
-      </c>
-      <c r="K36" s="88">
+        <v>4833.333333333333</v>
+      </c>
+      <c r="K36" s="87">
         <f t="shared" si="3"/>
         <v>35000</v>
       </c>
-      <c r="L36" s="158"/>
+      <c r="L36" s="151"/>
       <c r="M36" s="6">
         <f t="shared" si="4"/>
-        <v>37250</v>
-      </c>
-      <c r="N36" s="11">
+        <v>39833.333333333336</v>
+      </c>
+      <c r="N36" s="10">
         <f t="shared" si="1"/>
-        <v>39485</v>
+        <v>42223.333333333336</v>
       </c>
     </row>
     <row r="37" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A37" s="125" t="s">
+      <c r="A37" s="122" t="s">
         <v>96</v>
       </c>
       <c r="B37" s="7"/>
       <c r="C37" s="7">
         <v>8</v>
       </c>
-      <c r="D37" s="132" t="s">
+      <c r="D37" s="128" t="s">
         <v>57</v>
       </c>
       <c r="E37" s="7">
         <v>0.49</v>
       </c>
-      <c r="F37" s="88">
+      <c r="F37" s="87">
         <v>36505</v>
       </c>
-      <c r="G37" s="187">
-        <f t="shared" ref="G36:G41" si="6">F37</f>
+      <c r="G37" s="180">
+        <f t="shared" ref="G37:G41" si="6">F37</f>
         <v>36505</v>
       </c>
-      <c r="H37" s="130">
+      <c r="H37" s="126">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I37" s="106"/>
-      <c r="J37" s="88">
+      <c r="I37" s="105"/>
+      <c r="J37" s="87">
         <f t="shared" si="2"/>
-        <v>2205</v>
-      </c>
-      <c r="K37" s="88">
+        <v>4736.6666666666661</v>
+      </c>
+      <c r="K37" s="87">
         <f t="shared" si="3"/>
         <v>34300</v>
       </c>
-      <c r="L37" s="158"/>
+      <c r="L37" s="151"/>
       <c r="M37" s="6">
         <f t="shared" si="4"/>
-        <v>36505</v>
-      </c>
-      <c r="N37" s="11">
+        <v>39036.666666666664</v>
+      </c>
+      <c r="N37" s="10">
         <f t="shared" si="1"/>
-        <v>38695.300000000003</v>
+        <v>41378.866666666661</v>
       </c>
     </row>
     <row r="38" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A38" s="125" t="s">
+      <c r="A38" s="122" t="s">
         <v>96</v>
       </c>
       <c r="B38" s="7"/>
       <c r="C38" s="7">
         <v>9</v>
       </c>
-      <c r="D38" s="132" t="s">
+      <c r="D38" s="128" t="s">
         <v>52</v>
       </c>
       <c r="E38" s="7">
         <v>0.49</v>
       </c>
-      <c r="F38" s="88">
+      <c r="F38" s="87">
         <v>36505</v>
       </c>
-      <c r="G38" s="187">
+      <c r="G38" s="180">
         <f t="shared" si="6"/>
         <v>36505</v>
       </c>
-      <c r="H38" s="130">
+      <c r="H38" s="126">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I38" s="106"/>
-      <c r="J38" s="88">
+      <c r="I38" s="105"/>
+      <c r="J38" s="87">
         <f t="shared" si="2"/>
-        <v>2205</v>
-      </c>
-      <c r="K38" s="88">
+        <v>4736.6666666666661</v>
+      </c>
+      <c r="K38" s="87">
         <f t="shared" si="3"/>
         <v>34300</v>
       </c>
-      <c r="L38" s="158"/>
+      <c r="L38" s="151"/>
       <c r="M38" s="6">
         <f t="shared" si="4"/>
-        <v>36505</v>
-      </c>
-      <c r="N38" s="11">
+        <v>39036.666666666664</v>
+      </c>
+      <c r="N38" s="10">
         <f t="shared" si="1"/>
-        <v>38695.300000000003</v>
+        <v>41378.866666666661</v>
       </c>
     </row>
     <row r="39" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A39" s="125" t="s">
+      <c r="A39" s="122" t="s">
         <v>96</v>
       </c>
       <c r="B39" s="7"/>
       <c r="C39" s="7">
         <v>10</v>
       </c>
-      <c r="D39" s="132" t="s">
+      <c r="D39" s="128" t="s">
         <v>62</v>
       </c>
       <c r="E39" s="7">
         <v>0.59</v>
       </c>
-      <c r="F39" s="88">
+      <c r="F39" s="87">
         <v>43955</v>
       </c>
-      <c r="G39" s="187">
+      <c r="G39" s="180">
         <f t="shared" si="6"/>
         <v>43955</v>
       </c>
-      <c r="H39" s="130">
+      <c r="H39" s="126">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I39" s="106"/>
-      <c r="J39" s="88">
+      <c r="I39" s="105"/>
+      <c r="J39" s="87">
         <f t="shared" si="2"/>
-        <v>2655</v>
-      </c>
-      <c r="K39" s="88">
+        <v>5703.333333333333</v>
+      </c>
+      <c r="K39" s="87">
         <f t="shared" si="3"/>
         <v>41300</v>
       </c>
-      <c r="L39" s="158"/>
+      <c r="L39" s="151"/>
       <c r="M39" s="6">
         <f t="shared" si="4"/>
-        <v>43955</v>
-      </c>
-      <c r="N39" s="11">
+        <v>47003.333333333336</v>
+      </c>
+      <c r="N39" s="10">
         <f t="shared" si="1"/>
-        <v>46592.3</v>
+        <v>49823.533333333333</v>
       </c>
     </row>
     <row r="40" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A40" s="125" t="s">
+      <c r="A40" s="122" t="s">
         <v>96</v>
       </c>
       <c r="B40" s="7"/>
       <c r="C40" s="7">
         <v>11</v>
       </c>
-      <c r="D40" s="132" t="s">
+      <c r="D40" s="128" t="s">
         <v>62</v>
       </c>
       <c r="E40" s="7">
         <v>0.56999999999999995</v>
       </c>
-      <c r="F40" s="88">
+      <c r="F40" s="87">
         <v>42464.999999999993</v>
       </c>
-      <c r="G40" s="187">
+      <c r="G40" s="180">
         <f t="shared" si="6"/>
         <v>42464.999999999993</v>
       </c>
-      <c r="H40" s="130">
+      <c r="H40" s="126">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I40" s="106"/>
-      <c r="J40" s="88">
+      <c r="I40" s="105"/>
+      <c r="J40" s="87">
         <f t="shared" si="2"/>
-        <v>2564.9999999999995</v>
-      </c>
-      <c r="K40" s="88">
+        <v>5509.9999999999991</v>
+      </c>
+      <c r="K40" s="87">
         <f t="shared" si="3"/>
         <v>39899.999999999993</v>
       </c>
-      <c r="L40" s="158"/>
+      <c r="L40" s="151"/>
       <c r="M40" s="6">
         <f t="shared" si="4"/>
-        <v>42464.999999999993</v>
-      </c>
-      <c r="N40" s="11">
+        <v>45409.999999999993</v>
+      </c>
+      <c r="N40" s="10">
         <f t="shared" si="1"/>
-        <v>45012.899999999994</v>
+        <v>48134.599999999991</v>
       </c>
     </row>
     <row r="41" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A41" s="125" t="s">
+      <c r="A41" s="122" t="s">
         <v>96</v>
       </c>
       <c r="B41" s="7"/>
       <c r="C41" s="7">
         <v>12</v>
       </c>
-      <c r="D41" s="132" t="s">
+      <c r="D41" s="128" t="s">
         <v>50</v>
       </c>
       <c r="E41" s="7">
         <v>0.54</v>
       </c>
-      <c r="F41" s="88">
+      <c r="F41" s="87">
         <v>40230.000000000007</v>
       </c>
-      <c r="G41" s="187">
+      <c r="G41" s="180">
         <f t="shared" si="6"/>
         <v>40230.000000000007</v>
       </c>
-      <c r="H41" s="130">
+      <c r="H41" s="126">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I41" s="106"/>
-      <c r="J41" s="88">
+      <c r="I41" s="105"/>
+      <c r="J41" s="87">
         <f t="shared" si="2"/>
-        <v>2430</v>
-      </c>
-      <c r="K41" s="88">
+        <v>5220</v>
+      </c>
+      <c r="K41" s="87">
         <f t="shared" si="3"/>
         <v>37800.000000000007</v>
       </c>
-      <c r="L41" s="158"/>
+      <c r="L41" s="151"/>
       <c r="M41" s="6">
         <f t="shared" si="4"/>
-        <v>40230.000000000007</v>
-      </c>
-      <c r="N41" s="11">
+        <v>43020.000000000007</v>
+      </c>
+      <c r="N41" s="10">
         <f t="shared" si="1"/>
-        <v>42643.80000000001</v>
+        <v>45601.200000000004</v>
       </c>
     </row>
     <row r="42" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A42" s="125" t="s">
+      <c r="A42" s="122" t="s">
         <v>96</v>
       </c>
       <c r="B42" s="7"/>
       <c r="C42" s="7">
         <v>13</v>
       </c>
-      <c r="D42" s="132" t="s">
+      <c r="D42" s="128" t="s">
         <v>66</v>
       </c>
       <c r="E42" s="7">
         <v>0.55000000000000004</v>
       </c>
-      <c r="F42" s="88">
+      <c r="F42" s="87">
         <v>40975.000000000007</v>
       </c>
-      <c r="G42" s="187">
+      <c r="G42" s="180">
         <f>F42</f>
         <v>40975.000000000007</v>
       </c>
-      <c r="H42" s="130">
+      <c r="H42" s="126">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I42" s="106"/>
-      <c r="J42" s="88">
+      <c r="I42" s="105"/>
+      <c r="J42" s="87">
         <f t="shared" si="2"/>
-        <v>2475.0000000000005</v>
-      </c>
-      <c r="K42" s="88">
+        <v>5316.666666666667</v>
+      </c>
+      <c r="K42" s="87">
         <f t="shared" si="3"/>
         <v>38500.000000000007</v>
       </c>
-      <c r="L42" s="158"/>
+      <c r="L42" s="151"/>
       <c r="M42" s="6">
         <f t="shared" si="4"/>
-        <v>40975.000000000007</v>
-      </c>
-      <c r="N42" s="11">
+        <v>43816.666666666672</v>
+      </c>
+      <c r="N42" s="10">
         <f t="shared" si="1"/>
-        <v>43433.500000000007</v>
+        <v>46445.666666666672</v>
       </c>
     </row>
     <row r="43" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A43" s="125" t="s">
+      <c r="A43" s="122" t="s">
         <v>96</v>
       </c>
       <c r="B43" s="7"/>
       <c r="C43" s="7">
         <v>14</v>
       </c>
-      <c r="D43" s="132" t="s">
+      <c r="D43" s="128" t="s">
         <v>66</v>
       </c>
       <c r="E43" s="7">
         <v>0.45</v>
       </c>
-      <c r="F43" s="88">
+      <c r="F43" s="87">
         <v>33525</v>
       </c>
-      <c r="G43" s="187">
+      <c r="G43" s="180">
         <f t="shared" ref="G43:G44" si="7">F43</f>
         <v>33525</v>
       </c>
-      <c r="H43" s="130">
+      <c r="H43" s="126">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I43" s="106"/>
-      <c r="J43" s="88">
+      <c r="I43" s="105"/>
+      <c r="J43" s="87">
         <f t="shared" si="2"/>
-        <v>2025.0000000000002</v>
-      </c>
-      <c r="K43" s="88">
+        <v>4350</v>
+      </c>
+      <c r="K43" s="87">
         <f t="shared" si="3"/>
         <v>31500</v>
       </c>
-      <c r="L43" s="158"/>
+      <c r="L43" s="151"/>
       <c r="M43" s="6">
         <f t="shared" si="4"/>
-        <v>33525</v>
-      </c>
-      <c r="N43" s="11">
+        <v>35850</v>
+      </c>
+      <c r="N43" s="10">
         <f t="shared" si="1"/>
-        <v>35536.5</v>
-      </c>
-      <c r="P43" s="108">
+        <v>38001</v>
+      </c>
+      <c r="P43" s="107">
         <f>L1-K52</f>
-        <v>591652.79040900059</v>
+        <v>48343.701813001186</v>
       </c>
     </row>
     <row r="44" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A44" s="125" t="s">
+      <c r="A44" s="122" t="s">
         <v>96</v>
       </c>
       <c r="B44" s="7"/>
       <c r="C44" s="7">
         <v>15</v>
       </c>
-      <c r="D44" s="132" t="s">
+      <c r="D44" s="128" t="s">
         <v>66</v>
       </c>
       <c r="E44" s="7">
         <v>0.61</v>
       </c>
-      <c r="F44" s="88">
+      <c r="F44" s="87">
         <v>45445</v>
       </c>
-      <c r="G44" s="187">
+      <c r="G44" s="180">
         <f t="shared" si="7"/>
         <v>45445</v>
       </c>
-      <c r="H44" s="130">
+      <c r="H44" s="126">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I44" s="106"/>
-      <c r="J44" s="88">
+      <c r="I44" s="105"/>
+      <c r="J44" s="87">
         <f t="shared" si="2"/>
-        <v>2745</v>
-      </c>
-      <c r="K44" s="88">
+        <v>5896.6666666666661</v>
+      </c>
+      <c r="K44" s="87">
         <f t="shared" si="3"/>
         <v>42700</v>
       </c>
-      <c r="L44" s="158"/>
+      <c r="L44" s="151"/>
       <c r="M44" s="6">
         <f t="shared" si="4"/>
-        <v>45445</v>
-      </c>
-      <c r="N44" s="11">
+        <v>48596.666666666664</v>
+      </c>
+      <c r="N44" s="10">
         <f t="shared" si="1"/>
-        <v>48171.7</v>
+        <v>51512.466666666667</v>
       </c>
     </row>
     <row r="45" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A45" s="125" t="s">
+      <c r="A45" s="122" t="s">
         <v>96</v>
       </c>
       <c r="B45" s="7"/>
       <c r="C45" s="7">
         <v>16</v>
       </c>
-      <c r="D45" s="132" t="s">
+      <c r="D45" s="128" t="s">
         <v>53</v>
       </c>
       <c r="E45" s="7">
         <v>0.54</v>
       </c>
-      <c r="F45" s="88">
+      <c r="F45" s="87">
         <v>40230.000000000007</v>
       </c>
-      <c r="G45" s="187">
-        <f t="shared" ref="G45:G51" si="8">F45</f>
+      <c r="G45" s="180">
+        <f t="shared" ref="G45:G48" si="8">F45</f>
         <v>40230.000000000007</v>
       </c>
-      <c r="H45" s="130">
+      <c r="H45" s="126">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I45" s="106"/>
-      <c r="J45" s="88">
+      <c r="I45" s="105"/>
+      <c r="J45" s="87">
         <f t="shared" si="2"/>
-        <v>2430</v>
-      </c>
-      <c r="K45" s="88">
+        <v>5220</v>
+      </c>
+      <c r="K45" s="87">
         <f t="shared" si="3"/>
         <v>37800.000000000007</v>
       </c>
-      <c r="L45" s="158"/>
+      <c r="L45" s="151"/>
       <c r="M45" s="6">
         <f t="shared" si="4"/>
-        <v>40230.000000000007</v>
-      </c>
-      <c r="N45" s="11">
+        <v>43020.000000000007</v>
+      </c>
+      <c r="N45" s="10">
         <f t="shared" si="1"/>
-        <v>42643.80000000001</v>
+        <v>45601.200000000004</v>
       </c>
     </row>
     <row r="46" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A46" s="125" t="s">
+      <c r="A46" s="122" t="s">
         <v>96</v>
       </c>
       <c r="B46" s="7"/>
       <c r="C46" s="7">
         <v>17</v>
       </c>
-      <c r="D46" s="132" t="s">
+      <c r="D46" s="128" t="s">
         <v>55</v>
       </c>
       <c r="E46" s="7">
         <v>0.5</v>
       </c>
-      <c r="F46" s="88">
+      <c r="F46" s="87">
         <v>37250</v>
       </c>
-      <c r="G46" s="187">
+      <c r="G46" s="180">
         <f>F46</f>
         <v>37250</v>
       </c>
-      <c r="H46" s="130">
+      <c r="H46" s="126">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I46" s="106"/>
-      <c r="J46" s="88">
+      <c r="I46" s="105"/>
+      <c r="J46" s="87">
         <f t="shared" si="2"/>
-        <v>2250</v>
-      </c>
-      <c r="K46" s="88">
+        <v>4833.333333333333</v>
+      </c>
+      <c r="K46" s="87">
         <f t="shared" si="3"/>
         <v>35000</v>
       </c>
-      <c r="L46" s="158"/>
+      <c r="L46" s="151"/>
       <c r="M46" s="6">
         <f t="shared" si="4"/>
-        <v>37250</v>
-      </c>
-      <c r="N46" s="11">
+        <v>39833.333333333336</v>
+      </c>
+      <c r="N46" s="10">
         <f t="shared" si="1"/>
-        <v>39485</v>
+        <v>42223.333333333336</v>
       </c>
       <c r="Q46" t="s">
         <v>132</v>
       </c>
     </row>
     <row r="47" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A47" s="125" t="s">
+      <c r="A47" s="122" t="s">
         <v>96</v>
       </c>
       <c r="B47" s="7"/>
       <c r="C47" s="7">
         <v>18</v>
       </c>
-      <c r="D47" s="132" t="s">
+      <c r="D47" s="128" t="s">
         <v>47</v>
       </c>
       <c r="E47" s="7">
         <v>0.5</v>
       </c>
-      <c r="F47" s="88">
+      <c r="F47" s="87">
         <v>37250</v>
       </c>
-      <c r="G47" s="187">
+      <c r="G47" s="180">
         <f t="shared" si="8"/>
         <v>37250</v>
       </c>
-      <c r="H47" s="130">
+      <c r="H47" s="126">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I47" s="106"/>
-      <c r="J47" s="88">
+      <c r="I47" s="105"/>
+      <c r="J47" s="87">
         <f t="shared" si="2"/>
-        <v>2250</v>
-      </c>
-      <c r="K47" s="88">
+        <v>4833.333333333333</v>
+      </c>
+      <c r="K47" s="87">
         <f t="shared" si="3"/>
         <v>35000</v>
       </c>
-      <c r="L47" s="158"/>
+      <c r="L47" s="151"/>
       <c r="M47" s="6">
         <f t="shared" si="4"/>
-        <v>37250</v>
-      </c>
-      <c r="N47" s="11">
+        <v>39833.333333333336</v>
+      </c>
+      <c r="N47" s="10">
         <f t="shared" si="1"/>
-        <v>39485</v>
-      </c>
-      <c r="O47" s="137"/>
-      <c r="Q47" s="134">
+        <v>42223.333333333336</v>
+      </c>
+      <c r="O47" s="133"/>
+      <c r="Q47" s="130">
         <f>M3-J52</f>
-        <v>2486405</v>
+        <v>2011536.666666667</v>
       </c>
     </row>
     <row r="48" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A48" s="125" t="s">
+      <c r="A48" s="122" t="s">
         <v>96</v>
       </c>
       <c r="B48" s="7"/>
       <c r="C48" s="7">
         <v>19</v>
       </c>
-      <c r="D48" s="132" t="s">
+      <c r="D48" s="128" t="s">
         <v>47</v>
       </c>
       <c r="E48" s="7">
         <v>0.49</v>
       </c>
-      <c r="F48" s="88">
+      <c r="F48" s="87">
         <v>36505</v>
       </c>
-      <c r="G48" s="187">
+      <c r="G48" s="180">
         <f t="shared" si="8"/>
         <v>36505</v>
       </c>
-      <c r="H48" s="130">
+      <c r="H48" s="126">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I48" s="106"/>
-      <c r="J48" s="88">
+      <c r="I48" s="105"/>
+      <c r="J48" s="87">
         <f t="shared" si="2"/>
-        <v>2205</v>
-      </c>
-      <c r="K48" s="88">
+        <v>4736.6666666666661</v>
+      </c>
+      <c r="K48" s="87">
         <f t="shared" si="3"/>
         <v>34300</v>
       </c>
-      <c r="L48" s="158"/>
+      <c r="L48" s="151"/>
       <c r="M48" s="6">
         <f t="shared" si="4"/>
-        <v>36505</v>
-      </c>
-      <c r="N48" s="11">
+        <v>39036.666666666664</v>
+      </c>
+      <c r="N48" s="10">
         <f t="shared" si="1"/>
-        <v>38695.300000000003</v>
+        <v>41378.866666666661</v>
       </c>
     </row>
     <row r="49" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A49" s="125" t="s">
+      <c r="A49" s="122" t="s">
         <v>96</v>
       </c>
       <c r="B49" s="7"/>
       <c r="C49" s="7">
         <v>20</v>
       </c>
-      <c r="D49" s="132" t="str">
+      <c r="D49" s="128" t="str">
         <f>D16</f>
         <v>FEUILLANT, GASTON</v>
       </c>
       <c r="E49" s="7">
         <v>0.49</v>
       </c>
-      <c r="F49" s="88">
+      <c r="F49" s="87">
         <v>36505</v>
       </c>
-      <c r="G49" s="187">
+      <c r="G49" s="180">
         <f>F49</f>
         <v>36505</v>
       </c>
-      <c r="H49" s="130">
+      <c r="H49" s="126">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I49" s="106"/>
-      <c r="J49" s="88">
+      <c r="I49" s="105"/>
+      <c r="J49" s="87">
         <f t="shared" si="2"/>
-        <v>2205</v>
-      </c>
-      <c r="K49" s="88">
+        <v>4736.6666666666661</v>
+      </c>
+      <c r="K49" s="87">
         <f t="shared" si="3"/>
         <v>34300</v>
       </c>
-      <c r="L49" s="158"/>
+      <c r="L49" s="151"/>
       <c r="M49" s="6">
         <f t="shared" si="4"/>
-        <v>36505</v>
-      </c>
-      <c r="N49" s="11">
+        <v>39036.666666666664</v>
+      </c>
+      <c r="N49" s="10">
         <f t="shared" si="1"/>
-        <v>38695.300000000003</v>
+        <v>41378.866666666661</v>
       </c>
     </row>
     <row r="50" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A50" s="125" t="s">
+      <c r="A50" s="122" t="s">
         <v>96</v>
       </c>
       <c r="B50" s="7"/>
       <c r="C50" s="7">
         <v>21</v>
       </c>
-      <c r="D50" s="132" t="s">
+      <c r="D50" s="128" t="s">
         <v>42</v>
       </c>
       <c r="E50" s="7">
         <v>0.59</v>
       </c>
-      <c r="F50" s="88">
+      <c r="F50" s="87">
         <v>43955</v>
       </c>
-      <c r="G50" s="188">
+      <c r="G50" s="181">
         <f>F50</f>
         <v>43955</v>
       </c>
-      <c r="H50" s="130">
+      <c r="H50" s="126">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I50" s="106"/>
-      <c r="J50" s="88">
+      <c r="I50" s="105"/>
+      <c r="J50" s="87">
         <f t="shared" si="2"/>
-        <v>2655</v>
-      </c>
-      <c r="K50" s="88">
+        <v>5703.333333333333</v>
+      </c>
+      <c r="K50" s="87">
         <f t="shared" si="3"/>
         <v>41300</v>
       </c>
-      <c r="L50" s="158"/>
+      <c r="L50" s="151"/>
       <c r="M50" s="6">
         <f t="shared" si="4"/>
-        <v>43955</v>
-      </c>
-      <c r="N50" s="11">
+        <v>47003.333333333336</v>
+      </c>
+      <c r="N50" s="10">
         <f t="shared" si="1"/>
-        <v>46592.3</v>
+        <v>49823.533333333333</v>
       </c>
     </row>
     <row r="51" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A51" s="125" t="s">
+      <c r="A51" s="122" t="s">
         <v>96</v>
       </c>
       <c r="B51" s="7"/>
       <c r="C51" s="7">
         <v>22</v>
       </c>
-      <c r="D51" s="132" t="s">
+      <c r="D51" s="128" t="s">
         <v>49</v>
       </c>
       <c r="E51" s="7">
         <v>0.56999999999999995</v>
       </c>
-      <c r="F51" s="88">
+      <c r="F51" s="87">
         <v>42464.999999999993</v>
       </c>
-      <c r="G51" s="187">
+      <c r="G51" s="180">
         <f>F51</f>
         <v>42464.999999999993</v>
       </c>
-      <c r="H51" s="130">
+      <c r="H51" s="126">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I51" s="106"/>
-      <c r="J51" s="88">
+      <c r="I51" s="105"/>
+      <c r="J51" s="87">
         <f t="shared" si="2"/>
-        <v>2564.9999999999995</v>
-      </c>
-      <c r="K51" s="88">
+        <v>5509.9999999999991</v>
+      </c>
+      <c r="K51" s="87">
         <f t="shared" si="3"/>
         <v>39899.999999999993</v>
       </c>
-      <c r="L51" s="158"/>
+      <c r="L51" s="151"/>
       <c r="M51" s="6">
         <f t="shared" si="4"/>
-        <v>42464.999999999993</v>
-      </c>
-      <c r="N51" s="11">
+        <v>45409.999999999993</v>
+      </c>
+      <c r="N51" s="10">
         <f t="shared" si="1"/>
-        <v>45012.899999999994</v>
+        <v>48134.599999999991</v>
       </c>
     </row>
     <row r="52" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="89"/>
-      <c r="B52" s="89"/>
-      <c r="C52" s="89"/>
-      <c r="D52" s="89"/>
-      <c r="E52" s="89">
+      <c r="A52" s="88"/>
+      <c r="B52" s="88"/>
+      <c r="C52" s="88"/>
+      <c r="D52" s="88"/>
+      <c r="E52" s="88">
         <f>SUM(E7:E51)</f>
         <v>99.999999999999986</v>
       </c>
-      <c r="F52" s="190">
+      <c r="F52" s="183">
         <f>SUM(F7:F51)</f>
         <v>6694001.5113024348</v>
       </c>
-      <c r="G52" s="190">
+      <c r="G52" s="183">
         <f>SUM(G7:G51)</f>
         <v>6941937.3369510006</v>
       </c>
-      <c r="H52" s="89"/>
-      <c r="I52" s="89"/>
-      <c r="J52" s="126">
+      <c r="H52" s="88"/>
+      <c r="I52" s="88"/>
+      <c r="J52" s="123">
         <f>SUM(J8:J51)</f>
-        <v>413595</v>
-      </c>
-      <c r="K52" s="90">
+        <v>888463.33333333314</v>
+      </c>
+      <c r="K52" s="89">
         <f>SUM(K7:K51)</f>
-        <v>6924023.2495910004</v>
-      </c>
-      <c r="L52" s="247">
+        <v>6951656.2981869997</v>
+      </c>
+      <c r="L52" s="185">
         <f>SUM(L7:L51)</f>
-        <v>1151834</v>
-      </c>
-      <c r="M52" s="91">
+        <v>1204999</v>
+      </c>
+      <c r="M52" s="90">
         <f>SUM(M7:M51)</f>
-        <v>8276064.8013024349</v>
-      </c>
-      <c r="N52" s="90">
+        <v>8875386.1392051</v>
+      </c>
+      <c r="N52" s="89">
         <f>SUM(N7:N51)</f>
-        <v>8772628.6893805824</v>
-      </c>
-      <c r="P52" s="134"/>
+        <v>9407909.3075574059</v>
+      </c>
+      <c r="P52" s="130"/>
     </row>
     <row r="53" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
-      <c r="K53" s="137">
+      <c r="K53" s="133">
         <f>K52-L1</f>
-        <v>-591652.79040900059</v>
+        <v>-48343.701813001186</v>
       </c>
     </row>
     <row r="54" spans="1:16" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C54" s="219"/>
-      <c r="D54" s="219"/>
-      <c r="E54" s="219"/>
-      <c r="F54" s="219"/>
-      <c r="G54" s="219"/>
-      <c r="H54" s="219"/>
-      <c r="I54" s="219"/>
-      <c r="J54" s="219"/>
-      <c r="K54" s="219"/>
-      <c r="L54" s="219"/>
-      <c r="M54" s="219"/>
-      <c r="N54" s="219"/>
+      <c r="C54" s="217"/>
+      <c r="D54" s="217"/>
+      <c r="E54" s="217"/>
+      <c r="F54" s="217"/>
+      <c r="G54" s="217"/>
+      <c r="H54" s="217"/>
+      <c r="I54" s="217"/>
+      <c r="J54" s="217"/>
+      <c r="K54" s="217"/>
+      <c r="L54" s="217"/>
+      <c r="M54" s="217"/>
+      <c r="N54" s="217"/>
     </row>
     <row r="55" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
-      <c r="C55" s="219"/>
-      <c r="D55" s="219"/>
-      <c r="E55" s="219"/>
-      <c r="F55" s="219"/>
-      <c r="G55" s="219"/>
-      <c r="H55" s="219"/>
-      <c r="I55" s="219"/>
-      <c r="J55" s="219"/>
-      <c r="K55" s="219"/>
-      <c r="L55" s="219"/>
-      <c r="M55" s="219"/>
-      <c r="N55" s="219"/>
+      <c r="C55" s="217"/>
+      <c r="D55" s="217"/>
+      <c r="E55" s="217"/>
+      <c r="F55" s="217"/>
+      <c r="G55" s="217"/>
+      <c r="H55" s="217"/>
+      <c r="I55" s="217"/>
+      <c r="J55" s="217"/>
+      <c r="K55" s="217"/>
+      <c r="L55" s="217"/>
+      <c r="M55" s="217"/>
+      <c r="N55" s="217"/>
     </row>
     <row r="56" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="C56" s="160"/>
-      <c r="D56" s="160"/>
-      <c r="E56" s="160"/>
-      <c r="F56" s="160"/>
-      <c r="G56" s="160"/>
-      <c r="H56" s="160"/>
-      <c r="I56" s="160"/>
-      <c r="J56" s="160"/>
-      <c r="K56" s="160"/>
-      <c r="L56" s="160"/>
-      <c r="M56" s="160"/>
-      <c r="N56" s="160"/>
+      <c r="C56" s="153"/>
+      <c r="D56" s="153"/>
+      <c r="E56" s="153"/>
+      <c r="F56" s="153"/>
+      <c r="G56" s="153"/>
+      <c r="H56" s="153"/>
+      <c r="I56" s="153"/>
+      <c r="J56" s="153"/>
+      <c r="K56" s="153"/>
+      <c r="L56" s="153"/>
+      <c r="M56" s="153"/>
+      <c r="N56" s="153"/>
     </row>
     <row r="57" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="C57" s="219" t="s">
+      <c r="C57" s="217" t="s">
         <v>129</v>
       </c>
-      <c r="D57" s="219"/>
-      <c r="E57" s="219"/>
-      <c r="F57" s="219"/>
-      <c r="G57" s="219"/>
-      <c r="H57" s="219"/>
-      <c r="I57" s="219"/>
-      <c r="J57" s="219"/>
-      <c r="K57" s="219"/>
-      <c r="L57" s="219"/>
-      <c r="M57" s="219"/>
-      <c r="N57" s="219"/>
+      <c r="D57" s="217"/>
+      <c r="E57" s="217"/>
+      <c r="F57" s="217"/>
+      <c r="G57" s="217"/>
+      <c r="H57" s="217"/>
+      <c r="I57" s="217"/>
+      <c r="J57" s="217"/>
+      <c r="K57" s="217"/>
+      <c r="L57" s="217"/>
+      <c r="M57" s="217"/>
+      <c r="N57" s="217"/>
     </row>
     <row r="58" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="C58" s="219"/>
-      <c r="D58" s="219"/>
-      <c r="E58" s="219"/>
-      <c r="F58" s="219"/>
-      <c r="G58" s="219"/>
-      <c r="H58" s="219"/>
-      <c r="I58" s="219"/>
-      <c r="J58" s="219"/>
-      <c r="K58" s="219"/>
-      <c r="L58" s="219"/>
-      <c r="M58" s="219"/>
-      <c r="N58" s="219"/>
+      <c r="C58" s="217"/>
+      <c r="D58" s="217"/>
+      <c r="E58" s="217"/>
+      <c r="F58" s="217"/>
+      <c r="G58" s="217"/>
+      <c r="H58" s="217"/>
+      <c r="I58" s="217"/>
+      <c r="J58" s="217"/>
+      <c r="K58" s="217"/>
+      <c r="L58" s="217"/>
+      <c r="M58" s="217"/>
+      <c r="N58" s="217"/>
     </row>
     <row r="59" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="C59" s="219"/>
-      <c r="D59" s="219"/>
-      <c r="E59" s="219"/>
-      <c r="F59" s="219"/>
-      <c r="G59" s="219"/>
-      <c r="H59" s="219"/>
-      <c r="I59" s="219"/>
-      <c r="J59" s="219"/>
-      <c r="K59" s="219"/>
-      <c r="L59" s="219"/>
-      <c r="M59" s="219"/>
-      <c r="N59" s="219"/>
+      <c r="C59" s="217"/>
+      <c r="D59" s="217"/>
+      <c r="E59" s="217"/>
+      <c r="F59" s="217"/>
+      <c r="G59" s="217"/>
+      <c r="H59" s="217"/>
+      <c r="I59" s="217"/>
+      <c r="J59" s="217"/>
+      <c r="K59" s="217"/>
+      <c r="L59" s="217"/>
+      <c r="M59" s="217"/>
+      <c r="N59" s="217"/>
     </row>
     <row r="60" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="C60" s="219"/>
-      <c r="D60" s="219"/>
-      <c r="E60" s="219"/>
-      <c r="F60" s="219"/>
-      <c r="G60" s="219"/>
-      <c r="H60" s="219"/>
-      <c r="I60" s="219"/>
-      <c r="J60" s="219"/>
-      <c r="K60" s="219"/>
-      <c r="L60" s="219"/>
-      <c r="M60" s="219"/>
-      <c r="N60" s="219"/>
+      <c r="C60" s="217"/>
+      <c r="D60" s="217"/>
+      <c r="E60" s="217"/>
+      <c r="F60" s="217"/>
+      <c r="G60" s="217"/>
+      <c r="H60" s="217"/>
+      <c r="I60" s="217"/>
+      <c r="J60" s="217"/>
+      <c r="K60" s="217"/>
+      <c r="L60" s="217"/>
+      <c r="M60" s="217"/>
+      <c r="N60" s="217"/>
     </row>
     <row r="61" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="C61" s="219"/>
-      <c r="D61" s="219"/>
-      <c r="E61" s="219"/>
-      <c r="F61" s="219"/>
-      <c r="G61" s="219"/>
-      <c r="H61" s="219"/>
-      <c r="I61" s="219"/>
-      <c r="J61" s="219"/>
-      <c r="K61" s="219"/>
-      <c r="L61" s="219"/>
-      <c r="M61" s="219"/>
-      <c r="N61" s="219"/>
+      <c r="C61" s="217"/>
+      <c r="D61" s="217"/>
+      <c r="E61" s="217"/>
+      <c r="F61" s="217"/>
+      <c r="G61" s="217"/>
+      <c r="H61" s="217"/>
+      <c r="I61" s="217"/>
+      <c r="J61" s="217"/>
+      <c r="K61" s="217"/>
+      <c r="L61" s="217"/>
+      <c r="M61" s="217"/>
+      <c r="N61" s="217"/>
     </row>
     <row r="62" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="C62" s="219"/>
-      <c r="D62" s="219"/>
-      <c r="E62" s="219"/>
-      <c r="F62" s="219"/>
-      <c r="G62" s="219"/>
-      <c r="H62" s="219"/>
-      <c r="I62" s="219"/>
-      <c r="J62" s="219"/>
-      <c r="K62" s="219"/>
-      <c r="L62" s="219"/>
-      <c r="M62" s="219"/>
-      <c r="N62" s="219"/>
+      <c r="C62" s="217"/>
+      <c r="D62" s="217"/>
+      <c r="E62" s="217"/>
+      <c r="F62" s="217"/>
+      <c r="G62" s="217"/>
+      <c r="H62" s="217"/>
+      <c r="I62" s="217"/>
+      <c r="J62" s="217"/>
+      <c r="K62" s="217"/>
+      <c r="L62" s="217"/>
+      <c r="M62" s="217"/>
+      <c r="N62" s="217"/>
     </row>
     <row r="63" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="C63" s="219"/>
-      <c r="D63" s="219"/>
-      <c r="E63" s="219"/>
-      <c r="F63" s="219"/>
-      <c r="G63" s="219"/>
-      <c r="H63" s="219"/>
-      <c r="I63" s="219"/>
-      <c r="J63" s="219"/>
-      <c r="K63" s="219"/>
-      <c r="L63" s="219"/>
-      <c r="M63" s="219"/>
-      <c r="N63" s="219"/>
+      <c r="C63" s="217"/>
+      <c r="D63" s="217"/>
+      <c r="E63" s="217"/>
+      <c r="F63" s="217"/>
+      <c r="G63" s="217"/>
+      <c r="H63" s="217"/>
+      <c r="I63" s="217"/>
+      <c r="J63" s="217"/>
+      <c r="K63" s="217"/>
+      <c r="L63" s="217"/>
+      <c r="M63" s="217"/>
+      <c r="N63" s="217"/>
     </row>
   </sheetData>
-  <mergeCells count="17">
-    <mergeCell ref="A5:A6"/>
-    <mergeCell ref="B5:B6"/>
-    <mergeCell ref="C5:C6"/>
-    <mergeCell ref="D5:D6"/>
-    <mergeCell ref="E5:E6"/>
+  <mergeCells count="18">
     <mergeCell ref="F5:F6"/>
     <mergeCell ref="C57:N63"/>
     <mergeCell ref="C54:N55"/>
@@ -6309,6 +6332,12 @@
     <mergeCell ref="L5:L6"/>
     <mergeCell ref="M5:M6"/>
     <mergeCell ref="I5:I6"/>
+    <mergeCell ref="A1:J4"/>
+    <mergeCell ref="A5:A6"/>
+    <mergeCell ref="B5:B6"/>
+    <mergeCell ref="C5:C6"/>
+    <mergeCell ref="D5:D6"/>
+    <mergeCell ref="E5:E6"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="3" orientation="landscape" r:id="rId1"/>
@@ -6332,7 +6361,7 @@
       <c r="C5" t="s">
         <v>144</v>
       </c>
-      <c r="D5" s="181">
+      <c r="D5" s="174">
         <v>-447223.45918396302</v>
       </c>
     </row>
@@ -6340,7 +6369,7 @@
       <c r="C6" t="s">
         <v>145</v>
       </c>
-      <c r="D6" s="181">
+      <c r="D6" s="174">
         <v>0</v>
       </c>
     </row>
@@ -6348,7 +6377,7 @@
       <c r="C7" t="s">
         <v>146</v>
       </c>
-      <c r="D7" s="181">
+      <c r="D7" s="174">
         <v>0</v>
       </c>
     </row>
@@ -6356,7 +6385,7 @@
       <c r="C8" t="s">
         <v>147</v>
       </c>
-      <c r="D8" s="181">
+      <c r="D8" s="174">
         <v>0</v>
       </c>
     </row>
@@ -6369,7 +6398,7 @@
       <c r="C11" t="s">
         <v>144</v>
       </c>
-      <c r="D11" s="181">
+      <c r="D11" s="174">
         <v>451182</v>
       </c>
     </row>
@@ -6377,7 +6406,7 @@
       <c r="C12" t="s">
         <v>145</v>
       </c>
-      <c r="D12" s="181">
+      <c r="D12" s="174">
         <v>40606.380000000005</v>
       </c>
     </row>
@@ -6385,7 +6414,7 @@
       <c r="C13" t="s">
         <v>146</v>
       </c>
-      <c r="D13" s="181">
+      <c r="D13" s="174">
         <v>41358.350000000006</v>
       </c>
     </row>
@@ -6393,7 +6422,7 @@
       <c r="C14" t="s">
         <v>147</v>
       </c>
-      <c r="D14" s="181">
+      <c r="D14" s="174">
         <v>37598.5</v>
       </c>
     </row>
@@ -6411,7 +6440,7 @@
       <c r="C17" t="s">
         <v>144</v>
       </c>
-      <c r="D17" s="181">
+      <c r="D17" s="174">
         <f>D11+D5</f>
         <v>3958.5408160369843</v>
       </c>
@@ -6420,7 +6449,7 @@
       <c r="C18" t="s">
         <v>145</v>
       </c>
-      <c r="D18" s="181">
+      <c r="D18" s="174">
         <v>40606.380000000005</v>
       </c>
     </row>
@@ -6428,7 +6457,7 @@
       <c r="C19" t="s">
         <v>146</v>
       </c>
-      <c r="D19" s="181">
+      <c r="D19" s="174">
         <v>41358.350000000006</v>
       </c>
     </row>
@@ -6436,7 +6465,7 @@
       <c r="C20" t="s">
         <v>147</v>
       </c>
-      <c r="D20" s="181">
+      <c r="D20" s="174">
         <v>37598.5</v>
       </c>
     </row>
@@ -6444,30 +6473,30 @@
       <c r="C21" t="s">
         <v>151</v>
       </c>
-      <c r="D21" s="181">
+      <c r="D21" s="174">
         <v>-25000</v>
       </c>
     </row>
     <row r="22" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C22" s="234" t="s">
+      <c r="C22" s="226" t="s">
         <v>150</v>
       </c>
-      <c r="D22" s="237">
+      <c r="D22" s="229">
         <f>SUM(D17:D21)</f>
         <v>98521.770816036995</v>
       </c>
     </row>
     <row r="23" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C23" s="235"/>
-      <c r="D23" s="238"/>
+      <c r="C23" s="227"/>
+      <c r="D23" s="230"/>
     </row>
     <row r="24" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C24" s="235"/>
-      <c r="D24" s="238"/>
+      <c r="C24" s="227"/>
+      <c r="D24" s="230"/>
     </row>
     <row r="25" spans="3:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C25" s="236"/>
-      <c r="D25" s="239"/>
+      <c r="C25" s="228"/>
+      <c r="D25" s="231"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -6492,211 +6521,211 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A1" s="48"/>
-      <c r="B1" s="49"/>
-      <c r="C1" s="49"/>
-      <c r="D1" s="50" t="s">
+      <c r="A1" s="47"/>
+      <c r="B1" s="48"/>
+      <c r="C1" s="48"/>
+      <c r="D1" s="49" t="s">
         <v>17</v>
       </c>
-      <c r="E1" s="50"/>
-      <c r="F1" s="49"/>
-      <c r="G1" s="49"/>
-      <c r="H1" s="49"/>
-      <c r="I1" s="49"/>
-      <c r="J1" s="49"/>
-      <c r="K1" s="49"/>
-      <c r="L1" s="50" t="s">
+      <c r="E1" s="49"/>
+      <c r="F1" s="48"/>
+      <c r="G1" s="48"/>
+      <c r="H1" s="48"/>
+      <c r="I1" s="48"/>
+      <c r="J1" s="48"/>
+      <c r="K1" s="48"/>
+      <c r="L1" s="49" t="s">
         <v>70</v>
       </c>
-      <c r="M1" s="49"/>
-      <c r="N1" s="52" t="str">
+      <c r="M1" s="48"/>
+      <c r="N1" s="51" t="str">
         <f>RESUMEN!C5</f>
         <v>VTO: 14/11</v>
       </c>
-      <c r="O1" s="52"/>
+      <c r="O1" s="51"/>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A2" s="49"/>
-      <c r="B2" s="51"/>
-      <c r="C2" s="51"/>
-      <c r="D2" s="50" t="s">
+      <c r="A2" s="48"/>
+      <c r="B2" s="50"/>
+      <c r="C2" s="50"/>
+      <c r="D2" s="49" t="s">
         <v>18</v>
       </c>
-      <c r="E2" s="49"/>
-      <c r="F2" s="49"/>
-      <c r="G2" s="49"/>
-      <c r="H2" s="49"/>
-      <c r="I2" s="49"/>
-      <c r="J2" s="49"/>
-      <c r="K2" s="49"/>
-      <c r="L2" s="49"/>
-      <c r="M2" s="49"/>
-      <c r="N2" s="49"/>
-      <c r="O2" s="49"/>
+      <c r="E2" s="48"/>
+      <c r="F2" s="48"/>
+      <c r="G2" s="48"/>
+      <c r="H2" s="48"/>
+      <c r="I2" s="48"/>
+      <c r="J2" s="48"/>
+      <c r="K2" s="48"/>
+      <c r="L2" s="48"/>
+      <c r="M2" s="48"/>
+      <c r="N2" s="48"/>
+      <c r="O2" s="48"/>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A3" s="49"/>
-      <c r="B3" s="51"/>
-      <c r="C3" s="51"/>
-      <c r="D3" s="50"/>
-      <c r="E3" s="49"/>
-      <c r="F3" s="49"/>
-      <c r="G3" s="49"/>
-      <c r="H3" s="49"/>
-      <c r="I3" s="49"/>
-      <c r="J3" s="50" t="s">
+      <c r="A3" s="48"/>
+      <c r="B3" s="50"/>
+      <c r="C3" s="50"/>
+      <c r="D3" s="49"/>
+      <c r="E3" s="48"/>
+      <c r="F3" s="48"/>
+      <c r="G3" s="48"/>
+      <c r="H3" s="48"/>
+      <c r="I3" s="48"/>
+      <c r="J3" s="49" t="s">
         <v>71</v>
       </c>
-      <c r="K3" s="50"/>
-      <c r="L3" s="53">
+      <c r="K3" s="49"/>
+      <c r="L3" s="52">
         <v>249991.29847799998</v>
       </c>
-      <c r="M3" s="49"/>
-      <c r="N3" s="54">
+      <c r="M3" s="48"/>
+      <c r="N3" s="53">
         <v>-1891.33</v>
       </c>
-      <c r="O3" s="54"/>
+      <c r="O3" s="53"/>
     </row>
     <row r="4" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="49"/>
-      <c r="B4" s="51"/>
-      <c r="C4" s="51"/>
-      <c r="D4" s="50"/>
-      <c r="E4" s="49"/>
-      <c r="F4" s="49"/>
-      <c r="G4" s="49"/>
-      <c r="H4" s="49"/>
-      <c r="I4" s="49"/>
-      <c r="J4" s="50" t="s">
+      <c r="A4" s="48"/>
+      <c r="B4" s="50"/>
+      <c r="C4" s="50"/>
+      <c r="D4" s="49"/>
+      <c r="E4" s="48"/>
+      <c r="F4" s="48"/>
+      <c r="G4" s="48"/>
+      <c r="H4" s="48"/>
+      <c r="I4" s="48"/>
+      <c r="J4" s="49" t="s">
         <v>72</v>
       </c>
-      <c r="K4" s="50"/>
-      <c r="L4" s="53">
-        <v>0</v>
-      </c>
-      <c r="M4" s="49"/>
-      <c r="N4" s="49"/>
-      <c r="O4" s="49"/>
+      <c r="K4" s="49"/>
+      <c r="L4" s="52">
+        <v>0</v>
+      </c>
+      <c r="M4" s="48"/>
+      <c r="N4" s="48"/>
+      <c r="O4" s="48"/>
     </row>
     <row r="5" spans="1:15" ht="30" x14ac:dyDescent="0.25">
-      <c r="A5" s="240" t="s">
+      <c r="A5" s="232" t="s">
         <v>73</v>
       </c>
-      <c r="B5" s="240" t="s">
+      <c r="B5" s="232" t="s">
         <v>22</v>
       </c>
-      <c r="C5" s="55" t="s">
+      <c r="C5" s="54" t="s">
         <v>74</v>
       </c>
-      <c r="D5" s="35" t="s">
+      <c r="D5" s="34" t="s">
         <v>23</v>
       </c>
-      <c r="E5" s="35" t="s">
+      <c r="E5" s="34" t="s">
         <v>24</v>
       </c>
-      <c r="F5" s="240" t="s">
+      <c r="F5" s="232" t="s">
         <v>75</v>
       </c>
-      <c r="G5" s="37" t="s">
+      <c r="G5" s="36" t="s">
         <v>76</v>
       </c>
-      <c r="H5" s="38" t="s">
+      <c r="H5" s="37" t="s">
         <v>27</v>
       </c>
-      <c r="I5" s="36" t="s">
+      <c r="I5" s="35" t="s">
         <v>77</v>
       </c>
-      <c r="J5" s="39" t="s">
+      <c r="J5" s="38" t="s">
         <v>28</v>
       </c>
-      <c r="K5" s="40" t="s">
+      <c r="K5" s="39" t="s">
         <v>28</v>
       </c>
-      <c r="L5" s="37" t="s">
+      <c r="L5" s="36" t="s">
         <v>29</v>
       </c>
-      <c r="M5" s="41"/>
-      <c r="N5" s="240" t="s">
+      <c r="M5" s="40"/>
+      <c r="N5" s="232" t="s">
         <v>78</v>
       </c>
-      <c r="O5" s="240" t="s">
+      <c r="O5" s="232" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A6" s="241"/>
-      <c r="B6" s="241"/>
-      <c r="C6" s="56" t="s">
+      <c r="A6" s="233"/>
+      <c r="B6" s="233"/>
+      <c r="C6" s="55" t="s">
         <v>80</v>
       </c>
-      <c r="D6" s="42" t="s">
+      <c r="D6" s="41" t="s">
         <v>30</v>
       </c>
-      <c r="E6" s="42" t="s">
+      <c r="E6" s="41" t="s">
         <v>31</v>
       </c>
-      <c r="F6" s="241"/>
-      <c r="G6" s="44" t="s">
+      <c r="F6" s="233"/>
+      <c r="G6" s="43" t="s">
         <v>81</v>
       </c>
-      <c r="H6" s="45">
+      <c r="H6" s="44">
         <v>0.06</v>
       </c>
-      <c r="I6" s="43" t="s">
+      <c r="I6" s="42" t="s">
         <v>82</v>
       </c>
-      <c r="J6" s="46" t="s">
+      <c r="J6" s="45" t="s">
         <v>32</v>
       </c>
-      <c r="K6" s="47" t="s">
+      <c r="K6" s="46" t="s">
         <v>83</v>
       </c>
-      <c r="L6" s="44" t="s">
+      <c r="L6" s="43" t="s">
         <v>84</v>
       </c>
-      <c r="M6" s="47"/>
-      <c r="N6" s="241"/>
-      <c r="O6" s="241"/>
+      <c r="M6" s="46"/>
+      <c r="N6" s="233"/>
+      <c r="O6" s="233"/>
     </row>
     <row r="7" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="15">
+      <c r="A7" s="14">
         <v>1</v>
       </c>
-      <c r="B7" s="84" t="s">
+      <c r="B7" s="83" t="s">
         <v>60</v>
       </c>
-      <c r="C7" s="87">
+      <c r="C7" s="86">
         <v>5.4</v>
       </c>
       <c r="D7" s="6">
         <v>13967.239436680005</v>
       </c>
-      <c r="E7" s="58">
+      <c r="E7" s="57">
         <f>D7</f>
         <v>13967.239436680005</v>
       </c>
-      <c r="F7" s="23">
-        <v>0</v>
-      </c>
-      <c r="G7" s="21">
-        <v>0</v>
-      </c>
-      <c r="H7" s="27">
-        <v>0</v>
-      </c>
-      <c r="I7" s="17">
+      <c r="F7" s="22">
+        <v>0</v>
+      </c>
+      <c r="G7" s="20">
+        <v>0</v>
+      </c>
+      <c r="H7" s="26">
+        <v>0</v>
+      </c>
+      <c r="I7" s="16">
         <v>0.54</v>
       </c>
-      <c r="J7" s="23">
+      <c r="J7" s="22">
         <v>11608.200117812001</v>
       </c>
-      <c r="K7" s="29">
-        <v>0</v>
-      </c>
-      <c r="L7" s="21">
+      <c r="K7" s="28">
+        <v>0</v>
+      </c>
+      <c r="L7" s="20">
         <v>11608.200117812001</v>
       </c>
-      <c r="M7" s="18"/>
+      <c r="M7" s="17"/>
       <c r="N7" s="6">
         <v>11608.200117812001</v>
       </c>
@@ -6705,44 +6734,44 @@
       </c>
     </row>
     <row r="8" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="15">
+      <c r="A8" s="14">
         <v>2</v>
       </c>
-      <c r="B8" s="84" t="s">
+      <c r="B8" s="83" t="s">
         <v>60</v>
       </c>
-      <c r="C8" s="87">
+      <c r="C8" s="86">
         <v>5.5</v>
       </c>
       <c r="D8" s="6">
         <v>14267.901278100004</v>
       </c>
-      <c r="E8" s="58">
+      <c r="E8" s="57">
         <f t="shared" ref="E8:E28" si="0">D8</f>
         <v>14267.901278100004</v>
       </c>
-      <c r="F8" s="23">
-        <v>0</v>
-      </c>
-      <c r="G8" s="21">
-        <v>0</v>
-      </c>
-      <c r="H8" s="27">
-        <v>0</v>
-      </c>
-      <c r="I8" s="17">
+      <c r="F8" s="22">
+        <v>0</v>
+      </c>
+      <c r="G8" s="20">
+        <v>0</v>
+      </c>
+      <c r="H8" s="26">
+        <v>0</v>
+      </c>
+      <c r="I8" s="16">
         <v>0.55000000000000004</v>
       </c>
-      <c r="J8" s="23">
+      <c r="J8" s="22">
         <v>11858.191416289999</v>
       </c>
-      <c r="K8" s="29">
-        <v>0</v>
-      </c>
-      <c r="L8" s="21">
+      <c r="K8" s="28">
+        <v>0</v>
+      </c>
+      <c r="L8" s="20">
         <v>11858.191416289999</v>
       </c>
-      <c r="M8" s="18"/>
+      <c r="M8" s="17"/>
       <c r="N8" s="6">
         <v>11858.191416289999</v>
       </c>
@@ -6751,44 +6780,44 @@
       </c>
     </row>
     <row r="9" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="15">
+      <c r="A9" s="14">
         <v>3</v>
       </c>
-      <c r="B9" s="84" t="s">
+      <c r="B9" s="83" t="s">
         <v>64</v>
       </c>
-      <c r="C9" s="87">
+      <c r="C9" s="86">
         <v>4.5</v>
       </c>
       <c r="D9" s="6">
         <v>11261.282863900002</v>
       </c>
-      <c r="E9" s="58">
+      <c r="E9" s="57">
         <f t="shared" si="0"/>
         <v>11261.282863900002</v>
       </c>
-      <c r="F9" s="23">
-        <v>0</v>
-      </c>
-      <c r="G9" s="21">
-        <v>0</v>
-      </c>
-      <c r="H9" s="27">
-        <v>0</v>
-      </c>
-      <c r="I9" s="17">
+      <c r="F9" s="22">
+        <v>0</v>
+      </c>
+      <c r="G9" s="20">
+        <v>0</v>
+      </c>
+      <c r="H9" s="26">
+        <v>0</v>
+      </c>
+      <c r="I9" s="16">
         <v>0.45</v>
       </c>
-      <c r="J9" s="23">
+      <c r="J9" s="22">
         <v>9358.278431509998</v>
       </c>
-      <c r="K9" s="29">
-        <v>0</v>
-      </c>
-      <c r="L9" s="21">
+      <c r="K9" s="28">
+        <v>0</v>
+      </c>
+      <c r="L9" s="20">
         <v>9358.278431509998</v>
       </c>
-      <c r="M9" s="18"/>
+      <c r="M9" s="17"/>
       <c r="N9" s="6">
         <v>9358.278431509998</v>
       </c>
@@ -6797,44 +6826,44 @@
       </c>
     </row>
     <row r="10" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="15">
+      <c r="A10" s="14">
         <v>4</v>
       </c>
-      <c r="B10" s="84" t="s">
+      <c r="B10" s="83" t="s">
         <v>64</v>
       </c>
-      <c r="C10" s="87">
+      <c r="C10" s="86">
         <v>6.1</v>
       </c>
       <c r="D10" s="6">
         <v>16071.872326620005</v>
       </c>
-      <c r="E10" s="58">
+      <c r="E10" s="57">
         <f t="shared" si="0"/>
         <v>16071.872326620005</v>
       </c>
-      <c r="F10" s="23">
-        <v>0</v>
-      </c>
-      <c r="G10" s="21">
-        <v>0</v>
-      </c>
-      <c r="H10" s="27">
-        <v>0</v>
-      </c>
-      <c r="I10" s="17">
+      <c r="F10" s="22">
+        <v>0</v>
+      </c>
+      <c r="G10" s="20">
+        <v>0</v>
+      </c>
+      <c r="H10" s="26">
+        <v>0</v>
+      </c>
+      <c r="I10" s="16">
         <v>0.61</v>
       </c>
-      <c r="J10" s="23">
+      <c r="J10" s="22">
         <v>13358.139207157999</v>
       </c>
-      <c r="K10" s="29">
-        <v>0</v>
-      </c>
-      <c r="L10" s="21">
+      <c r="K10" s="28">
+        <v>0</v>
+      </c>
+      <c r="L10" s="20">
         <v>13358.139207157999</v>
       </c>
-      <c r="M10" s="18"/>
+      <c r="M10" s="17"/>
       <c r="N10" s="6">
         <v>13358.139207157999</v>
       </c>
@@ -6843,44 +6872,44 @@
       </c>
     </row>
     <row r="11" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="15">
+      <c r="A11" s="14">
         <v>5</v>
       </c>
-      <c r="B11" s="84" t="s">
+      <c r="B11" s="83" t="s">
         <v>37</v>
       </c>
-      <c r="C11" s="87">
+      <c r="C11" s="86">
         <v>5.4</v>
       </c>
       <c r="D11" s="6">
         <v>13967.239436680005</v>
       </c>
-      <c r="E11" s="58">
+      <c r="E11" s="57">
         <f t="shared" si="0"/>
         <v>13967.239436680005</v>
       </c>
-      <c r="F11" s="23">
-        <v>0</v>
-      </c>
-      <c r="G11" s="21">
-        <v>0</v>
-      </c>
-      <c r="H11" s="27">
-        <v>0</v>
-      </c>
-      <c r="I11" s="17">
+      <c r="F11" s="22">
+        <v>0</v>
+      </c>
+      <c r="G11" s="20">
+        <v>0</v>
+      </c>
+      <c r="H11" s="26">
+        <v>0</v>
+      </c>
+      <c r="I11" s="16">
         <v>0.54</v>
       </c>
-      <c r="J11" s="23">
+      <c r="J11" s="22">
         <v>11608.200117812001</v>
       </c>
-      <c r="K11" s="29">
-        <v>0</v>
-      </c>
-      <c r="L11" s="21">
+      <c r="K11" s="28">
+        <v>0</v>
+      </c>
+      <c r="L11" s="20">
         <v>11608.200117812001</v>
       </c>
-      <c r="M11" s="18"/>
+      <c r="M11" s="17"/>
       <c r="N11" s="6">
         <v>11608.200117812001</v>
       </c>
@@ -6889,44 +6918,44 @@
       </c>
     </row>
     <row r="12" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="15">
+      <c r="A12" s="14">
         <v>6</v>
       </c>
-      <c r="B12" s="85" t="s">
+      <c r="B12" s="84" t="s">
         <v>45</v>
       </c>
-      <c r="C12" s="87">
+      <c r="C12" s="86">
         <v>5</v>
       </c>
       <c r="D12" s="6">
         <v>12764.592071000003</v>
       </c>
-      <c r="E12" s="58">
+      <c r="E12" s="57">
         <f t="shared" si="0"/>
         <v>12764.592071000003</v>
       </c>
-      <c r="F12" s="23">
-        <v>0</v>
-      </c>
-      <c r="G12" s="21">
-        <v>0</v>
-      </c>
-      <c r="H12" s="27">
-        <v>0</v>
-      </c>
-      <c r="I12" s="17">
+      <c r="F12" s="22">
+        <v>0</v>
+      </c>
+      <c r="G12" s="20">
+        <v>0</v>
+      </c>
+      <c r="H12" s="26">
+        <v>0</v>
+      </c>
+      <c r="I12" s="16">
         <v>0.5</v>
       </c>
-      <c r="J12" s="23">
+      <c r="J12" s="22">
         <v>10608.2349239</v>
       </c>
-      <c r="K12" s="29">
-        <v>0</v>
-      </c>
-      <c r="L12" s="21">
+      <c r="K12" s="28">
+        <v>0</v>
+      </c>
+      <c r="L12" s="20">
         <v>10608.2349239</v>
       </c>
-      <c r="M12" s="18"/>
+      <c r="M12" s="17"/>
       <c r="N12" s="6">
         <v>10608.2349239</v>
       </c>
@@ -6935,44 +6964,44 @@
       </c>
     </row>
     <row r="13" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="15">
+      <c r="A13" s="14">
         <v>7</v>
       </c>
-      <c r="B13" s="84" t="s">
+      <c r="B13" s="83" t="s">
         <v>60</v>
       </c>
-      <c r="C13" s="87">
+      <c r="C13" s="86">
         <v>5</v>
       </c>
       <c r="D13" s="6">
         <v>12764.592071000003</v>
       </c>
-      <c r="E13" s="58">
+      <c r="E13" s="57">
         <f t="shared" si="0"/>
         <v>12764.592071000003</v>
       </c>
-      <c r="F13" s="23">
-        <v>0</v>
-      </c>
-      <c r="G13" s="21">
-        <v>0</v>
-      </c>
-      <c r="H13" s="27">
-        <v>0</v>
-      </c>
-      <c r="I13" s="17">
+      <c r="F13" s="22">
+        <v>0</v>
+      </c>
+      <c r="G13" s="20">
+        <v>0</v>
+      </c>
+      <c r="H13" s="26">
+        <v>0</v>
+      </c>
+      <c r="I13" s="16">
         <v>0.5</v>
       </c>
-      <c r="J13" s="23">
+      <c r="J13" s="22">
         <v>10608.2349239</v>
       </c>
-      <c r="K13" s="29">
-        <v>0</v>
-      </c>
-      <c r="L13" s="21">
+      <c r="K13" s="28">
+        <v>0</v>
+      </c>
+      <c r="L13" s="20">
         <v>10608.2349239</v>
       </c>
-      <c r="M13" s="18"/>
+      <c r="M13" s="17"/>
       <c r="N13" s="6">
         <v>10608.2349239</v>
       </c>
@@ -6981,44 +7010,44 @@
       </c>
     </row>
     <row r="14" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="15">
+      <c r="A14" s="14">
         <v>8</v>
       </c>
-      <c r="B14" s="84" t="s">
+      <c r="B14" s="83" t="s">
         <v>57</v>
       </c>
-      <c r="C14" s="87">
+      <c r="C14" s="86">
         <v>4.9000000000000004</v>
       </c>
       <c r="D14" s="6">
         <v>12463.930229580003</v>
       </c>
-      <c r="E14" s="58">
+      <c r="E14" s="57">
         <f t="shared" si="0"/>
         <v>12463.930229580003</v>
       </c>
-      <c r="F14" s="23">
-        <v>0</v>
-      </c>
-      <c r="G14" s="21">
-        <v>0</v>
-      </c>
-      <c r="H14" s="27">
-        <v>0</v>
-      </c>
-      <c r="I14" s="17">
+      <c r="F14" s="22">
+        <v>0</v>
+      </c>
+      <c r="G14" s="20">
+        <v>0</v>
+      </c>
+      <c r="H14" s="26">
+        <v>0</v>
+      </c>
+      <c r="I14" s="16">
         <v>0.49</v>
       </c>
-      <c r="J14" s="23">
+      <c r="J14" s="22">
         <v>10358.243625421999</v>
       </c>
-      <c r="K14" s="29">
-        <v>0</v>
-      </c>
-      <c r="L14" s="21">
+      <c r="K14" s="28">
+        <v>0</v>
+      </c>
+      <c r="L14" s="20">
         <v>10358.243625421999</v>
       </c>
-      <c r="M14" s="18"/>
+      <c r="M14" s="17"/>
       <c r="N14" s="6">
         <v>10358.243625421999</v>
       </c>
@@ -7027,44 +7056,44 @@
       </c>
     </row>
     <row r="15" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="15">
+      <c r="A15" s="14">
         <v>9</v>
       </c>
-      <c r="B15" s="84" t="s">
+      <c r="B15" s="83" t="s">
         <v>52</v>
       </c>
-      <c r="C15" s="87">
+      <c r="C15" s="86">
         <v>4.9000000000000004</v>
       </c>
       <c r="D15" s="6">
         <v>12463.930229580003</v>
       </c>
-      <c r="E15" s="58">
+      <c r="E15" s="57">
         <f t="shared" si="0"/>
         <v>12463.930229580003</v>
       </c>
-      <c r="F15" s="23">
-        <v>0</v>
-      </c>
-      <c r="G15" s="21">
-        <v>0</v>
-      </c>
-      <c r="H15" s="27">
-        <v>0</v>
-      </c>
-      <c r="I15" s="17">
+      <c r="F15" s="22">
+        <v>0</v>
+      </c>
+      <c r="G15" s="20">
+        <v>0</v>
+      </c>
+      <c r="H15" s="26">
+        <v>0</v>
+      </c>
+      <c r="I15" s="16">
         <v>0.49</v>
       </c>
-      <c r="J15" s="23">
+      <c r="J15" s="22">
         <v>10358.243625421999</v>
       </c>
-      <c r="K15" s="29">
-        <v>0</v>
-      </c>
-      <c r="L15" s="21">
+      <c r="K15" s="28">
+        <v>0</v>
+      </c>
+      <c r="L15" s="20">
         <v>10358.243625421999</v>
       </c>
-      <c r="M15" s="18"/>
+      <c r="M15" s="17"/>
       <c r="N15" s="6">
         <v>10358.243625421999</v>
       </c>
@@ -7073,44 +7102,44 @@
       </c>
     </row>
     <row r="16" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="15">
+      <c r="A16" s="14">
         <v>10</v>
       </c>
-      <c r="B16" s="84" t="s">
+      <c r="B16" s="83" t="s">
         <v>62</v>
       </c>
-      <c r="C16" s="87">
+      <c r="C16" s="86">
         <v>5.9</v>
       </c>
       <c r="D16" s="6">
         <v>15470.548643780005</v>
       </c>
-      <c r="E16" s="58">
+      <c r="E16" s="57">
         <f t="shared" si="0"/>
         <v>15470.548643780005</v>
       </c>
-      <c r="F16" s="23">
-        <v>0</v>
-      </c>
-      <c r="G16" s="21">
-        <v>0</v>
-      </c>
-      <c r="H16" s="27">
-        <v>0</v>
-      </c>
-      <c r="I16" s="17">
+      <c r="F16" s="22">
+        <v>0</v>
+      </c>
+      <c r="G16" s="20">
+        <v>0</v>
+      </c>
+      <c r="H16" s="26">
+        <v>0</v>
+      </c>
+      <c r="I16" s="16">
         <v>0.59</v>
       </c>
-      <c r="J16" s="23">
+      <c r="J16" s="22">
         <v>12858.156610202001</v>
       </c>
-      <c r="K16" s="29">
-        <v>0</v>
-      </c>
-      <c r="L16" s="21">
+      <c r="K16" s="28">
+        <v>0</v>
+      </c>
+      <c r="L16" s="20">
         <v>12858.156610202001</v>
       </c>
-      <c r="M16" s="18"/>
+      <c r="M16" s="17"/>
       <c r="N16" s="6">
         <v>12858.156610202001</v>
       </c>
@@ -7119,44 +7148,44 @@
       </c>
     </row>
     <row r="17" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="15">
+      <c r="A17" s="14">
         <v>11</v>
       </c>
-      <c r="B17" s="84" t="s">
+      <c r="B17" s="83" t="s">
         <v>62</v>
       </c>
-      <c r="C17" s="87">
+      <c r="C17" s="86">
         <v>5.7</v>
       </c>
       <c r="D17" s="6">
         <v>14869.224960940002</v>
       </c>
-      <c r="E17" s="58">
+      <c r="E17" s="57">
         <f t="shared" si="0"/>
         <v>14869.224960940002</v>
       </c>
-      <c r="F17" s="23">
-        <v>0</v>
-      </c>
-      <c r="G17" s="21">
-        <v>0</v>
-      </c>
-      <c r="H17" s="27">
-        <v>0</v>
-      </c>
-      <c r="I17" s="17">
+      <c r="F17" s="22">
+        <v>0</v>
+      </c>
+      <c r="G17" s="20">
+        <v>0</v>
+      </c>
+      <c r="H17" s="26">
+        <v>0</v>
+      </c>
+      <c r="I17" s="16">
         <v>0.56999999999999995</v>
       </c>
-      <c r="J17" s="23">
+      <c r="J17" s="22">
         <v>12358.174013246</v>
       </c>
-      <c r="K17" s="29">
-        <v>0</v>
-      </c>
-      <c r="L17" s="21">
+      <c r="K17" s="28">
+        <v>0</v>
+      </c>
+      <c r="L17" s="20">
         <v>12358.174013246</v>
       </c>
-      <c r="M17" s="18"/>
+      <c r="M17" s="17"/>
       <c r="N17" s="6">
         <v>12358.174013246</v>
       </c>
@@ -7165,44 +7194,44 @@
       </c>
     </row>
     <row r="18" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="15">
+      <c r="A18" s="14">
         <v>12</v>
       </c>
-      <c r="B18" s="84" t="s">
+      <c r="B18" s="83" t="s">
         <v>50</v>
       </c>
-      <c r="C18" s="87">
+      <c r="C18" s="86">
         <v>5.4</v>
       </c>
       <c r="D18" s="6">
         <v>13967.239436680005</v>
       </c>
-      <c r="E18" s="58">
+      <c r="E18" s="57">
         <f t="shared" si="0"/>
         <v>13967.239436680005</v>
       </c>
-      <c r="F18" s="23">
-        <v>0</v>
-      </c>
-      <c r="G18" s="21">
-        <v>0</v>
-      </c>
-      <c r="H18" s="27">
-        <v>0</v>
-      </c>
-      <c r="I18" s="17">
+      <c r="F18" s="22">
+        <v>0</v>
+      </c>
+      <c r="G18" s="20">
+        <v>0</v>
+      </c>
+      <c r="H18" s="26">
+        <v>0</v>
+      </c>
+      <c r="I18" s="16">
         <v>0.54</v>
       </c>
-      <c r="J18" s="23">
+      <c r="J18" s="22">
         <v>11608.200117812001</v>
       </c>
-      <c r="K18" s="29">
-        <v>0</v>
-      </c>
-      <c r="L18" s="21">
+      <c r="K18" s="28">
+        <v>0</v>
+      </c>
+      <c r="L18" s="20">
         <v>11608.200117812001</v>
       </c>
-      <c r="M18" s="18"/>
+      <c r="M18" s="17"/>
       <c r="N18" s="6">
         <v>11608.200117812001</v>
       </c>
@@ -7211,44 +7240,44 @@
       </c>
     </row>
     <row r="19" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="15">
+      <c r="A19" s="14">
         <v>13</v>
       </c>
-      <c r="B19" s="84" t="s">
+      <c r="B19" s="83" t="s">
         <v>66</v>
       </c>
-      <c r="C19" s="87">
+      <c r="C19" s="86">
         <v>5.5</v>
       </c>
       <c r="D19" s="6">
         <v>14267.901278100004</v>
       </c>
-      <c r="E19" s="58">
+      <c r="E19" s="57">
         <f t="shared" si="0"/>
         <v>14267.901278100004</v>
       </c>
-      <c r="F19" s="23">
-        <v>0</v>
-      </c>
-      <c r="G19" s="21">
-        <v>0</v>
-      </c>
-      <c r="H19" s="27">
-        <v>0</v>
-      </c>
-      <c r="I19" s="17">
+      <c r="F19" s="22">
+        <v>0</v>
+      </c>
+      <c r="G19" s="20">
+        <v>0</v>
+      </c>
+      <c r="H19" s="26">
+        <v>0</v>
+      </c>
+      <c r="I19" s="16">
         <v>0.55000000000000004</v>
       </c>
-      <c r="J19" s="23">
+      <c r="J19" s="22">
         <v>11858.191416289999</v>
       </c>
-      <c r="K19" s="29">
-        <v>0</v>
-      </c>
-      <c r="L19" s="21">
+      <c r="K19" s="28">
+        <v>0</v>
+      </c>
+      <c r="L19" s="20">
         <v>11858.191416289999</v>
       </c>
-      <c r="M19" s="18"/>
+      <c r="M19" s="17"/>
       <c r="N19" s="6">
         <v>11858.191416289999</v>
       </c>
@@ -7257,44 +7286,44 @@
       </c>
     </row>
     <row r="20" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="15">
+      <c r="A20" s="14">
         <v>14</v>
       </c>
-      <c r="B20" s="84" t="s">
+      <c r="B20" s="83" t="s">
         <v>66</v>
       </c>
-      <c r="C20" s="87">
+      <c r="C20" s="86">
         <v>4.5</v>
       </c>
       <c r="D20" s="6">
         <v>11261.282863900002</v>
       </c>
-      <c r="E20" s="58">
+      <c r="E20" s="57">
         <f t="shared" si="0"/>
         <v>11261.282863900002</v>
       </c>
-      <c r="F20" s="23">
-        <v>0</v>
-      </c>
-      <c r="G20" s="21">
-        <v>0</v>
-      </c>
-      <c r="H20" s="27">
-        <v>0</v>
-      </c>
-      <c r="I20" s="17">
+      <c r="F20" s="22">
+        <v>0</v>
+      </c>
+      <c r="G20" s="20">
+        <v>0</v>
+      </c>
+      <c r="H20" s="26">
+        <v>0</v>
+      </c>
+      <c r="I20" s="16">
         <v>0.45</v>
       </c>
-      <c r="J20" s="23">
+      <c r="J20" s="22">
         <v>9358.278431509998</v>
       </c>
-      <c r="K20" s="29">
-        <v>0</v>
-      </c>
-      <c r="L20" s="21">
+      <c r="K20" s="28">
+        <v>0</v>
+      </c>
+      <c r="L20" s="20">
         <v>9358.278431509998</v>
       </c>
-      <c r="M20" s="18"/>
+      <c r="M20" s="17"/>
       <c r="N20" s="6">
         <v>9358.278431509998</v>
       </c>
@@ -7303,44 +7332,44 @@
       </c>
     </row>
     <row r="21" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="15">
+      <c r="A21" s="14">
         <v>15</v>
       </c>
-      <c r="B21" s="84" t="s">
+      <c r="B21" s="83" t="s">
         <v>66</v>
       </c>
-      <c r="C21" s="87">
+      <c r="C21" s="86">
         <v>6.1</v>
       </c>
       <c r="D21" s="6">
         <v>16071.872326620005</v>
       </c>
-      <c r="E21" s="58">
+      <c r="E21" s="57">
         <f t="shared" si="0"/>
         <v>16071.872326620005</v>
       </c>
-      <c r="F21" s="23">
-        <v>0</v>
-      </c>
-      <c r="G21" s="21">
+      <c r="F21" s="22">
+        <v>0</v>
+      </c>
+      <c r="G21" s="20">
         <v>0</v>
       </c>
       <c r="H21" s="6">
         <v>0</v>
       </c>
-      <c r="I21" s="17">
+      <c r="I21" s="16">
         <v>0.61</v>
       </c>
-      <c r="J21" s="23">
+      <c r="J21" s="22">
         <v>13358.139207157999</v>
       </c>
-      <c r="K21" s="29">
-        <v>0</v>
-      </c>
-      <c r="L21" s="21">
+      <c r="K21" s="28">
+        <v>0</v>
+      </c>
+      <c r="L21" s="20">
         <v>13358.139207157999</v>
       </c>
-      <c r="M21" s="18"/>
+      <c r="M21" s="17"/>
       <c r="N21" s="6">
         <v>13358.139207157999</v>
       </c>
@@ -7349,44 +7378,44 @@
       </c>
     </row>
     <row r="22" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="15">
+      <c r="A22" s="14">
         <v>16</v>
       </c>
-      <c r="B22" s="84" t="s">
+      <c r="B22" s="83" t="s">
         <v>53</v>
       </c>
-      <c r="C22" s="87">
+      <c r="C22" s="86">
         <v>5.4</v>
       </c>
       <c r="D22" s="6">
         <v>13967.239436680005</v>
       </c>
-      <c r="E22" s="58">
+      <c r="E22" s="57">
         <f t="shared" si="0"/>
         <v>13967.239436680005</v>
       </c>
-      <c r="F22" s="23">
-        <v>0</v>
-      </c>
-      <c r="G22" s="21">
-        <v>0</v>
-      </c>
-      <c r="H22" s="27">
-        <v>0</v>
-      </c>
-      <c r="I22" s="17">
+      <c r="F22" s="22">
+        <v>0</v>
+      </c>
+      <c r="G22" s="20">
+        <v>0</v>
+      </c>
+      <c r="H22" s="26">
+        <v>0</v>
+      </c>
+      <c r="I22" s="16">
         <v>0.54</v>
       </c>
-      <c r="J22" s="23">
+      <c r="J22" s="22">
         <v>11608.200117812001</v>
       </c>
-      <c r="K22" s="29">
-        <v>0</v>
-      </c>
-      <c r="L22" s="21">
+      <c r="K22" s="28">
+        <v>0</v>
+      </c>
+      <c r="L22" s="20">
         <v>11608.200117812001</v>
       </c>
-      <c r="M22" s="18"/>
+      <c r="M22" s="17"/>
       <c r="N22" s="6">
         <v>11608.200117812001</v>
       </c>
@@ -7395,44 +7424,44 @@
       </c>
     </row>
     <row r="23" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="15">
+      <c r="A23" s="14">
         <v>17</v>
       </c>
-      <c r="B23" s="84" t="s">
+      <c r="B23" s="83" t="s">
         <v>55</v>
       </c>
-      <c r="C23" s="87">
+      <c r="C23" s="86">
         <v>5</v>
       </c>
       <c r="D23" s="6">
         <v>12764.592071000003</v>
       </c>
-      <c r="E23" s="58">
+      <c r="E23" s="57">
         <f t="shared" si="0"/>
         <v>12764.592071000003</v>
       </c>
-      <c r="F23" s="23">
-        <v>0</v>
-      </c>
-      <c r="G23" s="21">
-        <v>0</v>
-      </c>
-      <c r="H23" s="27">
-        <v>0</v>
-      </c>
-      <c r="I23" s="17">
+      <c r="F23" s="22">
+        <v>0</v>
+      </c>
+      <c r="G23" s="20">
+        <v>0</v>
+      </c>
+      <c r="H23" s="26">
+        <v>0</v>
+      </c>
+      <c r="I23" s="16">
         <v>0.5</v>
       </c>
-      <c r="J23" s="23">
+      <c r="J23" s="22">
         <v>10608.2349239</v>
       </c>
-      <c r="K23" s="29">
-        <v>0</v>
-      </c>
-      <c r="L23" s="21">
+      <c r="K23" s="28">
+        <v>0</v>
+      </c>
+      <c r="L23" s="20">
         <v>10608.2349239</v>
       </c>
-      <c r="M23" s="18"/>
+      <c r="M23" s="17"/>
       <c r="N23" s="6">
         <v>10608.2349239</v>
       </c>
@@ -7441,44 +7470,44 @@
       </c>
     </row>
     <row r="24" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="15">
+      <c r="A24" s="14">
         <v>18</v>
       </c>
-      <c r="B24" s="84" t="s">
+      <c r="B24" s="83" t="s">
         <v>47</v>
       </c>
-      <c r="C24" s="87">
+      <c r="C24" s="86">
         <v>5</v>
       </c>
       <c r="D24" s="6">
         <v>12764.592071000003</v>
       </c>
-      <c r="E24" s="58">
+      <c r="E24" s="57">
         <f t="shared" si="0"/>
         <v>12764.592071000003</v>
       </c>
-      <c r="F24" s="23">
-        <v>0</v>
-      </c>
-      <c r="G24" s="21">
-        <v>0</v>
-      </c>
-      <c r="H24" s="27">
-        <v>0</v>
-      </c>
-      <c r="I24" s="17">
+      <c r="F24" s="22">
+        <v>0</v>
+      </c>
+      <c r="G24" s="20">
+        <v>0</v>
+      </c>
+      <c r="H24" s="26">
+        <v>0</v>
+      </c>
+      <c r="I24" s="16">
         <v>0.5</v>
       </c>
-      <c r="J24" s="23">
+      <c r="J24" s="22">
         <v>10608.2349239</v>
       </c>
-      <c r="K24" s="29">
-        <v>0</v>
-      </c>
-      <c r="L24" s="21">
+      <c r="K24" s="28">
+        <v>0</v>
+      </c>
+      <c r="L24" s="20">
         <v>10608.2349239</v>
       </c>
-      <c r="M24" s="18"/>
+      <c r="M24" s="17"/>
       <c r="N24" s="6">
         <v>10608.2349239</v>
       </c>
@@ -7487,44 +7516,44 @@
       </c>
     </row>
     <row r="25" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="15">
+      <c r="A25" s="14">
         <v>19</v>
       </c>
-      <c r="B25" s="84" t="s">
+      <c r="B25" s="83" t="s">
         <v>47</v>
       </c>
-      <c r="C25" s="87">
+      <c r="C25" s="86">
         <v>4.9000000000000004</v>
       </c>
       <c r="D25" s="6">
         <v>12463.930229580003</v>
       </c>
-      <c r="E25" s="58">
+      <c r="E25" s="57">
         <f t="shared" si="0"/>
         <v>12463.930229580003</v>
       </c>
-      <c r="F25" s="23">
-        <v>0</v>
-      </c>
-      <c r="G25" s="21">
-        <v>0</v>
-      </c>
-      <c r="H25" s="27">
-        <v>0</v>
-      </c>
-      <c r="I25" s="17">
+      <c r="F25" s="22">
+        <v>0</v>
+      </c>
+      <c r="G25" s="20">
+        <v>0</v>
+      </c>
+      <c r="H25" s="26">
+        <v>0</v>
+      </c>
+      <c r="I25" s="16">
         <v>0.49</v>
       </c>
-      <c r="J25" s="23">
+      <c r="J25" s="22">
         <v>10358.243625421999</v>
       </c>
-      <c r="K25" s="29">
-        <v>0</v>
-      </c>
-      <c r="L25" s="21">
+      <c r="K25" s="28">
+        <v>0</v>
+      </c>
+      <c r="L25" s="20">
         <v>10358.243625421999</v>
       </c>
-      <c r="M25" s="18"/>
+      <c r="M25" s="17"/>
       <c r="N25" s="6">
         <v>10358.243625421999</v>
       </c>
@@ -7533,44 +7562,44 @@
       </c>
     </row>
     <row r="26" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="15">
+      <c r="A26" s="14">
         <v>20</v>
       </c>
-      <c r="B26" s="84" t="s">
+      <c r="B26" s="83" t="s">
         <v>85</v>
       </c>
-      <c r="C26" s="87">
+      <c r="C26" s="86">
         <v>4.9000000000000004</v>
       </c>
       <c r="D26" s="6">
         <v>12463.930229580003</v>
       </c>
-      <c r="E26" s="58">
+      <c r="E26" s="57">
         <f t="shared" si="0"/>
         <v>12463.930229580003</v>
       </c>
-      <c r="F26" s="23">
-        <v>0</v>
-      </c>
-      <c r="G26" s="21">
-        <v>0</v>
-      </c>
-      <c r="H26" s="27">
-        <v>0</v>
-      </c>
-      <c r="I26" s="17">
+      <c r="F26" s="22">
+        <v>0</v>
+      </c>
+      <c r="G26" s="20">
+        <v>0</v>
+      </c>
+      <c r="H26" s="26">
+        <v>0</v>
+      </c>
+      <c r="I26" s="16">
         <v>0.49</v>
       </c>
-      <c r="J26" s="23">
+      <c r="J26" s="22">
         <v>10358.243625421999</v>
       </c>
-      <c r="K26" s="29">
-        <v>0</v>
-      </c>
-      <c r="L26" s="21">
+      <c r="K26" s="28">
+        <v>0</v>
+      </c>
+      <c r="L26" s="20">
         <v>10358.243625421999</v>
       </c>
-      <c r="M26" s="18"/>
+      <c r="M26" s="17"/>
       <c r="N26" s="6">
         <v>10358.243625421999</v>
       </c>
@@ -7579,44 +7608,44 @@
       </c>
     </row>
     <row r="27" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="15">
+      <c r="A27" s="14">
         <v>21</v>
       </c>
-      <c r="B27" s="84" t="s">
+      <c r="B27" s="83" t="s">
         <v>42</v>
       </c>
-      <c r="C27" s="87">
+      <c r="C27" s="86">
         <v>5.9</v>
       </c>
       <c r="D27" s="6">
         <v>15470.548643780005</v>
       </c>
-      <c r="E27" s="58">
+      <c r="E27" s="57">
         <f t="shared" si="0"/>
         <v>15470.548643780005</v>
       </c>
-      <c r="F27" s="23">
-        <v>0</v>
-      </c>
-      <c r="G27" s="21">
-        <v>0</v>
-      </c>
-      <c r="H27" s="27">
-        <v>0</v>
-      </c>
-      <c r="I27" s="17">
+      <c r="F27" s="22">
+        <v>0</v>
+      </c>
+      <c r="G27" s="20">
+        <v>0</v>
+      </c>
+      <c r="H27" s="26">
+        <v>0</v>
+      </c>
+      <c r="I27" s="16">
         <v>0.59</v>
       </c>
-      <c r="J27" s="23">
+      <c r="J27" s="22">
         <v>12858.156610202001</v>
       </c>
-      <c r="K27" s="29">
-        <v>0</v>
-      </c>
-      <c r="L27" s="21">
+      <c r="K27" s="28">
+        <v>0</v>
+      </c>
+      <c r="L27" s="20">
         <v>12858.156610202001</v>
       </c>
-      <c r="M27" s="18"/>
+      <c r="M27" s="17"/>
       <c r="N27" s="6">
         <v>12858.156610202001</v>
       </c>
@@ -7625,44 +7654,44 @@
       </c>
     </row>
     <row r="28" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="15">
+      <c r="A28" s="14">
         <v>22</v>
       </c>
-      <c r="B28" s="86" t="s">
+      <c r="B28" s="85" t="s">
         <v>49</v>
       </c>
-      <c r="C28" s="87">
+      <c r="C28" s="86">
         <v>5.7</v>
       </c>
       <c r="D28" s="6">
         <v>14869.224960940002</v>
       </c>
-      <c r="E28" s="58">
+      <c r="E28" s="57">
         <f t="shared" si="0"/>
         <v>14869.224960940002</v>
       </c>
-      <c r="F28" s="23">
-        <v>0</v>
-      </c>
-      <c r="G28" s="21">
-        <v>0</v>
-      </c>
-      <c r="H28" s="27">
-        <v>0</v>
-      </c>
-      <c r="I28" s="17">
+      <c r="F28" s="22">
+        <v>0</v>
+      </c>
+      <c r="G28" s="20">
+        <v>0</v>
+      </c>
+      <c r="H28" s="26">
+        <v>0</v>
+      </c>
+      <c r="I28" s="16">
         <v>0.56999999999999995</v>
       </c>
-      <c r="J28" s="23">
+      <c r="J28" s="22">
         <v>12358.174013246</v>
       </c>
-      <c r="K28" s="29">
-        <v>0</v>
-      </c>
-      <c r="L28" s="21">
+      <c r="K28" s="28">
+        <v>0</v>
+      </c>
+      <c r="L28" s="20">
         <v>12358.174013246</v>
       </c>
-      <c r="M28" s="18"/>
+      <c r="M28" s="17"/>
       <c r="N28" s="6">
         <v>12358.174013246</v>
       </c>
@@ -7671,66 +7700,66 @@
       </c>
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A29" s="15"/>
-      <c r="B29" s="34"/>
-      <c r="C29" s="34"/>
+      <c r="A29" s="14"/>
+      <c r="B29" s="33"/>
+      <c r="C29" s="33"/>
       <c r="D29" s="6"/>
       <c r="E29" s="6"/>
-      <c r="F29" s="23"/>
-      <c r="G29" s="21"/>
-      <c r="H29" s="27"/>
-      <c r="I29" s="17"/>
-      <c r="J29" s="23"/>
-      <c r="K29" s="29"/>
-      <c r="L29" s="21"/>
-      <c r="M29" s="18"/>
+      <c r="F29" s="22"/>
+      <c r="G29" s="20"/>
+      <c r="H29" s="26"/>
+      <c r="I29" s="16"/>
+      <c r="J29" s="22"/>
+      <c r="K29" s="28"/>
+      <c r="L29" s="20"/>
+      <c r="M29" s="17"/>
       <c r="N29" s="6"/>
       <c r="O29" s="6"/>
     </row>
     <row r="30" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="13"/>
-      <c r="B30" s="14"/>
-      <c r="C30" s="57">
+      <c r="A30" s="12"/>
+      <c r="B30" s="13"/>
+      <c r="C30" s="56">
         <v>116.60000000000001</v>
       </c>
-      <c r="D30" s="26">
+      <c r="D30" s="25">
         <v>161487.47195715201</v>
       </c>
-      <c r="E30" s="30">
+      <c r="E30" s="29">
         <v>161487.47195715201</v>
       </c>
-      <c r="F30" s="28">
-        <v>0</v>
-      </c>
-      <c r="G30" s="32">
-        <v>0</v>
-      </c>
-      <c r="H30" s="31">
-        <v>0</v>
-      </c>
-      <c r="I30" s="16">
+      <c r="F30" s="27">
+        <v>0</v>
+      </c>
+      <c r="G30" s="31">
+        <v>0</v>
+      </c>
+      <c r="H30" s="30">
+        <v>0</v>
+      </c>
+      <c r="I30" s="15">
         <v>11.66</v>
       </c>
-      <c r="J30" s="24">
+      <c r="J30" s="23">
         <v>249880.59402534799</v>
       </c>
-      <c r="K30" s="25">
-        <v>0</v>
-      </c>
-      <c r="L30" s="22">
+      <c r="K30" s="24">
+        <v>0</v>
+      </c>
+      <c r="L30" s="21">
         <v>249880.59402534799</v>
       </c>
-      <c r="M30" s="19"/>
-      <c r="N30" s="20">
+      <c r="M30" s="18"/>
+      <c r="N30" s="19">
         <v>249880.59402534799</v>
       </c>
-      <c r="O30" s="20">
+      <c r="O30" s="19">
         <v>264873.42966686888</v>
       </c>
     </row>
     <row r="33" spans="5:6" x14ac:dyDescent="0.25">
-      <c r="E33" s="33"/>
-      <c r="F33" s="33"/>
+      <c r="E33" s="32"/>
+      <c r="F33" s="32"/>
     </row>
   </sheetData>
   <mergeCells count="5">
